--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -1978,7 +1978,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>transition — 10 Sep 3 W9 producer stops kept (built from K-R15)</t>
+          <t>transition — 10 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from K-R15)</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>transition — 7 Sep 3 W9 producer stops kept (built from K-R18)</t>
+          <t>transition — 7 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from K-R18)</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>transition — 8 Sep 3 W9 producer stops kept (built from K-R20)</t>
+          <t>transition — 8 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from K-R20)</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>transition — 9 Sep 3 W9 producer stops kept (built from K-R27)</t>
+          <t>transition — 9 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from K-R27)</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>transition — 2 Sep 3 W9 producer stops kept (built from K-R29)</t>
+          <t>transition — 2 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from K-R29)</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -2641,7 +2641,11 @@
           <t>Imlay City (3) • Yale (2)</t>
         </is>
       </c>
-      <c r="J48" s="3" t="n"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>SHORT DAY (5 stops): nothing else due within reach — finish early or add nearby not-yet-due prospects</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=333%20Gordon%20Drive%2C%20Yale%2C%20Michigan%2C%2048097&amp;waypoints=147%20N%20Almont%20Ave%2C%20Imlay%20City%2C%20Michigan%2C%2048444%7C6672%20Newark%20Road%2C%20Imlay%20City%2C%20MI%2048444%7C1834%20S%20Cedar%20St%2C%20Imlay%20City%2C%20Michigan%2C%2048444%7C7470%20South%20Brockway%20Road%2C%20Yale%2C%20Michigan%2C%2048097</t>
@@ -2767,7 +2771,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Warren (6) • St. Clair Shores (1)</t>
+          <t>Warren (6) • St Clair Shores (2)</t>
         </is>
       </c>
       <c r="J51" s="3" t="n"/>
@@ -22220,7 +22224,7 @@
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
-          <t>Saint Clair</t>
+          <t>St Clair</t>
         </is>
       </c>
       <c r="L309" s="3" t="inlineStr">
@@ -22280,7 +22284,7 @@
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
-          <t>Saint Clair</t>
+          <t>St Clair</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr">
@@ -30740,7 +30744,7 @@
       </c>
       <c r="K451" s="2" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L451" s="3" t="inlineStr">
@@ -30800,7 +30804,7 @@
       </c>
       <c r="K452" s="2" t="inlineStr">
         <is>
-          <t>Saint Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr">
@@ -36200,7 +36204,7 @@
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr">
@@ -36260,7 +36264,7 @@
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
-          <t>Saint Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L543" s="3" t="inlineStr">
@@ -37675,7 +37679,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="6" t="inlineStr">
@@ -37711,12 +37715,12 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Port Huron (5) • Marysville (2) • Saint Clair (2)</t>
+          <t>Port Huron (5) • Marysville (2) • St Clair (2)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -38264,7 +38268,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>St. Clair Shores (3) • Roseville (3) • Saint Clair Shores (2)</t>
+          <t>St Clair Shores (5) • Roseville (3) • Warren (2)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -38464,7 +38468,9 @@
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="5" t="n"/>
+      <c r="G27" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -38566,7 +38572,9 @@
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="5" t="n"/>
+      <c r="G30" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -38635,7 +38643,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="6" t="inlineStr">
@@ -39742,7 +39750,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Fort Gratiot</t>
+          <t>Fort Gratiot Township</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -39978,7 +39986,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Saint Clair</t>
+          <t>St Clair</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -40387,7 +40395,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Saint Clair</t>
+          <t>St Clair</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -40560,7 +40568,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Bruce Township</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -40796,7 +40804,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Bruce Township</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -41830,7 +41838,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -42349,7 +42357,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Bloomfield Township</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
@@ -42805,7 +42813,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -42864,7 +42872,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Mt. Clemens</t>
+          <t>Mount Clemens</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -42923,7 +42931,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Macomb</t>
+          <t>Macomb Township</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -43151,7 +43159,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Commerce Charter Township</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -43269,7 +43277,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -43328,7 +43336,7 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
@@ -43619,7 +43627,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Commerce Charter Township</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -46633,7 +46641,7 @@
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>West Bloomfield Township</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -49748,7 +49756,7 @@
       </c>
       <c r="J191" s="5" t="inlineStr">
         <is>
-          <t>Saint Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K191" s="6" t="inlineStr">
@@ -49807,7 +49815,7 @@
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K192" s="6" t="inlineStr">
@@ -49866,7 +49874,7 @@
       </c>
       <c r="J193" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K193" s="6" t="inlineStr">
@@ -50031,7 +50039,7 @@
       </c>
       <c r="J196" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K196" s="6" t="inlineStr">
@@ -50090,7 +50098,7 @@
       </c>
       <c r="J197" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K197" s="6" t="inlineStr">
@@ -50377,7 +50385,7 @@
       </c>
       <c r="J202" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
@@ -57275,7 +57283,7 @@
       </c>
       <c r="J320" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>West Bloomfield Township</t>
         </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
@@ -57334,7 +57342,7 @@
       </c>
       <c r="J321" s="5" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Bloomfield Township</t>
         </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
@@ -57422,7 +57430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="15" min="1" max="1"/>
@@ -57853,86 +57861,86 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>K-A09</t>
+          <t>K-A08, K-A19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>K-A23, K-A26</t>
+          <t>K-A09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
@@ -57941,51 +57949,51 @@
         <v>5</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>K-A22</t>
+          <t>K-A23, K-A26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Bingham Farms</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>K-A15</t>
+          <t>K-A22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Bingham Farms</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -57995,10 +58003,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
@@ -58011,27 +58019,27 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>K-A20</t>
+          <t>K-A15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Royal Oak</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0</v>
@@ -58040,18 +58048,18 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>K-A21</t>
+          <t>K-A20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Rochester Hills</t>
+          <t>Royal Oak</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -58070,28 +58078,28 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>K-A05</t>
+          <t>K-A21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Allen Park</t>
+          <t>Rochester Hills</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>2</v>
@@ -58100,24 +58108,24 @@
         <v>1</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>K-A30</t>
+          <t>K-A05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Fort Gratiot</t>
+          <t>Allen Park</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -58130,10 +58138,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -58143,14 +58151,14 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>K-A02</t>
+          <t>K-A30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Shelby Township</t>
+          <t>Fort Gratiot</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -58160,40 +58168,40 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>K-A06</t>
+          <t>K-A02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>St. Clair Shores</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
@@ -58202,14 +58210,14 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>K-A08, K-A19</t>
+          <t>K-A06</t>
         </is>
       </c>
     </row>
@@ -58447,40 +58455,40 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Saint Clair Shores</t>
+          <t>Bloomfield Hills</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>K-A19</t>
+          <t>K-A07, K-A15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Bloomfield Hills</t>
+          <t>Imlay City</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -58490,30 +58498,30 @@
         <v>0</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>K-A07, K-A15</t>
+          <t>K-A01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Imlay City</t>
+          <t>Hazel Park</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -58523,13 +58531,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
@@ -58539,47 +58547,47 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>K-A01</t>
+          <t>K-A23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Hazel Park</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>K-A23</t>
+          <t>K-A27, K-A29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Walled Lake</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -58589,10 +58597,10 @@
         <v>1</v>
       </c>
       <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
@@ -58605,24 +58613,24 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>K-A27, K-A29</t>
+          <t>K-A20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Walled Lake</t>
+          <t>Lathrup Village</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>1</v>
@@ -58631,64 +58639,64 @@
         <v>0</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>K-A20</t>
+          <t>K-A15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Lathrup Village</t>
+          <t>Bloomfield</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>K-A15</t>
+          <t>K-A07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Bloomfield</t>
+          <t>Pontiac</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>0</v>
@@ -58697,7 +58705,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>1</v>
@@ -58711,7 +58719,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Pontiac</t>
+          <t>Center Line</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -58737,14 +58745,14 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>K-A07</t>
+          <t>K-A23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Center Line</t>
+          <t>Marysville</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -58766,28 +58774,28 @@
         <v>0</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>K-A23</t>
+          <t>K-A03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Marysville</t>
+          <t>Northville</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
@@ -58796,21 +58804,21 @@
         <v>0</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>K-A03</t>
+          <t>K-A20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Northville</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -58832,28 +58840,28 @@
         <v>3</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>K-A20</t>
+          <t>K-A28, K-A30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
@@ -58865,28 +58873,28 @@
         <v>3</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>K-A28, K-A30</t>
+          <t>K-A28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
@@ -58895,87 +58903,87 @@
         <v>0</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>K-A28</t>
+          <t>K-A01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>K-A01</t>
+          <t>K-A04</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>K-A04</t>
+          <t>K-A15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bruce Township</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -58997,18 +59005,18 @@
         <v>0</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>K-A15</t>
+          <t>K-A04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Bruce Township</t>
+          <t>St Clair</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -59018,40 +59026,40 @@
         <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>K-A04</t>
+          <t>K-A03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Saint Clair</t>
+          <t>Redford Charter Township</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
@@ -59060,21 +59068,21 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>K-A03</t>
+          <t>K-A25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Redford Charter Township</t>
+          <t>Ypsilanti</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -59093,32 +59101,32 @@
         <v>0</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>K-A25</t>
+          <t>K-A27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Ypsilanti</t>
+          <t>Beverly Hills</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E52" s="5" t="n">
         <v>0</v>
       </c>
@@ -59126,21 +59134,21 @@
         <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>K-A27</t>
+          <t>K-A15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -59166,14 +59174,14 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>K-A15</t>
+          <t>K-A05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Clawson</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -59183,13 +59191,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
@@ -59199,21 +59207,21 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>K-A05</t>
+          <t>K-A13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Clawson</t>
+          <t>Redford</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
@@ -59222,35 +59230,35 @@
         <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>K-A13</t>
+          <t>K-A25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Redford</t>
+          <t>Kimball</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E56" s="5" t="n">
         <v>0</v>
       </c>
@@ -59258,54 +59266,54 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>K-A25</t>
+          <t>K-A03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Kimball</t>
+          <t>Fort Gratiot Township</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>K-A03</t>
+          <t>K-A02</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Fort Gratiot Township</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -59338,18 +59346,18 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Croswell</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
       </c>
@@ -59357,7 +59365,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>1</v>
@@ -59371,7 +59379,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Croswell</t>
+          <t>New Baltimore</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -59381,10 +59389,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0</v>
@@ -59397,14 +59405,14 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>K-A02</t>
+          <t>K-A04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>New Baltimore</t>
+          <t>Lenox</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -59414,10 +59422,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>0</v>
@@ -59437,17 +59445,17 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Lenox</t>
+          <t>Utica</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
@@ -59456,32 +59464,32 @@
         <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>K-A04</t>
+          <t>K-A06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Utica</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
@@ -59489,61 +59497,61 @@
         <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>K-A06</t>
-        </is>
-      </c>
+      <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>K-A15</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Oak Park</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E65" s="5" t="n">
         <v>0</v>
       </c>
@@ -59551,21 +59559,21 @@
         <v>0</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>K-A15</t>
+          <t>K-A21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Oak Park</t>
+          <t>Macomb Township</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -59591,14 +59599,14 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>K-A21</t>
+          <t>K-A08</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Macomb Township</t>
+          <t>Mount Clemens</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -59631,7 +59639,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Mount Clemens</t>
+          <t>Sylvan Lake</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -59641,13 +59649,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>0</v>
@@ -59657,21 +59665,21 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>K-A08</t>
+          <t>K-A07</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Sylvan Lake</t>
+          <t>White Lake</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -59680,13 +59688,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -59697,7 +59705,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>White Lake</t>
+          <t>White Lake Charter Township</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -59716,7 +59724,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>0</v>
@@ -59730,18 +59738,18 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>White Lake Charter Township</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
       </c>
@@ -59749,21 +59757,21 @@
         <v>0</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>K-A07</t>
+          <t>K-A15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Grosse Pointe Woods</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -59773,14 +59781,14 @@
         <v>0</v>
       </c>
       <c r="D72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G72" s="5" t="n">
         <v>0</v>
       </c>
@@ -59788,39 +59796,6 @@
         <v>0</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>K-A15</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Grosse Pointe Woods</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>K-A19</t>
         </is>

--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -2453,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
@@ -2462,17 +2462,17 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Commerce Township (4) • West Bloomfield (3)</t>
+          <t>Commerce Township (4) • West Bloomfield (4)</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2157%20ORCHARD%20LAKE%20RD%2C%20SYLVAN%20LAKE%2C%20Michigan&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0</v>
@@ -2505,17 +2505,17 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Farmington Hills (5) • Farmington (2)</t>
+          <t>Farmington Hills (6) • Farmington (2)</t>
         </is>
       </c>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6543%20TELEGRAPH%20RD%2C%20BLOOMFIELD%20TOWNSHIP%2C%20Michigan&amp;waypoints=32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152%7C17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075&amp;waypoints=32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152</t>
         </is>
       </c>
     </row>
@@ -2539,26 +2539,26 @@
         <v>10</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Hamtramck (4) • Roseville (2)</t>
+          <t>Hamtramck (4) • Madison Heights (2)</t>
         </is>
       </c>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=12169%20JOSEPH%20CAMPAU%20ST%2C%20HAMTRAMCK%2C%20MI%2C%2048212&amp;waypoints=26328%20Van%20Dyke%20Ave%2C%20Center%20Line%2C%20MI%2048015%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066%7C18245%20East%2010%20Mile%20Road%2C%20Ste%20120%2C%20Roseville%2C%20MI%2048066%7C20599%20Mack%20Ave%2C%20Grosse%20Pointe%20Woods%2C%20MI%2048236%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236%7C15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230%7C9230%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C9021%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%20nan%7C9421%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038&amp;waypoints=350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C26393%20Dequindre%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C12169%20JOSEPH%20CAMPAU%20ST%2C%20HAMTRAMCK%2C%20MI%2C%2048212%7C9421%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C9021%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%20nan%7C9230%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066</t>
         </is>
       </c>
     </row>
@@ -2582,26 +2582,26 @@
         <v>10</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>South Lyon (3) • Northville (2)</t>
+          <t>Northville (2) • Livonia (2)</t>
         </is>
       </c>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=28670%20Telegraph%20Road%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=12660%2010%20Mile%20Rd%2C%20South%20Lyon%2C%20MI%2048178%7C26006%20Pontiac%20Trail%2C%20South%20Lyon%2C%20MI%2C%2048178%7C23200%20Pontiac%20Trail%2C%20South%20Lyon%2C%20MI%2048178%7C2900%20Packard%20Street%2C%20Ypsilanti%2C%20Michigan%2C%2048197%7C5624%20Research%20Drive%2C%20Canton%2C%20Michigan%2C%2048188%7C38253%20Ann%20Arbor%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2900%20Packard%20Street%2C%20Ypsilanti%2C%20Michigan%2C%2048197&amp;waypoints=23200%20Pontiac%20Trail%2C%20South%20Lyon%2C%20MI%2048178%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C19000%20St%20Joe%27s%20Pkwy%20suite%20200%2C%20Livonia%2C%20Michigan%2C%2048152%7C38253%20Ann%20Arbor%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185%7C5624%20Research%20Drive%2C%20Canton%2C%20Michigan%2C%2048188</t>
         </is>
       </c>
     </row>
@@ -2685,13 +2685,13 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Sterling Heights (7) • Clinton Township (3)</t>
+          <t>Sterling Heights (6) • Clinton Township (3)</t>
         </is>
       </c>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038&amp;waypoints=41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313%7C42755%20Mound%20Rd%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C13425%2019%20Mile%20Rd%20Ste%20100%2C%20Sterling%20Heights%2C%20MI%2048313%7C13700%2019%20Mile%20Rd%2C%20Sterling%20Heights%2C%20MI%2048313%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038%7C43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310&amp;waypoints=41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C42755%20Mound%20Rd%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313%7C13425%2019%20Mile%20Rd%20Ste%20100%2C%20Sterling%20Heights%2C%20MI%2048313%7C13700%2019%20Mile%20Rd%2C%20Sterling%20Heights%2C%20MI%2048313%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038%7C43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088</t>
         </is>
       </c>
     </row>
@@ -2728,13 +2728,13 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Sterling Heights (4) • Troy (3)</t>
+          <t>Sterling Heights (5) • Troy (3)</t>
         </is>
       </c>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081&amp;waypoints=44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan%7C3940%20John%20R%20Road%2C%20Troy%2C%20MI%2048083%7C3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C2891%20E%20Maple%20Rd%20Ste%20102%2C%20Troy%2C%20MI%2C%2048083%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081&amp;waypoints=44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan%7C3940%20John%20R%20Road%2C%20Troy%2C%20MI%2048083%7C3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C2891%20E%20Maple%20Rd%20Ste%20102%2C%20Troy%2C%20MI%2C%2048083%7C2107%20East%2014%20Mile%20Road%2C%20Sterling%20Heights%2C%20MI%2048310%7C38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080</t>
         </is>
       </c>
     </row>
@@ -2771,13 +2771,13 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Warren (4) • Madison Heights (3)</t>
+          <t>Warren (4) • Sterling Heights (3)</t>
         </is>
       </c>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093&amp;waypoints=44225%20Utica%20Road%2C%20Utica%2C%20Michigan%2C%2048317%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C26393%20Dequindre%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C27650%20Dequindre%20Road%2C%20Suite%202000%2C%20Warren%2C%20Michigan%2C%2048092%7C29245%20Ryan%20Rd%20suite%20300%2C%20Warren%2C%20Michigan%2C%2048092%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310&amp;waypoints=64541%20Van%20Dyke%2C%20Washington%2C%20Michigan%2C%2048095%7C44225%20Utica%20Road%2C%20Utica%2C%20Michigan%2C%2048317%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093%7C29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093%7C29245%20Ryan%20Rd%20suite%20300%2C%20Warren%2C%20Michigan%2C%2048092%7C27650%20Dequindre%20Road%2C%20Suite%202000%2C%20Warren%2C%20Michigan%2C%2048092%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135&amp;waypoints=19000%20St%20Joe%27s%20Pkwy%20suite%20200%2C%20Livonia%2C%20Michigan%2C%2048152%7C37508%20W%20SEVEN%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%7C23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C17800%20Newburgh%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076&amp;waypoints=37508%20W%20SEVEN%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%7C17800%20Newburgh%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239</t>
         </is>
       </c>
     </row>
@@ -2947,13 +2947,13 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Shelby Township (3) • Washington (2)</t>
+          <t>Shelby Township (3) • Clinton Township (3)</t>
         </is>
       </c>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=36750%2026%20Mile%20Rd%2C%20ste%20140%2C%20New%20Baltimore%2C%20Michigan%2C%2048047&amp;waypoints=79720%20Kidder%20Rd%20Bruce%20Township%2C%20Michigan%2C%2048065%7C64541%20Van%20Dyke%2C%20Washington%2C%20Michigan%2C%2048095%7C57850%20Van%20Dyke%20Ave%20ste%20600%2C%20Washington%2C%20Michigan%2C%2048094%7C50720%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C15125%2022%20Mile%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C45640%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20Michigan%2C%2048315%7C41060%20Hayes%20Road%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C43555%20Dalcoma%20Dr%20suite%204%20Clinton%20Twp%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C36267%2026%20Mile%20Road%2C%20Suite%203%2C%20Lenox%2C%20MI%2C%2048048</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=36750%2026%20Mile%20Rd%2C%20ste%20140%2C%20New%20Baltimore%2C%20Michigan%2C%2048047&amp;waypoints=79720%20Kidder%20Rd%20Bruce%20Township%2C%20Michigan%2C%2048065%7C57850%20Van%20Dyke%20Ave%20ste%20600%2C%20Washington%2C%20Michigan%2C%2048094%7C50720%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C15125%2022%20Mile%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C45640%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20Michigan%2C%2048315%7C41060%20Hayes%20Road%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C43555%20Dalcoma%20Dr%20suite%204%20Clinton%20Twp%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C36267%2026%20Mile%20Road%2C%20Suite%203%2C%20Lenox%2C%20MI%2C%2048048</t>
         </is>
       </c>
     </row>
@@ -2990,13 +2990,13 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Southfield (3) • West Bloomfield (2)</t>
+          <t>Southfield (3) • Farmington Hills (2)</t>
         </is>
       </c>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302&amp;waypoints=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2940%20Crooks%20Rd%2C%20Rochester%20Hills%2C%20Michigan%2C%2048309&amp;waypoints=5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>0</v>
@@ -3029,17 +3029,17 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Livonia (4) • Dearborn Heights (2)</t>
+          <t>Livonia (3) • Farmington (2)</t>
         </is>
       </c>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239&amp;waypoints=23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C36600%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127%7C22318%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22318%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127&amp;waypoints=6543%20TELEGRAPH%20RD%2C%20BLOOMFIELD%20TOWNSHIP%2C%20Michigan%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C36600%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3072,17 +3072,17 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Commerce Township (5) • White Lake (1)</t>
+          <t>Commerce Township (5) • Novi (1)</t>
         </is>
       </c>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=26850%20PROVIDENCE%20PKWY%20STE%20455%2C%20NOVI%2C%20Michigan&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C2630%20UNION%20LAKE%20RD%20STE%20100%2C%20COMMERCE%20TOWNSHIP%2C%20Michigan%7C2685%20Union%20Lake%20Rd%20Commerce%20Charter%20Twp%2C%20Commerce%20Charter%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C100%20N%20POND%20DR%20STE%20C%2C%20WALLED%20LAKE%2C%20MI%2C%2048390</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2157%20ORCHARD%20LAKE%20RD%2C%20SYLVAN%20LAKE%2C%20Michigan&amp;waypoints=1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C26850%20PROVIDENCE%20PKWY%20STE%20455%2C%20NOVI%2C%20Michigan%7C100%20N%20POND%20DR%20STE%20C%2C%20WALLED%20LAKE%2C%20MI%2C%2048390%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2685%20Union%20Lake%20Rd%20Commerce%20Charter%20Twp%2C%20Commerce%20Charter%20Township%2C%20Michigan%2C%2048382%7C2630%20UNION%20LAKE%20RD%20STE%20100%2C%20COMMERCE%20TOWNSHIP%2C%20Michigan%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>0</v>
@@ -3115,17 +3115,17 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Warren (5) • Sterling Heights (3)</t>
+          <t>Warren (5) • Sterling Heights (2)</t>
         </is>
       </c>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22250%20PROVIDENCE%20DR%20STE%20500%2C%20SOUTHFIELD%2C%20Michigan&amp;waypoints=115%20E%20Long%20Lake%20Rd%2C%20Troy%2C%20MI%2048085%7C35200%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C34764%20Dequindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2048310%7C2107%20East%2014%20Mile%20Road%2C%20Sterling%20Heights%2C%20MI%2048310%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088%7C11885%20E%2012%20Mile%20Rd%20Ste%20200B%2C%20Warren%2C%20MI%2048093%7C28401%20Hoover%2C%20Warren%2C%20Michigan%2C%2048093%7C28111%20HOOVER%20RD%20STE%201A%2C%20WARREN%2C%20Michigan%7C28111%20Hoover%20Rd%2C%20Ste%205A%20Warren%2C%20Mi%2048093%2C%20Usa%2C%20Warren%2C%20MI%2048093</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22250%20PROVIDENCE%20DR%20STE%20500%2C%20SOUTHFIELD%2C%20Michigan&amp;waypoints=115%20E%20Long%20Lake%20Rd%2C%20Troy%2C%20MI%2048085%7C35200%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C34764%20Dequindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2048310%7C11885%20E%2012%20Mile%20Rd%20Ste%20200B%2C%20Warren%2C%20MI%2048093%7C28401%20Hoover%2C%20Warren%2C%20Michigan%2C%2048093%7C28111%20HOOVER%20RD%20STE%201A%2C%20WARREN%2C%20Michigan%7C28111%20Hoover%20Rd%2C%20Ste%205A%20Warren%2C%20Mi%2048093%2C%20Usa%2C%20Warren%2C%20MI%2048093%7C27427%20Schoenherr%20Rd%2C%20Warren%2C%20MI%2048088%7C20599%20Mack%20Ave%2C%20Grosse%20Pointe%20Woods%2C%20MI%2048236</t>
         </is>
       </c>
     </row>
@@ -3162,13 +3162,13 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Warren (3) • St Clair Shores (2)</t>
+          <t>Sterling Heights (2) • St Clair Shores (2)</t>
         </is>
       </c>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230&amp;waypoints=13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080%7C20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066%7C27472%20Schoenherr%20Rd%20%23100%2C%20Warren%2C%20MI%2C%2048088%7C27427%20Schoenherr%20Rd%2C%20Warren%2C%20MI%2048088%7C21647%20Ryan%20Rd%2C%20Warren%2C%20MI%2C%2048091%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230&amp;waypoints=13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080%7C20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066%7C27472%20Schoenherr%20Rd%20%23100%2C%20Warren%2C%20MI%2C%2048088%7C21647%20Ryan%20Rd%2C%20Warren%2C%20MI%2C%2048091%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236</t>
         </is>
       </c>
     </row>
@@ -3205,13 +3205,13 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Farmington Hills (5) • West Bloomfield (2)</t>
+          <t>Farmington Hills (4) • West Bloomfield (3)</t>
         </is>
       </c>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167&amp;waypoints=6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167&amp;waypoints=6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C29201%20Telegraph%20Rd%2C%20ste%20403%2C%20Southfield%2C%20MI%2C%2048034%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=28001%20Harper%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081&amp;waypoints=12169%20JOSEPH%20CAMPAU%20ST%2C%20HAMTRAMCK%2C%20MI%2C%2048212%7C12101%20Joseph%20Campau%20Avenue%2C%20Hamtramck%2C%20MI%2048212%7C9421%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C9021%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%20nan%7C9230%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C18700%20Mack%20Ave%2C%20Grosse%20Pointe%2C%20MI%20nan%7C20901%20Moross%20Rd%2C%20Grosse%20Pointe%2C%20MI%2048236%7C20225%20East%209%20Mile%20Road%2C%20St.%20Clair%20Shores%2C%20MI%2048080%7C18325%20E%2010%20Mile%20Rd%2C%20Ste%20100%2C%20Roseville%2C%20MI%20480664990</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=12101%20Joseph%20Campau%20Avenue%2C%20Hamtramck%2C%20MI%2048212&amp;waypoints=26328%20Van%20Dyke%20Ave%2C%20Center%20Line%2C%20MI%2048015%7C18245%20East%2010%20Mile%20Road%2C%20Ste%20120%2C%20Roseville%2C%20MI%2048066%7C28001%20Harper%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081%7C20901%20Moross%20Rd%2C%20Grosse%20Pointe%2C%20MI%2048236%7C18700%20Mack%20Ave%2C%20Grosse%20Pointe%2C%20MI%20nan%7C9230%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C9021%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%20nan%7C9421%20Joseph%20Campau%20St%2C%20Hamtramck%2C%20MI%2048212%7C12169%20JOSEPH%20CAMPAU%20ST%2C%20HAMTRAMCK%2C%20MI%2C%2048212</t>
         </is>
       </c>
     </row>
@@ -3291,13 +3291,13 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Sterling Heights (8) • Rochester Hills (1)</t>
+          <t>Sterling Heights (7) • Madison Heights (2)</t>
         </is>
       </c>
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=28324%20Dequindre%20Road%2C%20Warren%2C%20Michigan%2C%2048092&amp;waypoints=2940%20Crooks%20Rd%2C%20Rochester%20Hills%2C%20Michigan%2C%2048309%7C44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan%7C41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C13700%2019%20Mile%20Rd%2C%20Sterling%20Heights%2C%20MI%2048313%7C39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=26393%20Dequindre%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071&amp;waypoints=44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan%7C41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C28324%20Dequindre%20Road%2C%20Warren%2C%20Michigan%2C%2048092</t>
         </is>
       </c>
     </row>
@@ -3334,13 +3334,13 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Southfield (6) • Livonia (2)</t>
+          <t>Southfield (5) • Livonia (2)</t>
         </is>
       </c>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152&amp;waypoints=29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C29201%20Telegraph%20Rd%2C%20ste%20403%2C%20Southfield%2C%20MI%2C%2048034%7C29829%20Telegraph%20Road%2C%20Southfield%2C%20MI%2048034%7C29877%20Telegraph%20Rd%20Ste%20200%2C%20Southfield%2C%20MI%2048034%7C29628%20Southfield%20Road%2C%20Southfield%2C%20Michigan%2C%2048076%7C17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075%7C23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075&amp;waypoints=23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C28670%20Telegraph%20Road%2C%20Southfield%2C%20Michigan%2C%2048034%7C29829%20Telegraph%20Road%2C%20Southfield%2C%20MI%2048034%7C29877%20Telegraph%20Rd%20Ste%20200%2C%20Southfield%2C%20MI%2048034%7C17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076</t>
         </is>
       </c>
     </row>
@@ -3377,13 +3377,13 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Farmington Hills (3) • Livonia (3)</t>
+          <t>Livonia (3) • Farmington Hills (2)</t>
         </is>
       </c>
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135&amp;waypoints=30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan</t>
         </is>
       </c>
     </row>
@@ -3450,10 +3450,10 @@
         <v>10</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0</v>
@@ -3463,13 +3463,13 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Livonia (4) • Plymouth (2)</t>
+          <t>Livonia (4) • Plymouth (3)</t>
         </is>
       </c>
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150&amp;waypoints=19000%20St%20Joe%27S%20Pkwy%20%23330%2C%20Livonia%2C%20MI%2048152%7C9368%20North%20Lilley%20Road%2C%20Plymouth%2C%20MI%2048170%7C41424%20Ann%20Arbor%20Rd%2C%20Plymouth%2C%20Michigan%2C%2048170%7C35330%20Nankin%20Blvd%20Ste%20701%2C%20Westland%2C%20MI%2048185%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C32950%205%20Mile%20Rd%2C%20Livonia%2C%20MI%2048154%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=9368%20North%20Lilley%20Road%2C%20Plymouth%2C%20MI%2048170&amp;waypoints=19000%20St%20Joe%27S%20Pkwy%20%23330%2C%20Livonia%2C%20MI%2048152%7C32950%205%20Mile%20Rd%2C%20Livonia%2C%20MI%2048154%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C35330%20Nankin%20Blvd%20Ste%20701%2C%20Westland%2C%20MI%2048185%7C9857%20N%20HAGGERTY%20RD%2C%20PLYMOUTH%2C%20Michigan%2C%20MI%2048170%7C41424%20Ann%20Arbor%20Rd%2C%20Plymouth%2C%20Michigan%2C%2048170</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038&amp;waypoints=4600%2014%20Mile%20Rd%20ste%201%2C%20Warren%2C%20Michigan%2C%2048092%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093%7C29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038&amp;waypoints=38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C4600%2014%20Mile%20Rd%20ste%201%2C%20Warren%2C%20Michigan%2C%2048092%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093%7C29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>0</v>
@@ -3631,17 +3631,17 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Troy (3) • Warren (3)</t>
+          <t>Sterling Heights (4) • Troy (2)</t>
         </is>
       </c>
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13425%2019%20Mile%20Rd%20Ste%20100%2C%20Sterling%20Heights%2C%20MI%2048313&amp;waypoints=3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083%7C3940%20John%20R%20Road%2C%20Troy%2C%20MI%2048083%7C2891%20E%20Maple%20Rd%20Ste%20102%2C%20Troy%2C%20MI%2C%2048083%7C27650%20Dequindre%20Road%2C%20Suite%202000%2C%20Warren%2C%20Michigan%2C%2048092%7C29245%20Ryan%20Rd%20suite%20300%2C%20Warren%2C%20Michigan%2C%2048092%7C8600%20Chicago%20Road%20St%2C%20Warren%2C%20MI%2C%2048093%7C38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C42755%20Mound%20Rd%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C44225%20Utica%20Road%2C%20Utica%2C%20Michigan%2C%2048317</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27650%20Dequindre%20Road%2C%20Suite%202000%2C%20Warren%2C%20Michigan%2C%2048092&amp;waypoints=64541%20Van%20Dyke%2C%20Washington%2C%20Michigan%2C%2048095%7C13700%2019%20Mile%20Rd%2C%20Sterling%20Heights%2C%20MI%2048313%7C13425%2019%20Mile%20Rd%20Ste%20100%2C%20Sterling%20Heights%2C%20MI%2048313%7C44225%20Utica%20Road%2C%20Utica%2C%20Michigan%2C%2048317%7C42755%20Mound%20Rd%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C3940%20John%20R%20Road%2C%20Troy%2C%20MI%2048083%7C2891%20E%20Maple%20Rd%20Ste%20102%2C%20Troy%2C%20MI%2C%2048083%7C2107%20East%2014%20Mile%20Road%2C%20Sterling%20Heights%2C%20MI%2048310%7C29245%20Ryan%20Rd%20suite%20300%2C%20Warren%2C%20Michigan%2C%2048092</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>0</v>
@@ -3674,17 +3674,17 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>West Bloomfield (2) • Madison Heights (2)</t>
+          <t>Southfield (2) • White Lake Charter Township (1)</t>
         </is>
       </c>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=8275%20N%20WAYNE%20RD%2C%20WESTLAND%2C%20Michigan%2C%2048185&amp;waypoints=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302&amp;waypoints=8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083</t>
         </is>
       </c>
     </row>
@@ -27485,45 +27485,45 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>📝 HEALING HANDS URGENT CARE</t>
+          <t>📝 Center For Hollistic Medicine</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 30</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>ed1959ed-68b4-4788-bfa4-24c1e6d994d6</t>
+          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J390" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>Sylvan Lake</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr">
         <is>
-          <t>2157 ORCHARD LAKE RD, SYLVAN LAKE, Michigan</t>
+          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
         </is>
       </c>
       <c r="M390" s="3" t="n"/>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>📝 ORCHARD PRIMARY CARE</t>
+          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
+          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -27694,7 +27694,7 @@
         </is>
       </c>
       <c r="J393" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
+          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
         </is>
       </c>
       <c r="M393" s="3" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>📝 Powers Family Medicine</t>
+          <t>📝 ORCHARD PRIMARY CARE</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>00-761-7874</t>
+          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -27754,7 +27754,7 @@
         </is>
       </c>
       <c r="J394" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="L394" s="3" t="inlineStr">
         <is>
-          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
+          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
         </is>
       </c>
       <c r="M394" s="3" t="n"/>
@@ -27785,7 +27785,7 @@
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>📝 Legacy Family Care</t>
+          <t>📝 Powers Family Medicine</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
+          <t>00-761-7874</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -27814,7 +27814,7 @@
         </is>
       </c>
       <c r="J395" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
       </c>
       <c r="L395" s="3" t="inlineStr">
         <is>
-          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
+          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
         </is>
       </c>
       <c r="M395" s="3" t="n"/>
@@ -27845,7 +27845,7 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>📝 Village Medical Farmington</t>
+          <t>📝 Legacy Family Care</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
+          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -27874,16 +27874,16 @@
         </is>
       </c>
       <c r="J396" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr">
         <is>
-          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
+          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
         </is>
       </c>
       <c r="M396" s="3" t="n"/>
@@ -27905,7 +27905,7 @@
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>📝 SHEIKH MEDICAL CENTER</t>
+          <t>📝 Village Medical Farmington</t>
         </is>
       </c>
       <c r="E397" s="3" t="inlineStr">
@@ -27920,7 +27920,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>7c32d0b4-c83f-4756-924c-9c8c74996a39</t>
+          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -27934,7 +27934,7 @@
         </is>
       </c>
       <c r="J397" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
       </c>
       <c r="L397" s="3" t="inlineStr">
         <is>
-          <t>22821 ORCHARD LAKE RD, FARMINGTON, MI, 48336</t>
+          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M397" s="3" t="n"/>
@@ -27965,12 +27965,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Middlebelt Medical Center</t>
+          <t>📝 SHEIKH MEDICAL CENTER</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jun 29</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -27980,17 +27980,17 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>1235147133</t>
+          <t>7c32d0b4-c83f-4756-924c-9c8c74996a39</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J398" s="2" t="n">
@@ -27998,12 +27998,12 @@
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr">
         <is>
-          <t>17940 Farmington Rd Ste 130, Livonia, MI 48152</t>
+          <t>22821 ORCHARD LAKE RD, FARMINGTON, MI, 48336</t>
         </is>
       </c>
       <c r="M398" s="3" t="n"/>
@@ -28025,12 +28025,12 @@
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>NORTHWAY MEDICAL CENTER</t>
+          <t>Middlebelt Medical Center</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 29</t>
+          <t>Tier 1 producer · last check-in Jun 29</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>dafed37b-6f1e-43be-91b6-aba048a40332</t>
+          <t>1235147133</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -28058,12 +28058,12 @@
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L399" s="3" t="inlineStr">
         <is>
-          <t>17330 Northland Park Ct Ste 100, Southfield, MI 48075</t>
+          <t>17940 Farmington Rd Ste 130, Livonia, MI 48152</t>
         </is>
       </c>
       <c r="M399" s="3" t="n"/>
@@ -28085,45 +28085,45 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell URGENT CARE BY WELLSTREET</t>
+          <t>NORTHWAY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 29</t>
+          <t>Tier 1 producer · last check-in May 29</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>5f3e3632-715d-4e1c-b4ca-4c6bc3dac21e</t>
+          <t>dafed37b-6f1e-43be-91b6-aba048a40332</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J400" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
-          <t>Bloomfield Township</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr">
         <is>
-          <t>6543 TELEGRAPH RD, BLOOMFIELD TOWNSHIP, Michigan</t>
+          <t>17330 Northland Park Ct Ste 100, Southfield, MI 48075</t>
         </is>
       </c>
       <c r="M400" s="3" t="n"/>
@@ -28145,45 +28145,45 @@
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>Chander Kanta MD</t>
+          <t>📝 Get Well Urgent Care Madison Heights</t>
         </is>
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 20</t>
+          <t>Tier 1 producer · last check-in Aug 25</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>1558467373</t>
+          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J401" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K401" s="2" t="inlineStr">
         <is>
-          <t>Center Line</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L401" s="3" t="inlineStr">
         <is>
-          <t>26328 Van Dyke Ave, Center Line, MI 48015</t>
+          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M401" s="3" t="n"/>
@@ -28205,12 +28205,12 @@
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>📝 Lupo Chiropractic Center</t>
+          <t>📝 Lifetime Family Care</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 17</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -28220,12 +28220,12 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>ea3dd183-15b5-491c-b6b5-55d6404f4a22</t>
+          <t>b70053c3-f0fd-41de-9386-95fcc448a738</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr">
@@ -28234,16 +28234,16 @@
         </is>
       </c>
       <c r="J402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr">
         <is>
-          <t>27850 Gratiot Avenue, Roseville, Michigan, 48066</t>
+          <t>26393 Dequindre Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M402" s="3" t="n"/>
@@ -28265,45 +28265,45 @@
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>Office of Clara Kamath Wood MD</t>
+          <t>📝 FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
         </is>
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Apr 20</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>ccad7a72-2fa8-4c91-af14-5995cd5adacf</t>
+          <t>f4a7f5a0-d8e0-49ff-874a-04f12057fc5f</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J403" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L403" s="3" t="inlineStr">
         <is>
-          <t>18245 East 10 Mile Road, Ste 120, Roseville, MI 48066</t>
+          <t>12169 JOSEPH CAMPAU ST, HAMTRAMCK, MI, 48212</t>
         </is>
       </c>
       <c r="M403" s="3" t="n"/>
@@ -28325,27 +28325,27 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Emcura Immediate Care - Grosse Pointe</t>
+          <t>TRUST FAMILY CARE CENTER, PLLC</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 3</t>
+          <t>Tier 1 producer · last check-in May 19</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>bf549ea4-0d9c-4877-927c-ed3f99bf0988</t>
+          <t>10524116-5eb6-4e8c-b740-351bf86df478</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr">
@@ -28354,16 +28354,16 @@
         </is>
       </c>
       <c r="J404" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe Woods</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr">
         <is>
-          <t>20599 Mack Ave, Grosse Pointe Woods, MI 48236</t>
+          <t>9421 Joseph Campau St, Hamtramck, MI 48212</t>
         </is>
       </c>
       <c r="M404" s="3" t="n"/>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Main Internal Medicine - Grosse Pointe</t>
+          <t>WAYNE COMMUNITY HEALTH CENTERS, INC</t>
         </is>
       </c>
       <c r="E405" s="3" t="inlineStr">
@@ -28400,17 +28400,17 @@
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>1073593174</t>
+          <t>b89491cd-a8b2-4493-8dba-2e2146e504a0</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J405" s="2" t="n">
@@ -28418,12 +28418,12 @@
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L405" s="3" t="inlineStr">
         <is>
-          <t>19251 Mack Ave #333, Grosse Pointe, Michigan, 48236</t>
+          <t>9021 Joseph Campau St, Hamtramck, MI nan</t>
         </is>
       </c>
       <c r="M405" s="3" t="n"/>
@@ -28445,12 +28445,12 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>📝 Jefferson Family Practice (Cornerstone)</t>
+          <t>METROPOLITAN MEDICAL CENTER, PLLC</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 1 producer · last check-in May 19</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -28460,17 +28460,17 @@
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>9b2159ca-9617-4ade-8a25-85a92fcca972</t>
+          <t>44ca23fe-7723-4691-8484-5995f7be8e7e</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J406" s="2" t="n">
@@ -28478,12 +28478,12 @@
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr">
         <is>
-          <t>15050 E Jefferson Ave suite 101, Grosse Pointe, Michigan, 48230</t>
+          <t>9230 Joseph Campau St, Hamtramck, MI 48212</t>
         </is>
       </c>
       <c r="M406" s="3" t="n"/>
@@ -28505,12 +28505,12 @@
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>METROPOLITAN MEDICAL CENTER, PLLC</t>
+          <t>📝 Jefferson Family Practice (Cornerstone)</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 19</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -28520,17 +28520,17 @@
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>44ca23fe-7723-4691-8484-5995f7be8e7e</t>
+          <t>9b2159ca-9617-4ade-8a25-85a92fcca972</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J407" s="2" t="n">
@@ -28538,12 +28538,12 @@
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Grosse Pointe</t>
         </is>
       </c>
       <c r="L407" s="3" t="inlineStr">
         <is>
-          <t>9230 Joseph Campau St, Hamtramck, MI 48212</t>
+          <t>15050 E Jefferson Ave suite 101, Grosse Pointe, Michigan, 48230</t>
         </is>
       </c>
       <c r="M407" s="3" t="n"/>
@@ -28565,7 +28565,7 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>WAYNE COMMUNITY HEALTH CENTERS, INC</t>
+          <t>📝 Henry Ford Main Internal Medicine - Grosse Pointe</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
@@ -28580,17 +28580,17 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>b89491cd-a8b2-4493-8dba-2e2146e504a0</t>
+          <t>1073593174</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J408" s="2" t="n">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Grosse Pointe</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr">
         <is>
-          <t>9021 Joseph Campau St, Hamtramck, MI nan</t>
+          <t>19251 Mack Ave #333, Grosse Pointe, Michigan, 48236</t>
         </is>
       </c>
       <c r="M408" s="3" t="n"/>
@@ -28625,12 +28625,12 @@
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>TRUST FAMILY CARE CENTER, PLLC</t>
+          <t>📝 Lupo Chiropractic Center</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 19</t>
+          <t>Tier 1 producer · last check-in Sep 17</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -28640,30 +28640,30 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>10524116-5eb6-4e8c-b740-351bf86df478</t>
+          <t>ea3dd183-15b5-491c-b6b5-55d6404f4a22</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J409" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K409" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L409" s="3" t="inlineStr">
         <is>
-          <t>9421 Joseph Campau St, Hamtramck, MI 48212</t>
+          <t>27850 Gratiot Avenue, Roseville, Michigan, 48066</t>
         </is>
       </c>
       <c r="M409" s="3" t="n"/>
@@ -28685,12 +28685,12 @@
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>📝 FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
+          <t>📝 Macomb Internal Medicine</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 1 producer · last check-in Jul 10</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -28700,7 +28700,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>f4a7f5a0-d8e0-49ff-874a-04f12057fc5f</t>
+          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -28714,16 +28714,16 @@
         </is>
       </c>
       <c r="J410" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr">
         <is>
-          <t>12169 JOSEPH CAMPAU ST, HAMTRAMCK, MI, 48212</t>
+          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
         </is>
       </c>
       <c r="M410" s="3" t="n"/>
@@ -28745,22 +28745,22 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>One Health</t>
+          <t>Trinity IHA Primary &amp; Urgent Care - South Lyon</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Mar 4</t>
+          <t>Tier 1 producer · last check-in Mar 4</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>0daacd4e-c7e1-4704-b9d1-efe7f6b22924</t>
+          <t>efc01329-3254-49cb-8fd4-1a6de92fe5ba</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -28774,7 +28774,7 @@
         </is>
       </c>
       <c r="J411" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
       </c>
       <c r="L411" s="3" t="inlineStr">
         <is>
-          <t>12660 10 Mile Rd, South Lyon, MI 48178</t>
+          <t>23200 Pontiac Trail, South Lyon, MI 48178</t>
         </is>
       </c>
       <c r="M411" s="3" t="n"/>
@@ -28805,22 +28805,22 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>📝 South Lyon Family Docs</t>
+          <t>📝 Village Medical - Northville West</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 2</t>
+          <t>Tier 1 producer · last check-in Sep 2</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>573750f7-b7bd-4246-b7ac-f1217823639f</t>
+          <t>1255345930</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -28834,16 +28834,16 @@
         </is>
       </c>
       <c r="J412" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>South Lyon</t>
+          <t>Northville</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr">
         <is>
-          <t>26006 Pontiac Trail, South Lyon, MI, 48178</t>
+          <t>422 N Center St, Northville, Michigan, 48167</t>
         </is>
       </c>
       <c r="M412" s="3" t="n"/>
@@ -28865,12 +28865,12 @@
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>Trinity IHA Primary &amp; Urgent Care - South Lyon</t>
+          <t>📝 Medical Clinic of Northville</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Mar 4</t>
+          <t>Tier 1 producer · last check-in Sep 2</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
@@ -28880,30 +28880,30 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>efc01329-3254-49cb-8fd4-1a6de92fe5ba</t>
+          <t>ebcb6f7a-eb6b-4759-81d9-516e3dc36b67</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J413" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
         <is>
-          <t>South Lyon</t>
+          <t>Northville</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
         <is>
-          <t>23200 Pontiac Trail, South Lyon, MI 48178</t>
+          <t>308 S Main St, Northville, Michigan, 48167</t>
         </is>
       </c>
       <c r="M413" s="3" t="n"/>
@@ -28925,12 +28925,12 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>📝 Hesselberg Chiropractic</t>
+          <t>📝 TONI BALLITCH TRATE, DO, PC</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
+          <t>Tier 1 producer · last check-in Aug 13</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -28940,12 +28940,12 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>83b9dec3-57ee-4777-b000-fcb1c228e6c7</t>
+          <t>a1394f28-7761-4612-ab27-23681dcadac0</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I414" s="2" t="inlineStr">
@@ -28954,16 +28954,16 @@
         </is>
       </c>
       <c r="J414" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
-          <t>Ypsilanti</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr">
         <is>
-          <t>2900 Packard Street, Ypsilanti, Michigan, 48197</t>
+          <t>38215 W 10 MILE RD STE 8, FARMINGTON HILLS, Michigan</t>
         </is>
       </c>
       <c r="M414" s="3" t="n"/>
@@ -28985,12 +28985,12 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>📝 Pryde Athletics and Physical Therapy</t>
+          <t>📝 Trinity IHA Primary Care - Schoolcraft Campus</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 23</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
@@ -29000,12 +29000,12 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>70091951-e0bd-42eb-9eb7-c5be5ce88649</t>
+          <t>4b1cacba-85fb-4f63-8660-c3314cf72677</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr">
@@ -29018,12 +29018,12 @@
       </c>
       <c r="K415" s="2" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L415" s="3" t="inlineStr">
         <is>
-          <t>5624 Research Drive, Canton, Michigan, 48188</t>
+          <t>19000 St Joe's Pkwy suite 200, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M415" s="3" t="n"/>
@@ -29105,12 +29105,12 @@
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>📝 Medical Clinic of Northville</t>
+          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 2</t>
+          <t>Tier 1 producer · last check-in Sep 1</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>ebcb6f7a-eb6b-4759-81d9-516e3dc36b67</t>
+          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -29134,16 +29134,16 @@
         </is>
       </c>
       <c r="J417" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
-          <t>Northville</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
         <is>
-          <t>308 S Main St, Northville, Michigan, 48167</t>
+          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M417" s="3" t="n"/>
@@ -29165,12 +29165,12 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>📝 Village Medical - Northville West</t>
+          <t>📝 Greg Monroe DO PC</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 2</t>
+          <t>Tier 1 producer · last check-in Sep 1</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>1255345930</t>
+          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -29198,12 +29198,12 @@
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
-          <t>Northville</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr">
         <is>
-          <t>422 N Center St, Northville, Michigan, 48167</t>
+          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
         </is>
       </c>
       <c r="M418" s="3" t="n"/>
@@ -29225,12 +29225,12 @@
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>📝 TONI BALLITCH TRATE, DO, PC</t>
+          <t>📝 Pryde Athletics and Physical Therapy</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 13</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
@@ -29240,12 +29240,12 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>a1394f28-7761-4612-ab27-23681dcadac0</t>
+          <t>70091951-e0bd-42eb-9eb7-c5be5ce88649</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I419" s="2" t="inlineStr">
@@ -29258,12 +29258,12 @@
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="L419" s="3" t="inlineStr">
         <is>
-          <t>38215 W 10 MILE RD STE 8, FARMINGTON HILLS, Michigan</t>
+          <t>5624 Research Drive, Canton, Michigan, 48188</t>
         </is>
       </c>
       <c r="M419" s="3" t="n"/>
@@ -29285,27 +29285,27 @@
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Go Health Urgent Care</t>
+          <t>📝 Hesselberg Chiropractic</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in May 27</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>14f29ff1-cd7e-4e90-b5c7-b1114551c5b9</t>
+          <t>83b9dec3-57ee-4777-b000-fcb1c228e6c7</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I420" s="2" t="inlineStr">
@@ -29314,16 +29314,16 @@
         </is>
       </c>
       <c r="J420" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Ypsilanti</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr">
         <is>
-          <t>28670 Telegraph Road, Southfield, Michigan, 48034</t>
+          <t>2900 Packard Street, Ypsilanti, Michigan, 48197</t>
         </is>
       </c>
       <c r="M420" s="3" t="n"/>
@@ -29705,7 +29705,7 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>📝 Sterling Physicians</t>
+          <t>📝 Associates in Family Practice</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
@@ -29720,7 +29720,7 @@
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>1972593499</t>
+          <t>1205856432</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
@@ -29743,7 +29743,7 @@
       </c>
       <c r="L427" s="3" t="inlineStr">
         <is>
-          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+          <t>42755 Mound Rd, Sterling Heights, Michigan, 48314</t>
         </is>
       </c>
       <c r="M427" s="3" t="n"/>
@@ -29765,7 +29765,7 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Office of Lillman Dwarka MD</t>
+          <t>Concentra Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>144c374c-b718-48c1-9b9f-daffbf7ba530</t>
+          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I428" s="2" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="L428" s="3" t="inlineStr">
         <is>
-          <t>38300 Van Dyke Ave, Ste 105, Sterling Heights, MI 48312</t>
+          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M428" s="3" t="n"/>
@@ -29825,12 +29825,12 @@
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>Concentra Urgent Care - Sterling Heights</t>
+          <t>Lakewood Primary Care</t>
         </is>
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
@@ -29840,12 +29840,12 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
+          <t>39254718-ba1d-4862-adfb-cd292a8eda27</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I429" s="2" t="inlineStr">
@@ -29854,7 +29854,7 @@
         </is>
       </c>
       <c r="J429" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K429" s="2" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="L429" s="3" t="inlineStr">
         <is>
-          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
+          <t>13425 19 Mile Rd Ste 100, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M429" s="3" t="n"/>
@@ -29885,12 +29885,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>📝 Associates in Family Practice</t>
+          <t>Professional Village Medical Center</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
@@ -29900,21 +29900,21 @@
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>1205856432</t>
+          <t>1427031756</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J430" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="L430" s="3" t="inlineStr">
         <is>
-          <t>42755 Mound Rd, Sterling Heights, Michigan, 48314</t>
+          <t>13700 19 Mile Rd, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M430" s="3" t="n"/>
@@ -29945,12 +29945,12 @@
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>Lakewood Primary Care</t>
+          <t>Clinton Preferred Pediatrics</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
@@ -29960,12 +29960,12 @@
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>39254718-ba1d-4862-adfb-cd292a8eda27</t>
+          <t>abd1a370-f826-48dd-a800-9a15983f52e8</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I431" s="2" t="inlineStr">
@@ -29974,16 +29974,16 @@
         </is>
       </c>
       <c r="J431" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L431" s="3" t="inlineStr">
         <is>
-          <t>13425 19 Mile Rd Ste 100, Sterling Heights, MI 48313</t>
+          <t>15500 19 Mile Rd Suite 300, Clinton Township, MI 48038</t>
         </is>
       </c>
       <c r="M431" s="3" t="n"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Professional Village Medical Center</t>
+          <t>📝 Swetech Medical Center</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
@@ -30020,30 +30020,30 @@
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>1427031756</t>
+          <t>1255427209</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J432" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K432" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr">
         <is>
-          <t>13700 19 Mile Rd, Sterling Heights, MI 48313</t>
+          <t>43600 Garfield Rd, Clinton Township, Michigan, 48038</t>
         </is>
       </c>
       <c r="M432" s="3" t="n"/>
@@ -30065,7 +30065,7 @@
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>Clinton Preferred Pediatrics</t>
+          <t>Macomb Pediatrics - Clinton Township</t>
         </is>
       </c>
       <c r="E433" s="3" t="inlineStr">
@@ -30080,7 +30080,7 @@
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>abd1a370-f826-48dd-a800-9a15983f52e8</t>
+          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="L433" s="3" t="inlineStr">
         <is>
-          <t>15500 19 Mile Rd Suite 300, Clinton Township, MI 48038</t>
+          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
         </is>
       </c>
       <c r="M433" s="3" t="n"/>
@@ -30125,12 +30125,12 @@
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>📝 Swetech Medical Center</t>
+          <t>📝 Northpointe Pediatrics</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
@@ -30140,12 +30140,12 @@
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>1255427209</t>
+          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I434" s="2" t="inlineStr">
@@ -30158,12 +30158,12 @@
       </c>
       <c r="K434" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr">
         <is>
-          <t>43600 Garfield Rd, Clinton Township, Michigan, 48038</t>
+          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
         </is>
       </c>
       <c r="M434" s="3" t="n"/>
@@ -30185,12 +30185,12 @@
       </c>
       <c r="D435" s="3" t="inlineStr">
         <is>
-          <t>Macomb Pediatrics - Clinton Township</t>
+          <t>📝 Sterling Physicians</t>
         </is>
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
@@ -30200,17 +30200,17 @@
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
+          <t>1972593499</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J435" s="2" t="n">
@@ -30218,12 +30218,12 @@
       </c>
       <c r="K435" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L435" s="3" t="inlineStr">
         <is>
-          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
+          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M435" s="3" t="n"/>
@@ -30545,12 +30545,12 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>📝 Legacy Family Medicine</t>
+          <t>Mercy Family Care Center</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
@@ -30560,17 +30560,17 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>1558340356</t>
+          <t>3dfcef6a-be30-4421-b9ae-e70c90558ff6</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J441" s="2" t="n">
@@ -30583,7 +30583,7 @@
       </c>
       <c r="L441" s="3" t="inlineStr">
         <is>
-          <t>35429 Schoenherr Rd, Sterling Heights, MI, 48312</t>
+          <t>2107 East 14 Mile Road, Sterling Heights, MI 48310</t>
         </is>
       </c>
       <c r="M441" s="3" t="n"/>
@@ -30605,12 +30605,12 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>📝 Schoenherr Parkway Family Practice</t>
+          <t>Office of Lillman Dwarka MD</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
@@ -30620,17 +30620,17 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>62e680e9-a222-400d-9186-a369d13cf23f</t>
+          <t>144c374c-b718-48c1-9b9f-daffbf7ba530</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J442" s="2" t="n">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="L442" s="3" t="inlineStr">
         <is>
-          <t>13951 Plumbrook, Sterling Heights, Michigan, 48312</t>
+          <t>38300 Van Dyke Ave, Ste 105, Sterling Heights, MI 48312</t>
         </is>
       </c>
       <c r="M442" s="3" t="n"/>
@@ -30665,12 +30665,12 @@
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>📝 Macomb Internal Medicine</t>
+          <t>📝 Legacy Family Medicine</t>
         </is>
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 10</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
+          <t>1558340356</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -30694,16 +30694,16 @@
         </is>
       </c>
       <c r="J443" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L443" s="3" t="inlineStr">
         <is>
-          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
+          <t>35429 Schoenherr Rd, Sterling Heights, MI, 48312</t>
         </is>
       </c>
       <c r="M443" s="3" t="n"/>
@@ -30845,12 +30845,12 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>📝 MNP</t>
+          <t>📝 Team Rehabilitation  - Washington</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
@@ -30860,12 +30860,12 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>40477f1c-8f50-4f86-8e7e-a5431b7f2fe6</t>
+          <t>940f0098-7ee4-47be-9425-5cd4bbc4dd0f</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I446" s="2" t="inlineStr">
@@ -30874,16 +30874,16 @@
         </is>
       </c>
       <c r="J446" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
-          <t>Utica</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr">
         <is>
-          <t>44225 Utica Road, Utica, Michigan, 48317</t>
+          <t>64541 Van Dyke, Washington, Michigan, 48095</t>
         </is>
       </c>
       <c r="M446" s="3" t="n"/>
@@ -30905,12 +30905,12 @@
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care - Sterling Heights</t>
+          <t>📝 MNP</t>
         </is>
       </c>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 3</t>
+          <t>Tier 1 producer · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
@@ -30920,12 +30920,12 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
+          <t>40477f1c-8f50-4f86-8e7e-a5431b7f2fe6</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr">
@@ -30934,16 +30934,16 @@
         </is>
       </c>
       <c r="J447" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Utica</t>
         </is>
       </c>
       <c r="L447" s="3" t="inlineStr">
         <is>
-          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
+          <t>44225 Utica Road, Utica, Michigan, 48317</t>
         </is>
       </c>
       <c r="M447" s="3" t="n"/>
@@ -30965,12 +30965,12 @@
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>📝 Tri-County Medical Clinic</t>
+          <t>📝 Schoenherr Parkway Family Practice</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 3</t>
+          <t>Tier 1 producer · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>1386634749</t>
+          <t>62e680e9-a222-400d-9186-a369d13cf23f</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="L448" s="3" t="inlineStr">
         <is>
-          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
+          <t>13951 Plumbrook, Sterling Heights, Michigan, 48312</t>
         </is>
       </c>
       <c r="M448" s="3" t="n"/>
@@ -31025,7 +31025,7 @@
       </c>
       <c r="D449" s="3" t="inlineStr">
         <is>
-          <t>📝 MedPro Primary Care</t>
+          <t>📝 Henry Ford Warren Family Physicians</t>
         </is>
       </c>
       <c r="E449" s="3" t="inlineStr">
@@ -31040,12 +31040,12 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
+          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
@@ -31054,16 +31054,16 @@
         </is>
       </c>
       <c r="J449" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K449" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L449" s="3" t="inlineStr">
         <is>
-          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
+          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
         </is>
       </c>
       <c r="M449" s="3" t="n"/>
@@ -31085,12 +31085,12 @@
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care Madison Heights</t>
+          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 25</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -31100,12 +31100,12 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
+          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I450" s="2" t="inlineStr">
@@ -31114,16 +31114,16 @@
         </is>
       </c>
       <c r="J450" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K450" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr">
         <is>
-          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
+          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
         </is>
       </c>
       <c r="M450" s="3" t="n"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="D451" s="3" t="inlineStr">
         <is>
-          <t>📝 Lifetime Family Care</t>
+          <t>📝 Corewell Health-East</t>
         </is>
       </c>
       <c r="E451" s="3" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>b70053c3-f0fd-41de-9386-95fcc448a738</t>
+          <t>04ad9387-b1fe-45cd-bd14-73188de8e04a</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -31174,16 +31174,16 @@
         </is>
       </c>
       <c r="J451" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K451" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L451" s="3" t="inlineStr">
         <is>
-          <t>26393 Dequindre Rd, Madison Heights, Michigan, 48071</t>
+          <t>29245 Ryan Rd suite 300, Warren, Michigan, 48092</t>
         </is>
       </c>
       <c r="M451" s="3" t="n"/>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="D453" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Health-East</t>
+          <t>📝 MedPro Primary Care</t>
         </is>
       </c>
       <c r="E453" s="3" t="inlineStr">
@@ -31280,12 +31280,12 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>04ad9387-b1fe-45cd-bd14-73188de8e04a</t>
+          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I453" s="2" t="inlineStr">
@@ -31294,16 +31294,16 @@
         </is>
       </c>
       <c r="J453" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L453" s="3" t="inlineStr">
         <is>
-          <t>29245 Ryan Rd suite 300, Warren, Michigan, 48092</t>
+          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M453" s="3" t="n"/>
@@ -31325,12 +31325,12 @@
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Warren Family Physicians</t>
+          <t>📝 Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Sep 3</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -31340,12 +31340,12 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
+          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I454" s="2" t="inlineStr">
@@ -31358,12 +31358,12 @@
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr">
         <is>
-          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
+          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M454" s="3" t="n"/>
@@ -31385,12 +31385,12 @@
       </c>
       <c r="D455" s="3" t="inlineStr">
         <is>
-          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
+          <t>📝 Tri-County Medical Clinic</t>
         </is>
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 27</t>
+          <t>Tier 1 producer · last check-in Sep 3</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
+          <t>1386634749</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -31418,12 +31418,12 @@
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L455" s="3" t="inlineStr">
         <is>
-          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
+          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
         </is>
       </c>
       <c r="M455" s="3" t="n"/>
@@ -31445,12 +31445,12 @@
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>📝 Trinity IHA Primary Care - Schoolcraft Campus</t>
+          <t>📝 Henry Ford Health Medical Center - Seven Mile Road</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>4b1cacba-85fb-4f63-8660-c3314cf72677</t>
+          <t>44019f00-063b-4cdc-83d9-96ee51f8c6e3</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="L456" s="3" t="inlineStr">
         <is>
-          <t>19000 St Joe's Pkwy suite 200, Livonia, Michigan, 48152</t>
+          <t>37508 W SEVEN MILE RD, LIVONIA, Michigan</t>
         </is>
       </c>
       <c r="M456" s="3" t="n"/>
@@ -31505,7 +31505,7 @@
       </c>
       <c r="D457" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Health Medical Center - Seven Mile Road</t>
+          <t>📝 Village Medical - Livonia</t>
         </is>
       </c>
       <c r="E457" s="3" t="inlineStr">
@@ -31520,7 +31520,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>44019f00-063b-4cdc-83d9-96ee51f8c6e3</t>
+          <t>e3d707da-675d-4d7c-9356-2f53ec4d8a2e</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -31534,7 +31534,7 @@
         </is>
       </c>
       <c r="J457" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
       </c>
       <c r="L457" s="3" t="inlineStr">
         <is>
-          <t>37508 W SEVEN MILE RD, LIVONIA, Michigan</t>
+          <t>17800 Newburgh Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M457" s="3" t="n"/>
@@ -31565,12 +31565,12 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>📝 Ivy Rehab - Farmington</t>
+          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -31580,12 +31580,12 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
+          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
@@ -31594,16 +31594,16 @@
         </is>
       </c>
       <c r="J458" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr">
         <is>
-          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
+          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M458" s="3" t="n"/>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="D459" s="3" t="inlineStr">
         <is>
-          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
+          <t>📝 Ivy Rehab - Farmington</t>
         </is>
       </c>
       <c r="E459" s="3" t="inlineStr">
@@ -31640,12 +31640,12 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
+          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
@@ -31658,12 +31658,12 @@
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L459" s="3" t="inlineStr">
         <is>
-          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
+          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M459" s="3" t="n"/>
@@ -31685,12 +31685,12 @@
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>📝 Triumph chiropractic</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -31700,12 +31700,12 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
+          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I460" s="2" t="inlineStr">
@@ -31714,7 +31714,7 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
       </c>
       <c r="L460" s="3" t="inlineStr">
         <is>
-          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
+          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M460" s="3" t="n"/>
@@ -31745,12 +31745,12 @@
       </c>
       <c r="D461" s="3" t="inlineStr">
         <is>
-          <t>📝 Triumph chiropractic</t>
+          <t>📝 Brentwood Pediatric Associates</t>
         </is>
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -31760,12 +31760,12 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
+          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I461" s="2" t="inlineStr">
@@ -31774,7 +31774,7 @@
         </is>
       </c>
       <c r="J461" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K461" s="2" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
       </c>
       <c r="L461" s="3" t="inlineStr">
         <is>
-          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
+          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M461" s="3" t="n"/>
@@ -31805,12 +31805,12 @@
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>📝 Brentwood Pediatric Associates</t>
+          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -31820,12 +31820,12 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
+          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr">
@@ -31843,7 +31843,7 @@
       </c>
       <c r="L462" s="3" t="inlineStr">
         <is>
-          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
+          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
         </is>
       </c>
       <c r="M462" s="3" t="n"/>
@@ -31865,12 +31865,12 @@
       </c>
       <c r="D463" s="3" t="inlineStr">
         <is>
-          <t>📝 Village Medical - Livonia</t>
+          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>e3d707da-675d-4d7c-9356-2f53ec4d8a2e</t>
+          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -31894,16 +31894,16 @@
         </is>
       </c>
       <c r="J463" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Redford</t>
         </is>
       </c>
       <c r="L463" s="3" t="inlineStr">
         <is>
-          <t>17800 Newburgh Road, Livonia, Michigan, 48152</t>
+          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
         </is>
       </c>
       <c r="M463" s="3" t="n"/>
@@ -31925,12 +31925,12 @@
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>📝 Greg Monroe DO PC</t>
+          <t>📝 Beaumont Medical Center - Redford</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 1</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
+          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -31954,16 +31954,16 @@
         </is>
       </c>
       <c r="J464" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K464" s="2" t="inlineStr">
         <is>
-          <t>Westland</t>
+          <t>Redford Charter Township</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr">
         <is>
-          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
+          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
         </is>
       </c>
       <c r="M464" s="3" t="n"/>
@@ -31985,12 +31985,12 @@
       </c>
       <c r="D465" s="3" t="inlineStr">
         <is>
-          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
+          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
         </is>
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 1</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -32000,12 +32000,12 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
+          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I465" s="2" t="inlineStr">
@@ -32014,16 +32014,16 @@
         </is>
       </c>
       <c r="J465" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K465" s="2" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L465" s="3" t="inlineStr">
         <is>
-          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
+          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
         </is>
       </c>
       <c r="M465" s="3" t="n"/>
@@ -33065,27 +33065,27 @@
       </c>
       <c r="D483" s="3" t="inlineStr">
         <is>
-          <t>📝 Team Rehabilitation  - Washington</t>
+          <t>📝 Academic Internal Medicine (Ascension)</t>
         </is>
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 27</t>
+          <t>Tier 3 · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>940f0098-7ee4-47be-9425-5cd4bbc4dd0f</t>
+          <t>97ae4125-fd10-47de-8cae-c053e42232d0</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I483" s="2" t="inlineStr">
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="J483" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K483" s="2" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
       </c>
       <c r="L483" s="3" t="inlineStr">
         <is>
-          <t>64541 Van Dyke, Washington, Michigan, 48095</t>
+          <t>57850 Van Dyke Ave ste 600, Washington, Michigan, 48094</t>
         </is>
       </c>
       <c r="M483" s="3" t="n"/>
@@ -33125,32 +33125,32 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>📝 Academic Internal Medicine (Ascension)</t>
+          <t>Pediatric Consultants of Troy - Shelby Township</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Aug 24</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jun 22</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>97ae4125-fd10-47de-8cae-c053e42232d0</t>
+          <t>7f486a16-5999-4a69-b80d-9de7d1f85a2d</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J484" s="2" t="n">
@@ -33158,12 +33158,12 @@
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr">
         <is>
-          <t>57850 Van Dyke Ave ste 600, Washington, Michigan, 48094</t>
+          <t>50720 Schoenherr Rd, Shelby Township, MI 48315</t>
         </is>
       </c>
       <c r="M484" s="3" t="n"/>
@@ -33185,12 +33185,12 @@
       </c>
       <c r="D485" s="3" t="inlineStr">
         <is>
-          <t>Pediatric Consultants of Troy - Shelby Township</t>
+          <t>Shelby Pediatric Associates &amp; Child Lung Center</t>
         </is>
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jun 22</t>
+          <t>Tier 2 ortho · last check-in Jun 22</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>7f486a16-5999-4a69-b80d-9de7d1f85a2d</t>
+          <t>cbb6770d-0a7e-4610-a0a9-34566000818b</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="L485" s="3" t="inlineStr">
         <is>
-          <t>50720 Schoenherr Rd, Shelby Township, MI 48315</t>
+          <t>15125 22 Mile Rd, Shelby Township, MI 48315</t>
         </is>
       </c>
       <c r="M485" s="3" t="n"/>
@@ -33245,12 +33245,12 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>Shelby Pediatric Associates &amp; Child Lung Center</t>
+          <t>📝 Cornerstone St. Clair Internists</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 22</t>
+          <t>Tier 2 ortho · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
@@ -33260,17 +33260,17 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>cbb6770d-0a7e-4610-a0a9-34566000818b</t>
+          <t>cc9cf66d-2e3c-4e56-9aeb-85ba4b7e600c</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J486" s="2" t="n">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="L486" s="3" t="inlineStr">
         <is>
-          <t>15125 22 Mile Rd, Shelby Township, MI 48315</t>
+          <t>45640 Schoenherr Rd, Shelby Township, Michigan, 48315</t>
         </is>
       </c>
       <c r="M486" s="3" t="n"/>
@@ -33305,27 +33305,27 @@
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>📝 Cornerstone St. Clair Internists</t>
+          <t>📝 Macomb Spine Care</t>
         </is>
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Aug 24</t>
+          <t>Tier 3 · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>cc9cf66d-2e3c-4e56-9aeb-85ba4b7e600c</t>
+          <t>c3d66a4c-f046-43dd-ae93-ae4aabe95524</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I487" s="2" t="inlineStr">
@@ -33338,12 +33338,12 @@
       </c>
       <c r="K487" s="2" t="inlineStr">
         <is>
-          <t>Shelby Township</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L487" s="3" t="inlineStr">
         <is>
-          <t>45640 Schoenherr Rd, Shelby Township, Michigan, 48315</t>
+          <t>41060 Hayes Road, Clinton Township, Michigan, 48038</t>
         </is>
       </c>
       <c r="M487" s="3" t="n"/>
@@ -33365,27 +33365,27 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>📝 Macomb Spine Care</t>
+          <t>📝 Macomb Internal Medicine</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Aug 24</t>
+          <t>Tier 1 producer · last check-in Jul 10</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>c3d66a4c-f046-43dd-ae93-ae4aabe95524</t>
+          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I488" s="2" t="inlineStr">
@@ -33394,7 +33394,7 @@
         </is>
       </c>
       <c r="J488" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
       </c>
       <c r="L488" s="3" t="inlineStr">
         <is>
-          <t>41060 Hayes Road, Clinton Township, Michigan, 48038</t>
+          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
         </is>
       </c>
       <c r="M488" s="3" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>📝 Center For Hollistic Medicine</t>
+          <t>📝 MARY LEE, MD, PC</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
@@ -33620,17 +33620,17 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
+          <t>d62a30ae-10fe-4408-a2cc-7b0aa9422bb8</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J492" s="2" t="n">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="L492" s="3" t="inlineStr">
         <is>
-          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
+          <t>5799 W MAPLE RD STE 163, WEST BLOOMFIELD, MI, 48322</t>
         </is>
       </c>
       <c r="M492" s="3" t="n"/>
@@ -33665,12 +33665,12 @@
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>📝 MARY LEE, MD, PC</t>
+          <t>📝 Henry Ford Primary Care Center - 160</t>
         </is>
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>d62a30ae-10fe-4408-a2cc-7b0aa9422bb8</t>
+          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
@@ -33694,16 +33694,16 @@
         </is>
       </c>
       <c r="J493" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K493" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L493" s="3" t="inlineStr">
         <is>
-          <t>5799 W MAPLE RD STE 163, WEST BLOOMFIELD, MI, 48322</t>
+          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M493" s="3" t="n"/>
@@ -33725,7 +33725,7 @@
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Primary Care Center - 160</t>
+          <t>📝 Levine Clinic of Chiropractic</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
@@ -33740,12 +33740,12 @@
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
+          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I494" s="2" t="inlineStr">
@@ -33754,7 +33754,7 @@
         </is>
       </c>
       <c r="J494" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K494" s="2" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="L494" s="3" t="inlineStr">
         <is>
-          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
+          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M494" s="3" t="n"/>
@@ -33785,12 +33785,12 @@
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>📝 Levine Clinic of Chiropractic</t>
+          <t>📝 Corewell Internal Medicine Southfield</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
@@ -33800,12 +33800,12 @@
       </c>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
+          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I495" s="2" t="inlineStr">
@@ -33814,16 +33814,16 @@
         </is>
       </c>
       <c r="J495" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L495" s="3" t="inlineStr">
         <is>
-          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
+          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M495" s="3" t="n"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Internal Medicine Southfield</t>
+          <t>📝 Jian Zu MD</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
+          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
@@ -33883,7 +33883,7 @@
       </c>
       <c r="L496" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
+          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M496" s="3" t="n"/>
@@ -33905,7 +33905,7 @@
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>📝 Jian Zu MD</t>
+          <t>📝 Carson Center Specialty</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
+          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
@@ -33934,7 +33934,7 @@
         </is>
       </c>
       <c r="J497" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="L497" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
+          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
         </is>
       </c>
       <c r="M497" s="3" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>📝 Berkley Urgent Care</t>
         </is>
       </c>
       <c r="E499" s="3" t="inlineStr">
@@ -34040,7 +34040,7 @@
       </c>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
+          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
@@ -34058,12 +34058,12 @@
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="L499" s="3" t="inlineStr">
         <is>
-          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
+          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
         </is>
       </c>
       <c r="M499" s="3" t="n"/>
@@ -34085,12 +34085,12 @@
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>📝 Berkley Urgent Care</t>
+          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -34100,12 +34100,12 @@
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
+          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I500" s="2" t="inlineStr">
@@ -34118,12 +34118,12 @@
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Bloomfield</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr">
         <is>
-          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
+          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
         </is>
       </c>
       <c r="M500" s="3" t="n"/>
@@ -34145,12 +34145,12 @@
       </c>
       <c r="D501" s="3" t="inlineStr">
         <is>
-          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
+          <t>📝 Stonebrooke Family Physicians</t>
         </is>
       </c>
       <c r="E501" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 14</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
+          <t>c9013f02-25d6-4df2-96f8-b4f1e9936878</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
@@ -34174,16 +34174,16 @@
         </is>
       </c>
       <c r="J501" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K501" s="2" t="inlineStr">
         <is>
-          <t>Bloomfield</t>
+          <t>Rochester Hills</t>
         </is>
       </c>
       <c r="L501" s="3" t="inlineStr">
         <is>
-          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
+          <t>2940 Crooks Rd, Rochester Hills, Michigan, 48309</t>
         </is>
       </c>
       <c r="M501" s="3" t="n"/>
@@ -34205,27 +34205,27 @@
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>📝 Village Medical Farmington</t>
+          <t>📝 Corewell URGENT CARE BY WELLSTREET</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Prospect · last check-in Jul 29</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
+          <t>5f3e3632-715d-4e1c-b4ca-4c6bc3dac21e</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I502" s="2" t="inlineStr">
@@ -34234,16 +34234,16 @@
         </is>
       </c>
       <c r="J502" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Bloomfield Township</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr">
         <is>
-          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
+          <t>6543 TELEGRAPH RD, BLOOMFIELD TOWNSHIP, Michigan</t>
         </is>
       </c>
       <c r="M502" s="3" t="n"/>
@@ -34325,12 +34325,12 @@
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
+          <t>📝 Village Medical Farmington</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
+          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -34354,16 +34354,16 @@
         </is>
       </c>
       <c r="J504" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr">
         <is>
-          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
+          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M504" s="3" t="n"/>
@@ -34385,12 +34385,12 @@
       </c>
       <c r="D505" s="3" t="inlineStr">
         <is>
-          <t>📝 Hermann Banks MD PC</t>
+          <t>📝 SHEIKH MEDICAL CENTER</t>
         </is>
       </c>
       <c r="E505" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -34400,12 +34400,12 @@
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>31597599-5a74-4f7a-8cb0-0ebbb4b41303</t>
+          <t>7c32d0b4-c83f-4756-924c-9c8c74996a39</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I505" s="2" t="inlineStr">
@@ -34414,16 +34414,16 @@
         </is>
       </c>
       <c r="J505" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L505" s="3" t="inlineStr">
         <is>
-          <t>14700 Farmington Rd, Livonia, Michigan, 48154</t>
+          <t>22821 ORCHARD LAKE RD, FARMINGTON, MI, 48336</t>
         </is>
       </c>
       <c r="M505" s="3" t="n"/>
@@ -34445,12 +34445,12 @@
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>📝 Primal Recovery and PT</t>
+          <t>📝 Hermann Banks MD PC</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
@@ -34460,12 +34460,12 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>d7144e2d-aac6-4f68-a775-78db28d6b445</t>
+          <t>31597599-5a74-4f7a-8cb0-0ebbb4b41303</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="I506" s="2" t="inlineStr">
@@ -34474,7 +34474,7 @@
         </is>
       </c>
       <c r="J506" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
       </c>
       <c r="L506" s="3" t="inlineStr">
         <is>
-          <t>36600 Plymouth Road, Livonia, Michigan, 48150</t>
+          <t>14700 Farmington Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M506" s="3" t="n"/>
@@ -34505,12 +34505,12 @@
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>Imad George MD P.C. MHP</t>
+          <t>📝 Primal Recovery and PT</t>
         </is>
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -34520,17 +34520,17 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>24a73c28-f1ec-4808-8b5a-4d6702f86f8a</t>
+          <t>d7144e2d-aac6-4f68-a775-78db28d6b445</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J507" s="2" t="n">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="L507" s="3" t="inlineStr">
         <is>
-          <t>28000 Joy Road, Livonia, MI 48150</t>
+          <t>36600 Plymouth Road, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M507" s="3" t="n"/>
@@ -34565,12 +34565,12 @@
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>Corewell Internal Medicine - Family Practice DEARBORN HEIGHTS</t>
+          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 1</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
@@ -34580,30 +34580,30 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>88431ac1-44b1-4daf-a322-1fb70f0223f1</t>
+          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J508" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K508" s="2" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr">
         <is>
-          <t>27031 W Warren St, Dearborn Heights, MI 48127</t>
+          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M508" s="3" t="n"/>
@@ -34625,12 +34625,12 @@
       </c>
       <c r="D509" s="3" t="inlineStr">
         <is>
-          <t>📝 Premier Pediatrics Dearborn Heights</t>
+          <t>Imad George MD P.C. MHP</t>
         </is>
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -34640,17 +34640,17 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>bb55a71e-e12b-49be-9449-435cdc38cca4</t>
+          <t>24a73c28-f1ec-4808-8b5a-4d6702f86f8a</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J509" s="2" t="n">
@@ -34658,12 +34658,12 @@
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L509" s="3" t="inlineStr">
         <is>
-          <t>22318 Ford Road, Dearborn Heights, Michigan, 48127</t>
+          <t>28000 Joy Road, Livonia, MI 48150</t>
         </is>
       </c>
       <c r="M509" s="3" t="n"/>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
+          <t>Corewell Internal Medicine - Family Practice DEARBORN HEIGHTS</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
@@ -34700,30 +34700,30 @@
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
+          <t>88431ac1-44b1-4daf-a322-1fb70f0223f1</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J510" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
-          <t>Redford</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr">
         <is>
-          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
+          <t>27031 W Warren St, Dearborn Heights, MI 48127</t>
         </is>
       </c>
       <c r="M510" s="3" t="n"/>
@@ -34745,12 +34745,12 @@
       </c>
       <c r="D511" s="3" t="inlineStr">
         <is>
-          <t>📝 Beaumont Medical Center - Redford</t>
+          <t>📝 Premier Pediatrics Dearborn Heights</t>
         </is>
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
@@ -34760,30 +34760,30 @@
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
+          <t>bb55a71e-e12b-49be-9449-435cdc38cca4</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J511" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K511" s="2" t="inlineStr">
         <is>
-          <t>Redford Charter Township</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L511" s="3" t="inlineStr">
         <is>
-          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
+          <t>22318 Ford Road, Dearborn Heights, Michigan, 48127</t>
         </is>
       </c>
       <c r="M511" s="3" t="n"/>
@@ -34805,12 +34805,12 @@
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>White Lake Family Medicine</t>
+          <t>📝 DMC Orthopedics - Commerce Township</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 21</t>
+          <t>Tier 1 producer · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
@@ -34820,30 +34820,30 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>6f873c6d-498d-4d61-b717-d6648675da4e</t>
+          <t>568c9052-985c-48fa-b5bc-44baafba3dea</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J512" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
-          <t>White Lake</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr">
         <is>
-          <t>9178 Highland Rd, White Lake, MI 483864619</t>
+          <t>1 William Carls Drive, Michigan, 48382</t>
         </is>
       </c>
       <c r="M512" s="3" t="n"/>
@@ -34865,12 +34865,12 @@
       </c>
       <c r="D513" s="3" t="inlineStr">
         <is>
-          <t>ALAN L FELDMAN, DO, PC</t>
+          <t>📝 Providence Park Pediatrics - Novi</t>
         </is>
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 26</t>
+          <t>Tier 1 producer · last check-in Sep 25</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
@@ -34880,17 +34880,17 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>5d0e63d7-bdd3-445e-a627-ef0ea5dc48f7</t>
+          <t>9db7de95-514d-45c7-8a73-449a08d1d590</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J513" s="2" t="n">
@@ -34898,12 +34898,12 @@
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L513" s="3" t="inlineStr">
         <is>
-          <t>1965 Union Lake Rd, Commerce Township, MI 48382</t>
+          <t>26850 PROVIDENCE PKWY STE 455, NOVI, Michigan</t>
         </is>
       </c>
       <c r="M513" s="3" t="n"/>
@@ -34925,12 +34925,12 @@
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>📝 CoreMed - Commerce</t>
+          <t>📝 PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 21</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>eab7d954-a523-466a-a75b-3eca7bf9c6d0</t>
+          <t>f5f4f354-94f3-42a1-a3be-10f8a64cdaae</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -34958,12 +34958,12 @@
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Walled Lake</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr">
         <is>
-          <t>2600 Union Lake Rd suite 140 Commerce Township, Michigan, 48382</t>
+          <t>100 N POND DR STE C, WALLED LAKE, MI, 48390</t>
         </is>
       </c>
       <c r="M514" s="3" t="n"/>
@@ -34985,12 +34985,12 @@
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>📝 IHA UNION LAKE PEDIATRICS</t>
+          <t>LAKES INTERNAL MEDICINE - 2150</t>
         </is>
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
@@ -35000,17 +35000,17 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>905d0bbb-d935-4258-8a1e-2e30d0a25987</t>
+          <t>8b9ada78-08d8-45f0-8d09-c043db61a6fd</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J515" s="2" t="n">
@@ -35018,12 +35018,12 @@
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L515" s="3" t="inlineStr">
         <is>
-          <t>2630 UNION LAKE RD STE 100, COMMERCE TOWNSHIP, Michigan</t>
+          <t>2300 Haggerty Rd Ste 2150, West Bloomfield, MI 48323</t>
         </is>
       </c>
       <c r="M515" s="3" t="n"/>
@@ -35045,12 +35045,12 @@
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>📝 Rodnick Chiropractic</t>
+          <t>COMMERCE PRIMARY CARE, PC</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
@@ -35060,30 +35060,30 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>97e1431f-4c5b-4ec4-b3a5-47267613937b</t>
+          <t>512973f9-6ce5-4941-bf0e-dbc021ae2dc0</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Aug 21 (Joe/Kristen)</t>
         </is>
       </c>
       <c r="J516" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K516" s="2" t="inlineStr">
         <is>
-          <t>Commerce Charter Township</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr">
         <is>
-          <t>2685 Union Lake Rd Commerce Charter Twp, Commerce Charter Township, Michigan, 48382</t>
+          <t>8800 Commerce Rd, Commerce Township, MI 48382</t>
         </is>
       </c>
       <c r="M516" s="3" t="n"/>
@@ -35105,12 +35105,12 @@
       </c>
       <c r="D517" s="3" t="inlineStr">
         <is>
-          <t>COMMERCE PRIMARY CARE, PC</t>
+          <t>📝 Rodnick Chiropractic</t>
         </is>
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 21</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -35120,30 +35120,30 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>512973f9-6ce5-4941-bf0e-dbc021ae2dc0</t>
+          <t>97e1431f-4c5b-4ec4-b3a5-47267613937b</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>Added Aug 21 (Joe/Kristen)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J517" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K517" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Commerce Charter Township</t>
         </is>
       </c>
       <c r="L517" s="3" t="inlineStr">
         <is>
-          <t>8800 Commerce Rd, Commerce Township, MI 48382</t>
+          <t>2685 Union Lake Rd Commerce Charter Twp, Commerce Charter Township, Michigan, 48382</t>
         </is>
       </c>
       <c r="M517" s="3" t="n"/>
@@ -35165,12 +35165,12 @@
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>📝 DMC Orthopedics - Commerce Township</t>
+          <t>📝 IHA UNION LAKE PEDIATRICS</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 21</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -35180,21 +35180,21 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>568c9052-985c-48fa-b5bc-44baafba3dea</t>
+          <t>905d0bbb-d935-4258-8a1e-2e30d0a25987</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J518" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
       </c>
       <c r="L518" s="3" t="inlineStr">
         <is>
-          <t>1 William Carls Drive, Michigan, 48382</t>
+          <t>2630 UNION LAKE RD STE 100, COMMERCE TOWNSHIP, Michigan</t>
         </is>
       </c>
       <c r="M518" s="3" t="n"/>
@@ -35225,12 +35225,12 @@
       </c>
       <c r="D519" s="3" t="inlineStr">
         <is>
-          <t>LAKES INTERNAL MEDICINE - 2150</t>
+          <t>📝 CoreMed - Commerce</t>
         </is>
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -35240,17 +35240,17 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>8b9ada78-08d8-45f0-8d09-c043db61a6fd</t>
+          <t>eab7d954-a523-466a-a75b-3eca7bf9c6d0</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J519" s="2" t="n">
@@ -35258,12 +35258,12 @@
       </c>
       <c r="K519" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L519" s="3" t="inlineStr">
         <is>
-          <t>2300 Haggerty Rd Ste 2150, West Bloomfield, MI 48323</t>
+          <t>2600 Union Lake Rd suite 140 Commerce Township, Michigan, 48382</t>
         </is>
       </c>
       <c r="M519" s="3" t="n"/>
@@ -35285,12 +35285,12 @@
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>📝 PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC</t>
+          <t>ALAN L FELDMAN, DO, PC</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in May 26</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -35300,17 +35300,17 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>f5f4f354-94f3-42a1-a3be-10f8a64cdaae</t>
+          <t>5d0e63d7-bdd3-445e-a627-ef0ea5dc48f7</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J520" s="2" t="n">
@@ -35318,12 +35318,12 @@
       </c>
       <c r="K520" s="2" t="inlineStr">
         <is>
-          <t>Walled Lake</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr">
         <is>
-          <t>100 N POND DR STE C, WALLED LAKE, MI, 48390</t>
+          <t>1965 Union Lake Rd, Commerce Township, MI 48382</t>
         </is>
       </c>
       <c r="M520" s="3" t="n"/>
@@ -35345,27 +35345,27 @@
       </c>
       <c r="D521" s="3" t="inlineStr">
         <is>
-          <t>📝 Providence Park Pediatrics - Novi</t>
+          <t>📝 HEALING HANDS URGENT CARE</t>
         </is>
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 25</t>
+          <t>Prospect · last check-in Jul 30</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>9db7de95-514d-45c7-8a73-449a08d1d590</t>
+          <t>ed1959ed-68b4-4788-bfa4-24c1e6d994d6</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I521" s="2" t="inlineStr">
@@ -35374,16 +35374,16 @@
         </is>
       </c>
       <c r="J521" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K521" s="2" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Sylvan Lake</t>
         </is>
       </c>
       <c r="L521" s="3" t="inlineStr">
         <is>
-          <t>26850 PROVIDENCE PKWY STE 455, NOVI, Michigan</t>
+          <t>2157 ORCHARD LAKE RD, SYLVAN LAKE, Michigan</t>
         </is>
       </c>
       <c r="M521" s="3" t="n"/>
@@ -35585,12 +35585,12 @@
       </c>
       <c r="D525" s="3" t="inlineStr">
         <is>
-          <t>Mercy Family Care Center</t>
+          <t>ASCENSION MACOMB OAKLAND HOSPITAL MOTOR CITY INTERNISTS</t>
         </is>
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -35600,7 +35600,7 @@
       </c>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>3dfcef6a-be30-4421-b9ae-e70c90558ff6</t>
+          <t>dc78e75f-e0d1-4c67-8de9-8ea4f13f15a1</t>
         </is>
       </c>
       <c r="H525" s="2" t="inlineStr">
@@ -35618,12 +35618,12 @@
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L525" s="3" t="inlineStr">
         <is>
-          <t>2107 East 14 Mile Road, Sterling Heights, MI 48310</t>
+          <t>11885 E 12 Mile Rd Ste 200B, Warren, MI 48093</t>
         </is>
       </c>
       <c r="M525" s="3" t="n"/>
@@ -35645,7 +35645,7 @@
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>📝 Northpointe Pediatrics</t>
+          <t>📝 Michigan Compassionate Care</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr">
@@ -35660,12 +35660,12 @@
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
+          <t>33d0c0aa-7d47-450d-9673-71acb651321c</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I526" s="2" t="inlineStr">
@@ -35674,7 +35674,7 @@
         </is>
       </c>
       <c r="J526" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
       </c>
       <c r="L526" s="3" t="inlineStr">
         <is>
-          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
+          <t>28401 Hoover, Warren, Michigan, 48093</t>
         </is>
       </c>
       <c r="M526" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="D527" s="3" t="inlineStr">
         <is>
-          <t>ASCENSION MACOMB OAKLAND HOSPITAL MOTOR CITY INTERNISTS</t>
+          <t>📝 FERRIS, MARY C, MEDICAL GROUP</t>
         </is>
       </c>
       <c r="E527" s="3" t="inlineStr">
@@ -35720,17 +35720,17 @@
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>dc78e75f-e0d1-4c67-8de9-8ea4f13f15a1</t>
+          <t>a5a045ce-889d-4018-81f5-3fd8d3d7af6b</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J527" s="2" t="n">
@@ -35743,7 +35743,7 @@
       </c>
       <c r="L527" s="3" t="inlineStr">
         <is>
-          <t>11885 E 12 Mile Rd Ste 200B, Warren, MI 48093</t>
+          <t>28111 HOOVER RD STE 1A, WARREN, Michigan</t>
         </is>
       </c>
       <c r="M527" s="3" t="n"/>
@@ -35765,7 +35765,7 @@
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>📝 Michigan Compassionate Care</t>
+          <t>Hoover Primary Care Medical Group</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr">
@@ -35780,21 +35780,21 @@
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>33d0c0aa-7d47-450d-9673-71acb651321c</t>
+          <t>d2472b07-69ea-403b-b954-d5d8227b1364</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J528" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
       </c>
       <c r="L528" s="3" t="inlineStr">
         <is>
-          <t>28401 Hoover, Warren, Michigan, 48093</t>
+          <t>28111 Hoover Rd, Ste 5A Warren, Mi 48093, Usa, Warren, MI 48093</t>
         </is>
       </c>
       <c r="M528" s="3" t="n"/>
@@ -35825,7 +35825,7 @@
       </c>
       <c r="D529" s="3" t="inlineStr">
         <is>
-          <t>📝 FERRIS, MARY C, MEDICAL GROUP</t>
+          <t>Macomb Neurology Associates</t>
         </is>
       </c>
       <c r="E529" s="3" t="inlineStr">
@@ -35840,17 +35840,17 @@
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>a5a045ce-889d-4018-81f5-3fd8d3d7af6b</t>
+          <t>1023090552</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J529" s="2" t="n">
@@ -35863,7 +35863,7 @@
       </c>
       <c r="L529" s="3" t="inlineStr">
         <is>
-          <t>28111 HOOVER RD STE 1A, WARREN, Michigan</t>
+          <t>27427 Schoenherr Rd, Warren, MI 48088</t>
         </is>
       </c>
       <c r="M529" s="3" t="n"/>
@@ -35885,27 +35885,27 @@
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>Hoover Primary Care Medical Group</t>
+          <t>Emcura Immediate Care - Grosse Pointe</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Prospect · last check-in Jun 3</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>d2472b07-69ea-403b-b954-d5d8227b1364</t>
+          <t>bf549ea4-0d9c-4877-927c-ed3f99bf0988</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I530" s="2" t="inlineStr">
@@ -35914,16 +35914,16 @@
         </is>
       </c>
       <c r="J530" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Grosse Pointe Woods</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr">
         <is>
-          <t>28111 Hoover Rd, Ste 5A Warren, Mi 48093, Usa, Warren, MI 48093</t>
+          <t>20599 Mack Ave, Grosse Pointe Woods, MI 48236</t>
         </is>
       </c>
       <c r="M530" s="3" t="n"/>
@@ -36065,12 +36065,12 @@
       </c>
       <c r="D533" s="3" t="inlineStr">
         <is>
-          <t>Macomb Pediatrics - Clinton Township</t>
+          <t>📝 Legacy Family Medicine</t>
         </is>
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
@@ -36080,17 +36080,17 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
+          <t>1558340356</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J533" s="2" t="n">
@@ -36098,12 +36098,12 @@
       </c>
       <c r="K533" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L533" s="3" t="inlineStr">
         <is>
-          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
+          <t>35429 Schoenherr Rd, Sterling Heights, MI, 48312</t>
         </is>
       </c>
       <c r="M533" s="3" t="n"/>
@@ -36125,12 +36125,12 @@
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Medical Center - East Jefferson</t>
+          <t>Macomb Pediatrics - Clinton Township</t>
         </is>
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 17</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
@@ -36140,17 +36140,17 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>1043384555</t>
+          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J534" s="2" t="n">
@@ -36158,12 +36158,12 @@
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>St Clair Shores</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr">
         <is>
-          <t>24725 E Jefferson, Saint Clair Shores, MI, 48080</t>
+          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
         </is>
       </c>
       <c r="M534" s="3" t="n"/>
@@ -36185,7 +36185,7 @@
       </c>
       <c r="D535" s="3" t="inlineStr">
         <is>
-          <t>📝 Cornerstone Lakefront Internists</t>
+          <t>📝 Henry Ford Medical Center - East Jefferson</t>
         </is>
       </c>
       <c r="E535" s="3" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>16c0ac85-6d3c-4c74-97b4-385a2a7fac00</t>
+          <t>1043384555</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -36223,7 +36223,7 @@
       </c>
       <c r="L535" s="3" t="inlineStr">
         <is>
-          <t>20952 Twelve Mile Rd ste 101, St. Clair Shores, Michigan, 48081</t>
+          <t>24725 E Jefferson, Saint Clair Shores, MI, 48080</t>
         </is>
       </c>
       <c r="M535" s="3" t="n"/>
@@ -36245,7 +36245,7 @@
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>📝 Lupo Chiropractic Center</t>
+          <t>📝 Cornerstone Lakefront Internists</t>
         </is>
       </c>
       <c r="E536" s="3" t="inlineStr">
@@ -36260,12 +36260,12 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>ea3dd183-15b5-491c-b6b5-55d6404f4a22</t>
+          <t>16c0ac85-6d3c-4c74-97b4-385a2a7fac00</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I536" s="2" t="inlineStr">
@@ -36278,12 +36278,12 @@
       </c>
       <c r="K536" s="2" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr">
         <is>
-          <t>27850 Gratiot Avenue, Roseville, Michigan, 48066</t>
+          <t>20952 Twelve Mile Rd ste 101, St. Clair Shores, Michigan, 48081</t>
         </is>
       </c>
       <c r="M536" s="3" t="n"/>
@@ -36305,12 +36305,12 @@
       </c>
       <c r="D537" s="3" t="inlineStr">
         <is>
-          <t>📝 Pulmonary &amp; Medical Associates</t>
+          <t>📝 Lupo Chiropractic Center</t>
         </is>
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Sep 17</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
@@ -36320,12 +36320,12 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>dda630a5-9d61-49cd-bec6-61084e47ddb9</t>
+          <t>ea3dd183-15b5-491c-b6b5-55d6404f4a22</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I537" s="2" t="inlineStr">
@@ -36334,16 +36334,16 @@
         </is>
       </c>
       <c r="J537" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L537" s="3" t="inlineStr">
         <is>
-          <t>27472 Schoenherr Rd #100, Warren, MI, 48088</t>
+          <t>27850 Gratiot Avenue, Roseville, Michigan, 48066</t>
         </is>
       </c>
       <c r="M537" s="3" t="n"/>
@@ -36365,7 +36365,7 @@
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>Macomb Neurology Associates</t>
+          <t>📝 Pulmonary &amp; Medical Associates</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr">
@@ -36380,21 +36380,21 @@
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>1023090552</t>
+          <t>dda630a5-9d61-49cd-bec6-61084e47ddb9</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J538" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
       </c>
       <c r="L538" s="3" t="inlineStr">
         <is>
-          <t>27427 Schoenherr Rd, Warren, MI 48088</t>
+          <t>27472 Schoenherr Rd #100, Warren, MI, 48088</t>
         </is>
       </c>
       <c r="M538" s="3" t="n"/>
@@ -36725,12 +36725,12 @@
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>Burhani Medical Center - use this one</t>
+          <t>📝 Center For Hollistic Medicine</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 13</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F544" s="2" t="inlineStr">
@@ -36740,17 +36740,17 @@
       </c>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>3ade325e-79e3-41bc-a8b9-565bcfc77f2c</t>
+          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
         </is>
       </c>
       <c r="H544" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J544" s="2" t="n">
@@ -36758,12 +36758,12 @@
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr">
         <is>
-          <t>32910 West 13 Mile Road, A101, Farmington Hills, MI 48334</t>
+          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
         </is>
       </c>
       <c r="M544" s="3" t="n"/>
@@ -36785,12 +36785,12 @@
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Primary Care - Orchard Lake Road North</t>
+          <t>Burhani Medical Center - use this one</t>
         </is>
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 13</t>
+          <t>Tier 1 producer · last check-in May 13</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
@@ -36800,21 +36800,21 @@
       </c>
       <c r="G545" s="2" t="inlineStr">
         <is>
-          <t>960ab807-be26-45c0-bbf9-135ef0a45ae0</t>
+          <t>3ade325e-79e3-41bc-a8b9-565bcfc77f2c</t>
         </is>
       </c>
       <c r="H545" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I545" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J545" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
       </c>
       <c r="L545" s="3" t="inlineStr">
         <is>
-          <t>27970 ORCHARD LAKE RD, FARMINGTON HILLS, Michigan, 48334</t>
+          <t>32910 West 13 Mile Road, A101, Farmington Hills, MI 48334</t>
         </is>
       </c>
       <c r="M545" s="3" t="n"/>
@@ -36845,12 +36845,12 @@
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>📝 ORCHARD PRIMARY CARE</t>
+          <t>📝 Henry Ford Primary Care - Orchard Lake Road North</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Aug 13</t>
         </is>
       </c>
       <c r="F546" s="2" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
+          <t>960ab807-be26-45c0-bbf9-135ef0a45ae0</t>
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr">
@@ -36874,7 +36874,7 @@
         </is>
       </c>
       <c r="J546" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
       </c>
       <c r="L546" s="3" t="inlineStr">
         <is>
-          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
+          <t>27970 ORCHARD LAKE RD, FARMINGTON HILLS, Michigan, 48334</t>
         </is>
       </c>
       <c r="M546" s="3" t="n"/>
@@ -36905,7 +36905,7 @@
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>📝 Powers Family Medicine</t>
+          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
         </is>
       </c>
       <c r="E547" s="3" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="G547" s="2" t="inlineStr">
         <is>
-          <t>00-761-7874</t>
+          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
         </is>
       </c>
       <c r="H547" s="2" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="L547" s="3" t="inlineStr">
         <is>
-          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
+          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
         </is>
       </c>
       <c r="M547" s="3" t="n"/>
@@ -36965,12 +36965,12 @@
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>📝 SHEIKH MEDICAL CENTER</t>
+          <t>📝 Legend Health - Now One Health</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="G548" s="2" t="inlineStr">
         <is>
-          <t>7c32d0b4-c83f-4756-924c-9c8c74996a39</t>
+          <t>078d2fa6-e81c-41d1-95f2-04234d511192</t>
         </is>
       </c>
       <c r="H548" s="2" t="inlineStr">
@@ -36998,12 +36998,12 @@
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr">
         <is>
-          <t>22821 ORCHARD LAKE RD, FARMINGTON, MI, 48336</t>
+          <t>29201 Telegraph Rd, ste 403, Southfield, MI, 48034</t>
         </is>
       </c>
       <c r="M548" s="3" t="n"/>
@@ -37205,45 +37205,45 @@
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>📝 FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
+          <t>Chander Kanta MD</t>
         </is>
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 2 ortho · last check-in Jun 20</t>
         </is>
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>f4a7f5a0-d8e0-49ff-874a-04f12057fc5f</t>
+          <t>1558467373</t>
         </is>
       </c>
       <c r="H552" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J552" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Center Line</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr">
         <is>
-          <t>12169 JOSEPH CAMPAU ST, HAMTRAMCK, MI, 48212</t>
+          <t>26328 Van Dyke Ave, Center Line, MI 48015</t>
         </is>
       </c>
       <c r="M552" s="3" t="n"/>
@@ -37265,12 +37265,12 @@
       </c>
       <c r="D553" s="3" t="inlineStr">
         <is>
-          <t>Priority Medical Center</t>
+          <t>Office of Clara Kamath Wood MD</t>
         </is>
       </c>
       <c r="E553" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in May 19</t>
+          <t>Tier 2 ortho · last check-in Apr 20</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
@@ -37280,7 +37280,7 @@
       </c>
       <c r="G553" s="2" t="inlineStr">
         <is>
-          <t>9d8474e5-a7b6-465e-b626-81635fd4f242</t>
+          <t>ccad7a72-2fa8-4c91-af14-5995cd5adacf</t>
         </is>
       </c>
       <c r="H553" s="2" t="inlineStr">
@@ -37298,12 +37298,12 @@
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L553" s="3" t="inlineStr">
         <is>
-          <t>12101 Joseph Campau Avenue, Hamtramck, MI 48212</t>
+          <t>18245 East 10 Mile Road, Ste 120, Roseville, MI 48066</t>
         </is>
       </c>
       <c r="M553" s="3" t="n"/>
@@ -37325,45 +37325,45 @@
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>TRUST FAMILY CARE CENTER, PLLC</t>
+          <t>📝 Epic Health - St Clair Shores</t>
         </is>
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 19</t>
+          <t>Tier 2 ortho · last check-in May 6</t>
         </is>
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>10524116-5eb6-4e8c-b740-351bf86df478</t>
+          <t>8c04fb31-3380-488f-aa8a-954ff32146f2</t>
         </is>
       </c>
       <c r="H554" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J554" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>St Clair Shores</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr">
         <is>
-          <t>9421 Joseph Campau St, Hamtramck, MI 48212</t>
+          <t>28001 Harper, St. Clair Shores, Michigan, 48081</t>
         </is>
       </c>
       <c r="M554" s="3" t="n"/>
@@ -37385,22 +37385,22 @@
       </c>
       <c r="D555" s="3" t="inlineStr">
         <is>
-          <t>WAYNE COMMUNITY HEALTH CENTERS, INC</t>
+          <t>Covenant Community Care - Grosse Pointe</t>
         </is>
       </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 2 ortho · last check-in Jul 7</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G555" s="2" t="inlineStr">
         <is>
-          <t>b89491cd-a8b2-4493-8dba-2e2146e504a0</t>
+          <t>9d486232-ffab-4685-aa35-45d74618d1e7</t>
         </is>
       </c>
       <c r="H555" s="2" t="inlineStr">
@@ -37414,16 +37414,16 @@
         </is>
       </c>
       <c r="J555" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Grosse Pointe</t>
         </is>
       </c>
       <c r="L555" s="3" t="inlineStr">
         <is>
-          <t>9021 Joseph Campau St, Hamtramck, MI nan</t>
+          <t>20901 Moross Rd, Grosse Pointe, MI 48236</t>
         </is>
       </c>
       <c r="M555" s="3" t="n"/>
@@ -37445,27 +37445,27 @@
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>METROPOLITAN MEDICAL CENTER, PLLC</t>
+          <t>Corewell Health Urgent Care</t>
         </is>
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 19</t>
+          <t>Tier 2 ortho · last check-in Jun 3</t>
         </is>
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
         <is>
-          <t>44ca23fe-7723-4691-8484-5995f7be8e7e</t>
+          <t>1d0a3fc4-bd55-4b73-b1fa-eb6ad99ce4e0</t>
         </is>
       </c>
       <c r="H556" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I556" s="2" t="inlineStr">
@@ -37474,16 +37474,16 @@
         </is>
       </c>
       <c r="J556" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
-          <t>Hamtramck</t>
+          <t>Grosse Pointe</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr">
         <is>
-          <t>9230 Joseph Campau St, Hamtramck, MI 48212</t>
+          <t>18700 Mack Ave, Grosse Pointe, MI nan</t>
         </is>
       </c>
       <c r="M556" s="3" t="n"/>
@@ -37505,27 +37505,27 @@
       </c>
       <c r="D557" s="3" t="inlineStr">
         <is>
-          <t>Corewell Health Urgent Care</t>
+          <t>METROPOLITAN MEDICAL CENTER, PLLC</t>
         </is>
       </c>
       <c r="E557" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 3</t>
+          <t>Tier 1 producer · last check-in May 19</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>1d0a3fc4-bd55-4b73-b1fa-eb6ad99ce4e0</t>
+          <t>44ca23fe-7723-4691-8484-5995f7be8e7e</t>
         </is>
       </c>
       <c r="H557" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I557" s="2" t="inlineStr">
@@ -37534,16 +37534,16 @@
         </is>
       </c>
       <c r="J557" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L557" s="3" t="inlineStr">
         <is>
-          <t>18700 Mack Ave, Grosse Pointe, MI nan</t>
+          <t>9230 Joseph Campau St, Hamtramck, MI 48212</t>
         </is>
       </c>
       <c r="M557" s="3" t="n"/>
@@ -37565,22 +37565,22 @@
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>Covenant Community Care - Grosse Pointe</t>
+          <t>WAYNE COMMUNITY HEALTH CENTERS, INC</t>
         </is>
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jul 7</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>9d486232-ffab-4685-aa35-45d74618d1e7</t>
+          <t>b89491cd-a8b2-4493-8dba-2e2146e504a0</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
@@ -37594,16 +37594,16 @@
         </is>
       </c>
       <c r="J558" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr">
         <is>
-          <t>20901 Moross Rd, Grosse Pointe, MI 48236</t>
+          <t>9021 Joseph Campau St, Hamtramck, MI nan</t>
         </is>
       </c>
       <c r="M558" s="3" t="n"/>
@@ -37625,27 +37625,27 @@
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>Correct Cornerstone Pediatrics - 9 Mile</t>
+          <t>TRUST FAMILY CARE CENTER, PLLC</t>
         </is>
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jul 21</t>
+          <t>Tier 1 producer · last check-in May 19</t>
         </is>
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G559" s="2" t="inlineStr">
         <is>
-          <t>73e281ce-3e3c-4048-afb7-bb11160a109f</t>
+          <t>10524116-5eb6-4e8c-b740-351bf86df478</t>
         </is>
       </c>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I559" s="2" t="inlineStr">
@@ -37654,16 +37654,16 @@
         </is>
       </c>
       <c r="J559" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K559" s="2" t="inlineStr">
         <is>
-          <t>St Clair Shores</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L559" s="3" t="inlineStr">
         <is>
-          <t>20225 East 9 Mile Road, St. Clair Shores, MI 48080</t>
+          <t>9421 Joseph Campau St, Hamtramck, MI 48212</t>
         </is>
       </c>
       <c r="M559" s="3" t="n"/>
@@ -37685,45 +37685,45 @@
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>Eastlake Pediatrics</t>
+          <t>📝 FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
         </is>
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jul 21</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
         <is>
-          <t>1558300699</t>
+          <t>f4a7f5a0-d8e0-49ff-874a-04f12057fc5f</t>
         </is>
       </c>
       <c r="H560" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J560" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr">
         <is>
-          <t>18325 E 10 Mile Rd, Ste 100, Roseville, MI 480664990</t>
+          <t>12169 JOSEPH CAMPAU ST, HAMTRAMCK, MI, 48212</t>
         </is>
       </c>
       <c r="M560" s="3" t="n"/>
@@ -37745,12 +37745,12 @@
       </c>
       <c r="D561" s="3" t="inlineStr">
         <is>
-          <t>📝 Epic Health - St Clair Shores</t>
+          <t>Priority Medical Center</t>
         </is>
       </c>
       <c r="E561" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in May 6</t>
+          <t>Tier 2 ortho · last check-in May 19</t>
         </is>
       </c>
       <c r="F561" s="2" t="inlineStr">
@@ -37760,17 +37760,17 @@
       </c>
       <c r="G561" s="2" t="inlineStr">
         <is>
-          <t>8c04fb31-3380-488f-aa8a-954ff32146f2</t>
+          <t>9d8474e5-a7b6-465e-b626-81635fd4f242</t>
         </is>
       </c>
       <c r="H561" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I561" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J561" s="2" t="n">
@@ -37778,12 +37778,12 @@
       </c>
       <c r="K561" s="2" t="inlineStr">
         <is>
-          <t>St Clair Shores</t>
+          <t>Hamtramck</t>
         </is>
       </c>
       <c r="L561" s="3" t="inlineStr">
         <is>
-          <t>28001 Harper, St. Clair Shores, Michigan, 48081</t>
+          <t>12101 Joseph Campau Avenue, Hamtramck, MI 48212</t>
         </is>
       </c>
       <c r="M561" s="3" t="n"/>
@@ -37805,12 +37805,12 @@
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>📝 Stonebrooke Family Physicians</t>
+          <t>MALI AND MALI PEDIATRICS - use this one</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 14</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
@@ -37820,30 +37820,30 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>c9013f02-25d6-4df2-96f8-b4f1e9936878</t>
+          <t>2e26f7de-9e76-464a-a322-fbef639b64d7</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J562" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
-          <t>Rochester Hills</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr">
         <is>
-          <t>2940 Crooks Rd, Rochester Hills, Michigan, 48309</t>
+          <t>44344 Dequindre Rd Ste 510, Sterling Heights, MI nan</t>
         </is>
       </c>
       <c r="M562" s="3" t="n"/>
@@ -37865,12 +37865,12 @@
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>MALI AND MALI PEDIATRICS - use this one</t>
+          <t>📝 Michigan Primary Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F563" s="2" t="inlineStr">
@@ -37880,17 +37880,17 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>2e26f7de-9e76-464a-a322-fbef639b64d7</t>
+          <t>ce3b56cf-1381-41d0-b067-752448464958</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I563" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J563" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="L563" s="3" t="inlineStr">
         <is>
-          <t>44344 Dequindre Rd Ste 510, Sterling Heights, MI nan</t>
+          <t>41400 Dequindre Rd, ste 121, Sterling Heights, Michigan, 48314</t>
         </is>
       </c>
       <c r="M563" s="3" t="n"/>
@@ -37925,12 +37925,12 @@
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>📝 Michigan Primary Care - Sterling Heights</t>
+          <t>Concentra Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F564" s="2" t="inlineStr">
@@ -37940,17 +37940,17 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>ce3b56cf-1381-41d0-b067-752448464958</t>
+          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J564" s="2" t="n">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="L564" s="3" t="inlineStr">
         <is>
-          <t>41400 Dequindre Rd, ste 121, Sterling Heights, Michigan, 48314</t>
+          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M564" s="3" t="n"/>
@@ -37985,12 +37985,12 @@
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>Professional Village Medical Center</t>
+          <t>📝 Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Sep 3</t>
         </is>
       </c>
       <c r="F565" s="2" t="inlineStr">
@@ -38000,21 +38000,21 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>1427031756</t>
+          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I565" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J565" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K565" s="2" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
       </c>
       <c r="L565" s="3" t="inlineStr">
         <is>
-          <t>13700 19 Mile Rd, Sterling Heights, MI 48313</t>
+          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M565" s="3" t="n"/>
@@ -38045,12 +38045,12 @@
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>Concentra Urgent Care - Sterling Heights</t>
+          <t>📝 Tri-County Medical Clinic</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Sep 3</t>
         </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
@@ -38060,17 +38060,17 @@
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
+          <t>1386634749</t>
         </is>
       </c>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J566" s="2" t="n">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="L566" s="3" t="inlineStr">
         <is>
-          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
+          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
         </is>
       </c>
       <c r="M566" s="3" t="n"/>
@@ -38105,12 +38105,12 @@
       </c>
       <c r="D567" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care - Sterling Heights</t>
+          <t>Lily’s Medical Group</t>
         </is>
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 3</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F567" s="2" t="inlineStr">
@@ -38120,21 +38120,21 @@
       </c>
       <c r="G567" s="2" t="inlineStr">
         <is>
-          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
+          <t>0aec7757-4391-42a3-94f2-3cfa9ea9aa99</t>
         </is>
       </c>
       <c r="H567" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I567" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J567" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="L567" s="3" t="inlineStr">
         <is>
-          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
+          <t>37300 Dequindre Rd Ste 102, Sterling Heights, MI 48310</t>
         </is>
       </c>
       <c r="M567" s="3" t="n"/>
@@ -38165,12 +38165,12 @@
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>📝 Tri-County Medical Clinic</t>
+          <t>📝 Sterling Physicians</t>
         </is>
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 3</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
@@ -38180,7 +38180,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>1386634749</t>
+          <t>1972593499</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="L568" s="3" t="inlineStr">
         <is>
-          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
+          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M568" s="3" t="n"/>
@@ -38225,12 +38225,12 @@
       </c>
       <c r="D569" s="3" t="inlineStr">
         <is>
-          <t>Lily’s Medical Group</t>
+          <t>📝 Get Well Urgent Care Madison Heights</t>
         </is>
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Aug 25</t>
         </is>
       </c>
       <c r="F569" s="2" t="inlineStr">
@@ -38240,30 +38240,30 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>0aec7757-4391-42a3-94f2-3cfa9ea9aa99</t>
+          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I569" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J569" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L569" s="3" t="inlineStr">
         <is>
-          <t>37300 Dequindre Rd Ste 102, Sterling Heights, MI 48310</t>
+          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M569" s="3" t="n"/>
@@ -38285,27 +38285,27 @@
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>📝 Sterling Physicians</t>
+          <t>📝 Corewell Health Urgent Care - Warren West</t>
         </is>
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Prospect · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>1972593499</t>
+          <t>9152636b-052e-44f2-ab21-a7abf86561ff</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I570" s="2" t="inlineStr">
@@ -38314,16 +38314,16 @@
         </is>
       </c>
       <c r="J570" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K570" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr">
         <is>
-          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+          <t>28324 Dequindre Road, Warren, Michigan, 48092</t>
         </is>
       </c>
       <c r="M570" s="3" t="n"/>
@@ -38345,27 +38345,27 @@
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Health Urgent Care - Warren West</t>
+          <t>📝 Lifetime Family Care</t>
         </is>
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F571" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>9152636b-052e-44f2-ab21-a7abf86561ff</t>
+          <t>b70053c3-f0fd-41de-9386-95fcc448a738</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I571" s="2" t="inlineStr">
@@ -38374,16 +38374,16 @@
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L571" s="3" t="inlineStr">
         <is>
-          <t>28324 Dequindre Road, Warren, Michigan, 48092</t>
+          <t>26393 Dequindre Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M571" s="3" t="n"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
+          <t>📝 Ivy Rehab - Farmington</t>
         </is>
       </c>
       <c r="E572" s="3" t="inlineStr">
@@ -38420,12 +38420,12 @@
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
+          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I572" s="2" t="inlineStr">
@@ -38438,12 +38438,12 @@
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr">
         <is>
-          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
+          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M572" s="3" t="n"/>
@@ -38465,12 +38465,12 @@
       </c>
       <c r="D573" s="3" t="inlineStr">
         <is>
-          <t>📝 Carson Center Specialty</t>
+          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F573" s="2" t="inlineStr">
@@ -38480,7 +38480,7 @@
       </c>
       <c r="G573" s="2" t="inlineStr">
         <is>
-          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
+          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
         </is>
       </c>
       <c r="H573" s="2" t="inlineStr">
@@ -38494,16 +38494,16 @@
         </is>
       </c>
       <c r="J573" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L573" s="3" t="inlineStr">
         <is>
-          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
+          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M573" s="3" t="n"/>
@@ -38525,12 +38525,12 @@
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>📝 Legend Health - Now One Health</t>
+          <t>Middlebelt Medical Center</t>
         </is>
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Jun 29</t>
         </is>
       </c>
       <c r="F574" s="2" t="inlineStr">
@@ -38540,17 +38540,17 @@
       </c>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>078d2fa6-e81c-41d1-95f2-04234d511192</t>
+          <t>1235147133</t>
         </is>
       </c>
       <c r="H574" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J574" s="2" t="n">
@@ -38558,12 +38558,12 @@
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr">
         <is>
-          <t>29201 Telegraph Rd, ste 403, Southfield, MI, 48034</t>
+          <t>17940 Farmington Rd Ste 130, Livonia, MI 48152</t>
         </is>
       </c>
       <c r="M574" s="3" t="n"/>
@@ -38585,12 +38585,12 @@
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>Franklin Medical Consultants</t>
+          <t>📝 Powers Family Medicine</t>
         </is>
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F575" s="2" t="inlineStr">
@@ -38600,30 +38600,30 @@
       </c>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>559bee40-1fa3-437d-9e4b-692838015293</t>
+          <t>00-761-7874</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I575" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J575" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K575" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L575" s="3" t="inlineStr">
         <is>
-          <t>29829 Telegraph Road, Southfield, MI 48034</t>
+          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
         </is>
       </c>
       <c r="M575" s="3" t="n"/>
@@ -38645,12 +38645,12 @@
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>MICHIGAN PREMIER INTERNISTS</t>
+          <t>📝 ORCHARD PRIMARY CARE</t>
         </is>
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F576" s="2" t="inlineStr">
@@ -38660,30 +38660,30 @@
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>1a1e59ec-5621-4caa-a9e9-b4d86b5218e7</t>
+          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J576" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr">
         <is>
-          <t>29877 Telegraph Rd Ste 200, Southfield, MI 48034</t>
+          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
         </is>
       </c>
       <c r="M576" s="3" t="n"/>
@@ -38705,12 +38705,12 @@
       </c>
       <c r="D577" s="3" t="inlineStr">
         <is>
-          <t>📝 1st Choice Urgent Care</t>
+          <t>📝 Henry Ford Go Health Urgent Care</t>
         </is>
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 25</t>
+          <t>Prospect · last check-in May 27</t>
         </is>
       </c>
       <c r="F577" s="2" t="inlineStr">
@@ -38720,7 +38720,7 @@
       </c>
       <c r="G577" s="2" t="inlineStr">
         <is>
-          <t>e7cc65bc-b486-4ee3-9c39-431666859cbd</t>
+          <t>14f29ff1-cd7e-4e90-b5c7-b1114551c5b9</t>
         </is>
       </c>
       <c r="H577" s="2" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="L577" s="3" t="inlineStr">
         <is>
-          <t>29628 Southfield Road, Southfield, Michigan, 48076</t>
+          <t>28670 Telegraph Road, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M577" s="3" t="n"/>
@@ -38765,12 +38765,12 @@
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>NORTHWAY MEDICAL CENTER</t>
+          <t>Franklin Medical Consultants</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 29</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F578" s="2" t="inlineStr">
@@ -38780,7 +38780,7 @@
       </c>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>dafed37b-6f1e-43be-91b6-aba048a40332</t>
+          <t>559bee40-1fa3-437d-9e4b-692838015293</t>
         </is>
       </c>
       <c r="H578" s="2" t="inlineStr">
@@ -38803,7 +38803,7 @@
       </c>
       <c r="L578" s="3" t="inlineStr">
         <is>
-          <t>17330 Northland Park Ct Ste 100, Southfield, MI 48075</t>
+          <t>29829 Telegraph Road, Southfield, MI 48034</t>
         </is>
       </c>
       <c r="M578" s="3" t="n"/>
@@ -38825,12 +38825,12 @@
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>📝 Ivy Rehab - Farmington</t>
+          <t>MICHIGAN PREMIER INTERNISTS</t>
         </is>
       </c>
       <c r="E579" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F579" s="2" t="inlineStr">
@@ -38840,17 +38840,17 @@
       </c>
       <c r="G579" s="2" t="inlineStr">
         <is>
-          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
+          <t>1a1e59ec-5621-4caa-a9e9-b4d86b5218e7</t>
         </is>
       </c>
       <c r="H579" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I579" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J579" s="2" t="n">
@@ -38858,12 +38858,12 @@
       </c>
       <c r="K579" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L579" s="3" t="inlineStr">
         <is>
-          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
+          <t>29877 Telegraph Rd Ste 200, Southfield, MI 48034</t>
         </is>
       </c>
       <c r="M579" s="3" t="n"/>
@@ -38885,12 +38885,12 @@
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
         </is>
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F580" s="2" t="inlineStr">
@@ -38900,12 +38900,12 @@
       </c>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
+          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
         </is>
       </c>
       <c r="H580" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I580" s="2" t="inlineStr">
@@ -38918,12 +38918,12 @@
       </c>
       <c r="K580" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr">
         <is>
-          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
+          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
         </is>
       </c>
       <c r="M580" s="3" t="n"/>
@@ -38945,12 +38945,12 @@
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>Middlebelt Medical Center</t>
+          <t>NORTHWAY MEDICAL CENTER</t>
         </is>
       </c>
       <c r="E581" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jun 29</t>
+          <t>Tier 1 producer · last check-in May 29</t>
         </is>
       </c>
       <c r="F581" s="2" t="inlineStr">
@@ -38960,7 +38960,7 @@
       </c>
       <c r="G581" s="2" t="inlineStr">
         <is>
-          <t>1235147133</t>
+          <t>dafed37b-6f1e-43be-91b6-aba048a40332</t>
         </is>
       </c>
       <c r="H581" s="2" t="inlineStr">
@@ -38978,12 +38978,12 @@
       </c>
       <c r="K581" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L581" s="3" t="inlineStr">
         <is>
-          <t>17940 Farmington Rd Ste 130, Livonia, MI 48152</t>
+          <t>17330 Northland Park Ct Ste 100, Southfield, MI 48075</t>
         </is>
       </c>
       <c r="M581" s="3" t="n"/>
@@ -39005,12 +39005,12 @@
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Primary Care Center - 160</t>
+          <t>White Lake Family Medicine</t>
         </is>
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Jul 21</t>
         </is>
       </c>
       <c r="F582" s="2" t="inlineStr">
@@ -39020,30 +39020,30 @@
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
+          <t>6f873c6d-498d-4d61-b717-d6648675da4e</t>
         </is>
       </c>
       <c r="H582" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J582" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K582" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>White Lake</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr">
         <is>
-          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
+          <t>9178 Highland Rd, White Lake, MI 483864619</t>
         </is>
       </c>
       <c r="M582" s="3" t="n"/>
@@ -39065,7 +39065,7 @@
       </c>
       <c r="D583" s="3" t="inlineStr">
         <is>
-          <t>📝 Levine Clinic of Chiropractic</t>
+          <t>📝 Henry Ford Primary Care Center - 160</t>
         </is>
       </c>
       <c r="E583" s="3" t="inlineStr">
@@ -39080,12 +39080,12 @@
       </c>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
+          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
         </is>
       </c>
       <c r="H583" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I583" s="2" t="inlineStr">
@@ -39094,7 +39094,7 @@
         </is>
       </c>
       <c r="J583" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
       </c>
       <c r="L583" s="3" t="inlineStr">
         <is>
-          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
+          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M583" s="3" t="n"/>
@@ -39125,12 +39125,12 @@
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Internal Medicine Southfield</t>
+          <t>📝 Levine Clinic of Chiropractic</t>
         </is>
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F584" s="2" t="inlineStr">
@@ -39140,12 +39140,12 @@
       </c>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
+          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I584" s="2" t="inlineStr">
@@ -39154,16 +39154,16 @@
         </is>
       </c>
       <c r="J584" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
+          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M584" s="3" t="n"/>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>📝 Jian Zu MD</t>
+          <t>📝 Corewell Internal Medicine Southfield</t>
         </is>
       </c>
       <c r="E585" s="3" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
+          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
         </is>
       </c>
       <c r="H585" s="2" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="L585" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
+          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M585" s="3" t="n"/>
@@ -39245,12 +39245,12 @@
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>📝 Legacy Family Care</t>
+          <t>📝 Triumph chiropractic</t>
         </is>
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
@@ -39260,12 +39260,12 @@
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
+          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
         </is>
       </c>
       <c r="H586" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I586" s="2" t="inlineStr">
@@ -39274,16 +39274,16 @@
         </is>
       </c>
       <c r="J586" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr">
         <is>
-          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
+          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M586" s="3" t="n"/>
@@ -39305,12 +39305,12 @@
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>📝 Triumph chiropractic</t>
+          <t>📝 Brentwood Pediatric Associates</t>
         </is>
       </c>
       <c r="E587" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F587" s="2" t="inlineStr">
@@ -39320,12 +39320,12 @@
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
+          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I587" s="2" t="inlineStr">
@@ -39334,7 +39334,7 @@
         </is>
       </c>
       <c r="J587" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
       </c>
       <c r="L587" s="3" t="inlineStr">
         <is>
-          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
+          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M587" s="3" t="n"/>
@@ -39365,12 +39365,12 @@
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>📝 Brentwood Pediatric Associates</t>
+          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F588" s="2" t="inlineStr">
@@ -39380,12 +39380,12 @@
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
+          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
         </is>
       </c>
       <c r="H588" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I588" s="2" t="inlineStr">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="L588" s="3" t="inlineStr">
         <is>
-          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
+          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
         </is>
       </c>
       <c r="M588" s="3" t="n"/>
@@ -39425,7 +39425,7 @@
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
+          <t>📝 Beaumont Medical Center - Redford</t>
         </is>
       </c>
       <c r="E589" s="3" t="inlineStr">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="G589" s="2" t="inlineStr">
         <is>
-          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
+          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
         </is>
       </c>
       <c r="H589" s="2" t="inlineStr">
@@ -39454,16 +39454,16 @@
         </is>
       </c>
       <c r="J589" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K589" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Redford Charter Township</t>
         </is>
       </c>
       <c r="L589" s="3" t="inlineStr">
         <is>
-          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
+          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
         </is>
       </c>
       <c r="M589" s="3" t="n"/>
@@ -39485,12 +39485,12 @@
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>📝 Greg Monroe DO PC</t>
+          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 1</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
+          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -39518,12 +39518,12 @@
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Westland</t>
+          <t>Redford</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr">
         <is>
-          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
+          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
         </is>
       </c>
       <c r="M590" s="3" t="n"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="D591" s="3" t="inlineStr">
         <is>
-          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
+          <t>📝 Greg Monroe DO PC</t>
         </is>
       </c>
       <c r="E591" s="3" t="inlineStr">
@@ -39560,7 +39560,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
+          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -39574,16 +39574,16 @@
         </is>
       </c>
       <c r="J591" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="L591" s="3" t="inlineStr">
         <is>
-          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
+          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
         </is>
       </c>
       <c r="M591" s="3" t="n"/>
@@ -40265,12 +40265,12 @@
       </c>
       <c r="D603" s="3" t="inlineStr">
         <is>
-          <t>Plymouth PT</t>
+          <t>LIVONIA MEDICAL CLINIC</t>
         </is>
       </c>
       <c r="E603" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 4</t>
+          <t>Tier 2 ortho · last check-in Jun 29</t>
         </is>
       </c>
       <c r="F603" s="2" t="inlineStr">
@@ -40280,12 +40280,12 @@
       </c>
       <c r="G603" s="2" t="inlineStr">
         <is>
-          <t>2c60eae5-2763-4890-8b2c-79d3e64f8375</t>
+          <t>591f9466-d788-4dd1-bb39-dcafc7382eba</t>
         </is>
       </c>
       <c r="H603" s="2" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I603" s="2" t="inlineStr">
@@ -40298,12 +40298,12 @@
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L603" s="3" t="inlineStr">
         <is>
-          <t>9368 North Lilley Road, Plymouth, MI 48170</t>
+          <t>32950 5 Mile Rd, Livonia, MI 48154</t>
         </is>
       </c>
       <c r="M603" s="3" t="n"/>
@@ -40325,27 +40325,27 @@
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>📝 Plymouth Urgent Care</t>
+          <t>📝 Hermann Banks MD PC</t>
         </is>
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Aug 27</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F604" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G604" s="2" t="inlineStr">
         <is>
-          <t>ea50a287-34fb-4325-8a2e-5ba156145624</t>
+          <t>31597599-5a74-4f7a-8cb0-0ebbb4b41303</t>
         </is>
       </c>
       <c r="H604" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="I604" s="2" t="inlineStr">
@@ -40354,16 +40354,16 @@
         </is>
       </c>
       <c r="J604" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr">
         <is>
-          <t>41424 Ann Arbor Rd, Plymouth, Michigan, 48170</t>
+          <t>14700 Farmington Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M604" s="3" t="n"/>
@@ -40385,22 +40385,22 @@
       </c>
       <c r="D605" s="3" t="inlineStr">
         <is>
-          <t>ADULT MEDICAL CARE, PLLC</t>
+          <t>Imad George MD P.C. MHP</t>
         </is>
       </c>
       <c r="E605" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 5</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F605" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G605" s="2" t="inlineStr">
         <is>
-          <t>577210d0-6649-4e69-ad97-285f00706766</t>
+          <t>24a73c28-f1ec-4808-8b5a-4d6702f86f8a</t>
         </is>
       </c>
       <c r="H605" s="2" t="inlineStr">
@@ -40414,16 +40414,16 @@
         </is>
       </c>
       <c r="J605" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
-          <t>Westland</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L605" s="3" t="inlineStr">
         <is>
-          <t>35330 Nankin Blvd Ste 701, Westland, MI 48185</t>
+          <t>28000 Joy Road, Livonia, MI 48150</t>
         </is>
       </c>
       <c r="M605" s="3" t="n"/>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>📝 Hermann Banks MD PC</t>
+          <t>Corewell Internal Medicine - Family Practice DEARBORN HEIGHTS</t>
         </is>
       </c>
       <c r="E606" s="3" t="inlineStr">
@@ -40460,30 +40460,30 @@
       </c>
       <c r="G606" s="2" t="inlineStr">
         <is>
-          <t>31597599-5a74-4f7a-8cb0-0ebbb4b41303</t>
+          <t>88431ac1-44b1-4daf-a322-1fb70f0223f1</t>
         </is>
       </c>
       <c r="H606" s="2" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I606" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J606" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr">
         <is>
-          <t>14700 Farmington Rd, Livonia, Michigan, 48154</t>
+          <t>27031 W Warren St, Dearborn Heights, MI 48127</t>
         </is>
       </c>
       <c r="M606" s="3" t="n"/>
@@ -40505,45 +40505,45 @@
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
-          <t>LIVONIA MEDICAL CLINIC</t>
+          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E607" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 29</t>
+          <t>Tier 1 producer · last check-in Sep 1</t>
         </is>
       </c>
       <c r="F607" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G607" s="2" t="inlineStr">
         <is>
-          <t>591f9466-d788-4dd1-bb39-dcafc7382eba</t>
+          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
         </is>
       </c>
       <c r="H607" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I607" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J607" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K607" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L607" s="3" t="inlineStr">
         <is>
-          <t>32950 5 Mile Rd, Livonia, MI 48154</t>
+          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M607" s="3" t="n"/>
@@ -40565,45 +40565,45 @@
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>📝 Beaumont Medical Center - Redford</t>
+          <t>ADULT MEDICAL CARE, PLLC</t>
         </is>
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 2 ortho · last check-in Jun 5</t>
         </is>
       </c>
       <c r="F608" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G608" s="2" t="inlineStr">
         <is>
-          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
+          <t>577210d0-6649-4e69-ad97-285f00706766</t>
         </is>
       </c>
       <c r="H608" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I608" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J608" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K608" s="2" t="inlineStr">
         <is>
-          <t>Redford Charter Township</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr">
         <is>
-          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
+          <t>35330 Nankin Blvd Ste 701, Westland, MI 48185</t>
         </is>
       </c>
       <c r="M608" s="3" t="n"/>
@@ -40625,22 +40625,22 @@
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
+          <t>📝 PRAVEEN MODI, MD, PC</t>
         </is>
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 2 ortho · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F609" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G609" s="2" t="inlineStr">
         <is>
-          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
+          <t>63a72095-741a-43fe-b865-a1f6398ee484</t>
         </is>
       </c>
       <c r="H609" s="2" t="inlineStr">
@@ -40654,16 +40654,16 @@
         </is>
       </c>
       <c r="J609" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K609" s="2" t="inlineStr">
         <is>
-          <t>Redford</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="L609" s="3" t="inlineStr">
         <is>
-          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
+          <t>9857 N HAGGERTY RD, PLYMOUTH, Michigan, MI 48170</t>
         </is>
       </c>
       <c r="M609" s="3" t="n"/>
@@ -40685,45 +40685,45 @@
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>Corewell Internal Medicine - Family Practice DEARBORN HEIGHTS</t>
+          <t>📝 Plymouth Urgent Care</t>
         </is>
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 2 ortho · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F610" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G610" s="2" t="inlineStr">
         <is>
-          <t>88431ac1-44b1-4daf-a322-1fb70f0223f1</t>
+          <t>ea50a287-34fb-4325-8a2e-5ba156145624</t>
         </is>
       </c>
       <c r="H610" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I610" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J610" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr">
         <is>
-          <t>27031 W Warren St, Dearborn Heights, MI 48127</t>
+          <t>41424 Ann Arbor Rd, Plymouth, Michigan, 48170</t>
         </is>
       </c>
       <c r="M610" s="3" t="n"/>
@@ -40745,27 +40745,27 @@
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>Imad George MD P.C. MHP</t>
+          <t>Plymouth PT</t>
         </is>
       </c>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 2 ortho · last check-in Jun 4</t>
         </is>
       </c>
       <c r="F611" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G611" s="2" t="inlineStr">
         <is>
-          <t>24a73c28-f1ec-4808-8b5a-4d6702f86f8a</t>
+          <t>2c60eae5-2763-4890-8b2c-79d3e64f8375</t>
         </is>
       </c>
       <c r="H611" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
       <c r="I611" s="2" t="inlineStr">
@@ -40774,16 +40774,16 @@
         </is>
       </c>
       <c r="J611" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K611" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="L611" s="3" t="inlineStr">
         <is>
-          <t>28000 Joy Road, Livonia, MI 48150</t>
+          <t>9368 North Lilley Road, Plymouth, MI 48170</t>
         </is>
       </c>
       <c r="M611" s="3" t="n"/>
@@ -41945,45 +41945,45 @@
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>📝 Universal Clinic &amp; Urgent Care</t>
+          <t>Office of Lillman Dwarka MD</t>
         </is>
       </c>
       <c r="E631" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Sep 2</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F631" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G631" s="2" t="inlineStr">
         <is>
-          <t>d689dac9-8b56-4f6e-9ba4-8bf3eb8e3550</t>
+          <t>144c374c-b718-48c1-9b9f-daffbf7ba530</t>
         </is>
       </c>
       <c r="H631" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I631" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J631" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K631" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L631" s="3" t="inlineStr">
         <is>
-          <t>4600 14 Mile Rd ste 1, Warren, Michigan, 48092</t>
+          <t>38300 Van Dyke Ave, Ste 105, Sterling Heights, MI 48312</t>
         </is>
       </c>
       <c r="M631" s="3" t="n"/>
@@ -42005,27 +42005,27 @@
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Warren Family Physicians</t>
+          <t>📝 Universal Clinic &amp; Urgent Care</t>
         </is>
       </c>
       <c r="E632" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Prospect · last check-in Sep 2</t>
         </is>
       </c>
       <c r="F632" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G632" s="2" t="inlineStr">
         <is>
-          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
+          <t>d689dac9-8b56-4f6e-9ba4-8bf3eb8e3550</t>
         </is>
       </c>
       <c r="H632" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I632" s="2" t="inlineStr">
@@ -42034,7 +42034,7 @@
         </is>
       </c>
       <c r="J632" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K632" s="2" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
       </c>
       <c r="L632" s="3" t="inlineStr">
         <is>
-          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
+          <t>4600 14 Mile Rd ste 1, Warren, Michigan, 48092</t>
         </is>
       </c>
       <c r="M632" s="3" t="n"/>
@@ -42065,12 +42065,12 @@
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
+          <t>📝 Henry Ford Warren Family Physicians</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 27</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F633" s="2" t="inlineStr">
@@ -42080,7 +42080,7 @@
       </c>
       <c r="G633" s="2" t="inlineStr">
         <is>
-          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
+          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
         </is>
       </c>
       <c r="H633" s="2" t="inlineStr">
@@ -42103,7 +42103,7 @@
       </c>
       <c r="L633" s="3" t="inlineStr">
         <is>
-          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
+          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
         </is>
       </c>
       <c r="M633" s="3" t="n"/>
@@ -42125,12 +42125,12 @@
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>📝 Northpointe Pediatrics</t>
+          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
         </is>
       </c>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F634" s="2" t="inlineStr">
@@ -42140,12 +42140,12 @@
       </c>
       <c r="G634" s="2" t="inlineStr">
         <is>
-          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
+          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
         </is>
       </c>
       <c r="H634" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I634" s="2" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="L634" s="3" t="inlineStr">
         <is>
-          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
+          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
         </is>
       </c>
       <c r="M634" s="3" t="n"/>
@@ -42185,12 +42185,12 @@
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>📝 Legacy Family Medicine</t>
+          <t>📝 Northpointe Pediatrics</t>
         </is>
       </c>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F635" s="2" t="inlineStr">
@@ -42200,12 +42200,12 @@
       </c>
       <c r="G635" s="2" t="inlineStr">
         <is>
-          <t>1558340356</t>
+          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
         </is>
       </c>
       <c r="H635" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I635" s="2" t="inlineStr">
@@ -42218,12 +42218,12 @@
       </c>
       <c r="K635" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L635" s="3" t="inlineStr">
         <is>
-          <t>35429 Schoenherr Rd, Sterling Heights, MI, 48312</t>
+          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
         </is>
       </c>
       <c r="M635" s="3" t="n"/>
@@ -42545,12 +42545,12 @@
       </c>
       <c r="D641" s="3" t="inlineStr">
         <is>
-          <t>📝 Brigid Healthcare</t>
+          <t>📝 Team Rehabilitation  - Washington</t>
         </is>
       </c>
       <c r="E641" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 14</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F641" s="2" t="inlineStr">
@@ -42560,12 +42560,12 @@
       </c>
       <c r="G641" s="2" t="inlineStr">
         <is>
-          <t>63bf16ad-3645-45fb-8f1d-e1eb3a131efc</t>
+          <t>940f0098-7ee4-47be-9425-5cd4bbc4dd0f</t>
         </is>
       </c>
       <c r="H641" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I641" s="2" t="inlineStr">
@@ -42574,16 +42574,16 @@
         </is>
       </c>
       <c r="J641" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K641" s="2" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="L641" s="3" t="inlineStr">
         <is>
-          <t>3456 Rochester Rd, Troy, Michigan, 48083</t>
+          <t>64541 Van Dyke, Washington, Michigan, 48095</t>
         </is>
       </c>
       <c r="M641" s="3" t="n"/>
@@ -42605,12 +42605,12 @@
       </c>
       <c r="D642" s="3" t="inlineStr">
         <is>
-          <t>Grace Medical of Troy</t>
+          <t>Professional Village Medical Center</t>
         </is>
       </c>
       <c r="E642" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F642" s="2" t="inlineStr">
@@ -42620,7 +42620,7 @@
       </c>
       <c r="G642" s="2" t="inlineStr">
         <is>
-          <t>1639490493</t>
+          <t>1427031756</t>
         </is>
       </c>
       <c r="H642" s="2" t="inlineStr">
@@ -42634,16 +42634,16 @@
         </is>
       </c>
       <c r="J642" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K642" s="2" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr">
         <is>
-          <t>3940 John R Road, Troy, MI 48083</t>
+          <t>13700 19 Mile Rd, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M642" s="3" t="n"/>
@@ -42665,12 +42665,12 @@
       </c>
       <c r="D643" s="3" t="inlineStr">
         <is>
-          <t>📝 Metro Medical Practice</t>
+          <t>Lakewood Primary Care</t>
         </is>
       </c>
       <c r="E643" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 14</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F643" s="2" t="inlineStr">
@@ -42680,17 +42680,17 @@
       </c>
       <c r="G643" s="2" t="inlineStr">
         <is>
-          <t>60-080-4525</t>
+          <t>39254718-ba1d-4862-adfb-cd292a8eda27</t>
         </is>
       </c>
       <c r="H643" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I643" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J643" s="2" t="n">
@@ -42698,12 +42698,12 @@
       </c>
       <c r="K643" s="2" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L643" s="3" t="inlineStr">
         <is>
-          <t>2891 E Maple Rd Ste 102, Troy, MI, 48083</t>
+          <t>13425 19 Mile Rd Ste 100, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M643" s="3" t="n"/>
@@ -42725,12 +42725,12 @@
       </c>
       <c r="D644" s="3" t="inlineStr">
         <is>
-          <t>📝 Oakland Family Practice</t>
+          <t>📝 MNP</t>
         </is>
       </c>
       <c r="E644" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F644" s="2" t="inlineStr">
@@ -42740,7 +42740,7 @@
       </c>
       <c r="G644" s="2" t="inlineStr">
         <is>
-          <t>13ba57d5-6bc6-4d44-8d40-efd8e7131d2e</t>
+          <t>40477f1c-8f50-4f86-8e7e-a5431b7f2fe6</t>
         </is>
       </c>
       <c r="H644" s="2" t="inlineStr">
@@ -42758,12 +42758,12 @@
       </c>
       <c r="K644" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Utica</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr">
         <is>
-          <t>27650 Dequindre Road, Suite 2000, Warren, Michigan, 48092</t>
+          <t>44225 Utica Road, Utica, Michigan, 48317</t>
         </is>
       </c>
       <c r="M644" s="3" t="n"/>
@@ -42785,12 +42785,12 @@
       </c>
       <c r="D645" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Health-East</t>
+          <t>📝 Associates in Family Practice</t>
         </is>
       </c>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F645" s="2" t="inlineStr">
@@ -42800,7 +42800,7 @@
       </c>
       <c r="G645" s="2" t="inlineStr">
         <is>
-          <t>04ad9387-b1fe-45cd-bd14-73188de8e04a</t>
+          <t>1205856432</t>
         </is>
       </c>
       <c r="H645" s="2" t="inlineStr">
@@ -42818,12 +42818,12 @@
       </c>
       <c r="K645" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L645" s="3" t="inlineStr">
         <is>
-          <t>29245 Ryan Rd suite 300, Warren, Michigan, 48092</t>
+          <t>42755 Mound Rd, Sterling Heights, Michigan, 48314</t>
         </is>
       </c>
       <c r="M645" s="3" t="n"/>
@@ -42845,45 +42845,45 @@
       </c>
       <c r="D646" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Medical Center - Warren</t>
+          <t>Grace Medical of Troy</t>
         </is>
       </c>
       <c r="E646" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 26</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F646" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>1932273448</t>
+          <t>1639490493</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I646" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J646" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K646" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr">
         <is>
-          <t>8600 Chicago Road St, Warren, MI, 48093</t>
+          <t>3940 John R Road, Troy, MI 48083</t>
         </is>
       </c>
       <c r="M646" s="3" t="n"/>
@@ -42905,12 +42905,12 @@
       </c>
       <c r="D647" s="3" t="inlineStr">
         <is>
-          <t>Office of Lillman Dwarka MD</t>
+          <t>📝 Metro Medical Practice</t>
         </is>
       </c>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Sep 14</t>
         </is>
       </c>
       <c r="F647" s="2" t="inlineStr">
@@ -42920,30 +42920,30 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>144c374c-b718-48c1-9b9f-daffbf7ba530</t>
+          <t>60-080-4525</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I647" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J647" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K647" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L647" s="3" t="inlineStr">
         <is>
-          <t>38300 Van Dyke Ave, Ste 105, Sterling Heights, MI 48312</t>
+          <t>2891 E Maple Rd Ste 102, Troy, MI, 48083</t>
         </is>
       </c>
       <c r="M647" s="3" t="n"/>
@@ -42965,12 +42965,12 @@
       </c>
       <c r="D648" s="3" t="inlineStr">
         <is>
-          <t>📝 Associates in Family Practice</t>
+          <t>Mercy Family Care Center</t>
         </is>
       </c>
       <c r="E648" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F648" s="2" t="inlineStr">
@@ -42980,17 +42980,17 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>1205856432</t>
+          <t>3dfcef6a-be30-4421-b9ae-e70c90558ff6</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I648" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J648" s="2" t="n">
@@ -43003,7 +43003,7 @@
       </c>
       <c r="L648" s="3" t="inlineStr">
         <is>
-          <t>42755 Mound Rd, Sterling Heights, Michigan, 48314</t>
+          <t>2107 East 14 Mile Road, Sterling Heights, MI 48310</t>
         </is>
       </c>
       <c r="M648" s="3" t="n"/>
@@ -43025,12 +43025,12 @@
       </c>
       <c r="D649" s="3" t="inlineStr">
         <is>
-          <t>📝 MNP</t>
+          <t>📝 Corewell Health-East</t>
         </is>
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F649" s="2" t="inlineStr">
@@ -43040,7 +43040,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>40477f1c-8f50-4f86-8e7e-a5431b7f2fe6</t>
+          <t>04ad9387-b1fe-45cd-bd14-73188de8e04a</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -43054,16 +43054,16 @@
         </is>
       </c>
       <c r="J649" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K649" s="2" t="inlineStr">
         <is>
-          <t>Utica</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L649" s="3" t="inlineStr">
         <is>
-          <t>44225 Utica Road, Utica, Michigan, 48317</t>
+          <t>29245 Ryan Rd suite 300, Warren, Michigan, 48092</t>
         </is>
       </c>
       <c r="M649" s="3" t="n"/>
@@ -43085,12 +43085,12 @@
       </c>
       <c r="D650" s="3" t="inlineStr">
         <is>
-          <t>Lakewood Primary Care</t>
+          <t>📝 Oakland Family Practice</t>
         </is>
       </c>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F650" s="2" t="inlineStr">
@@ -43100,17 +43100,17 @@
       </c>
       <c r="G650" s="2" t="inlineStr">
         <is>
-          <t>39254718-ba1d-4862-adfb-cd292a8eda27</t>
+          <t>13ba57d5-6bc6-4d44-8d40-efd8e7131d2e</t>
         </is>
       </c>
       <c r="H650" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I650" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J650" s="2" t="n">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="K650" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr">
         <is>
-          <t>13425 19 Mile Rd Ste 100, Sterling Heights, MI 48313</t>
+          <t>27650 Dequindre Road, Suite 2000, Warren, Michigan, 48092</t>
         </is>
       </c>
       <c r="M650" s="3" t="n"/>
@@ -43145,12 +43145,12 @@
       </c>
       <c r="D651" s="3" t="inlineStr">
         <is>
-          <t>📝 Center For Hollistic Medicine</t>
+          <t>Core Med  - White Lake</t>
         </is>
       </c>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Jul 21</t>
         </is>
       </c>
       <c r="F651" s="2" t="inlineStr">
@@ -43160,17 +43160,17 @@
       </c>
       <c r="G651" s="2" t="inlineStr">
         <is>
-          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
+          <t>ecbe00dd-1c49-4028-a575-d8852e23deba</t>
         </is>
       </c>
       <c r="H651" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I651" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J651" s="2" t="n">
@@ -43178,12 +43178,12 @@
       </c>
       <c r="K651" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>White Lake Charter Township</t>
         </is>
       </c>
       <c r="L651" s="3" t="inlineStr">
         <is>
-          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
+          <t>8355 Highland Road, White Lake Charter Township, MI 48386</t>
         </is>
       </c>
       <c r="M651" s="3" t="n"/>
@@ -43265,12 +43265,12 @@
       </c>
       <c r="D653" s="3" t="inlineStr">
         <is>
-          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
+          <t>📝 Legacy Family Care</t>
         </is>
       </c>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F653" s="2" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
+          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">
@@ -43298,12 +43298,12 @@
       </c>
       <c r="K653" s="2" t="inlineStr">
         <is>
-          <t>Bloomfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L653" s="3" t="inlineStr">
         <is>
-          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
+          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
         </is>
       </c>
       <c r="M653" s="3" t="n"/>
@@ -43325,12 +43325,12 @@
       </c>
       <c r="D654" s="3" t="inlineStr">
         <is>
-          <t>📝 MedPro Primary Care</t>
+          <t>📝 Jian Zu MD</t>
         </is>
       </c>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F654" s="2" t="inlineStr">
@@ -43340,12 +43340,12 @@
       </c>
       <c r="G654" s="2" t="inlineStr">
         <is>
-          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
+          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
         </is>
       </c>
       <c r="H654" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I654" s="2" t="inlineStr">
@@ -43354,16 +43354,16 @@
         </is>
       </c>
       <c r="J654" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K654" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr">
         <is>
-          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
+          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M654" s="3" t="n"/>
@@ -43385,12 +43385,12 @@
       </c>
       <c r="D655" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care Madison Heights</t>
+          <t>📝 Carson Center Specialty</t>
         </is>
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 25</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F655" s="2" t="inlineStr">
@@ -43400,12 +43400,12 @@
       </c>
       <c r="G655" s="2" t="inlineStr">
         <is>
-          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
+          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
         </is>
       </c>
       <c r="H655" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I655" s="2" t="inlineStr">
@@ -43418,12 +43418,12 @@
       </c>
       <c r="K655" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L655" s="3" t="inlineStr">
         <is>
-          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
+          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
         </is>
       </c>
       <c r="M655" s="3" t="n"/>
@@ -43445,7 +43445,7 @@
       </c>
       <c r="D656" s="3" t="inlineStr">
         <is>
-          <t>📝 Berkley Urgent Care</t>
+          <t>📝 ROSE MEDICINE</t>
         </is>
       </c>
       <c r="E656" s="3" t="inlineStr">
@@ -43460,12 +43460,12 @@
       </c>
       <c r="G656" s="2" t="inlineStr">
         <is>
-          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
+          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
         </is>
       </c>
       <c r="H656" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I656" s="2" t="inlineStr">
@@ -43478,12 +43478,12 @@
       </c>
       <c r="K656" s="2" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Bingham Farms</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr">
         <is>
-          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
+          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
         </is>
       </c>
       <c r="M656" s="3" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="D657" s="3" t="inlineStr">
         <is>
-          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>📝 Berkley Urgent Care</t>
         </is>
       </c>
       <c r="E657" s="3" t="inlineStr">
@@ -43520,7 +43520,7 @@
       </c>
       <c r="G657" s="2" t="inlineStr">
         <is>
-          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
+          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
         </is>
       </c>
       <c r="H657" s="2" t="inlineStr">
@@ -43538,12 +43538,12 @@
       </c>
       <c r="K657" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="L657" s="3" t="inlineStr">
         <is>
-          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
+          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
         </is>
       </c>
       <c r="M657" s="3" t="n"/>
@@ -43565,12 +43565,12 @@
       </c>
       <c r="D658" s="3" t="inlineStr">
         <is>
-          <t>📝 ROSE MEDICINE</t>
+          <t>📝 MedPro Primary Care</t>
         </is>
       </c>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F658" s="2" t="inlineStr">
@@ -43580,12 +43580,12 @@
       </c>
       <c r="G658" s="2" t="inlineStr">
         <is>
-          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
+          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
         </is>
       </c>
       <c r="H658" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I658" s="2" t="inlineStr">
@@ -43594,16 +43594,16 @@
         </is>
       </c>
       <c r="J658" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K658" s="2" t="inlineStr">
         <is>
-          <t>Bingham Farms</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr">
         <is>
-          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
+          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M658" s="3" t="n"/>
@@ -43625,12 +43625,12 @@
       </c>
       <c r="D659" s="3" t="inlineStr">
         <is>
-          <t>📝 Village Medical Farmington</t>
+          <t>📝 Brigid Healthcare</t>
         </is>
       </c>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Sep 14</t>
         </is>
       </c>
       <c r="F659" s="2" t="inlineStr">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="G659" s="2" t="inlineStr">
         <is>
-          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
+          <t>63bf16ad-3645-45fb-8f1d-e1eb3a131efc</t>
         </is>
       </c>
       <c r="H659" s="2" t="inlineStr">
@@ -43658,12 +43658,12 @@
       </c>
       <c r="K659" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L659" s="3" t="inlineStr">
         <is>
-          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
+          <t>3456 Rochester Rd, Troy, Michigan, 48083</t>
         </is>
       </c>
       <c r="M659" s="3" t="n"/>
@@ -43685,22 +43685,22 @@
       </c>
       <c r="D660" s="3" t="inlineStr">
         <is>
-          <t>📝 BETTER HEALTH CLINIC</t>
+          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Sep 1</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>1e77e934-4008-4672-ac72-64c80d79458e</t>
+          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
         </is>
       </c>
       <c r="H660" s="2" t="inlineStr">
@@ -43714,16 +43714,16 @@
         </is>
       </c>
       <c r="J660" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K660" s="2" t="inlineStr">
         <is>
-          <t>Westland</t>
+          <t>Bloomfield</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr">
         <is>
-          <t>8275 N WAYNE RD, WESTLAND, Michigan, 48185</t>
+          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
         </is>
       </c>
       <c r="M660" s="3" t="n"/>
@@ -66295,16 +66295,16 @@
         <v>50</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -66345,7 +66345,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>14</v>
@@ -66354,7 +66354,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -66370,7 +66370,7 @@
         <v>50</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>6</v>
@@ -66379,7 +66379,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -66395,10 +66395,10 @@
         <v>50</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>0</v>
@@ -66420,7 +66420,7 @@
         <v>49</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>12</v>
@@ -66429,7 +66429,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -2466,13 +2466,13 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Commerce Township (4) • West Bloomfield (4)</t>
+          <t>Commerce Township (4) • West Bloomfield (3)</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322</t>
         </is>
       </c>
     </row>
@@ -2595,13 +2595,13 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Northville (2) • Livonia (2)</t>
+          <t>Northville (2) • South Lyon (1)</t>
         </is>
       </c>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2900%20Packard%20Street%2C%20Ypsilanti%2C%20Michigan%2C%2048197&amp;waypoints=23200%20Pontiac%20Trail%2C%20South%20Lyon%2C%20MI%2048178%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C19000%20St%20Joe%27s%20Pkwy%20suite%20200%2C%20Livonia%2C%20Michigan%2C%2048152%7C38253%20Ann%20Arbor%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185%7C5624%20Research%20Drive%2C%20Canton%2C%20Michigan%2C%2048188</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2900%20Packard%20Street%2C%20Ypsilanti%2C%20Michigan%2C%2048197&amp;waypoints=23200%20Pontiac%20Trail%2C%20South%20Lyon%2C%20MI%2048178%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185%7C38253%20Ann%20Arbor%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C5624%20Research%20Drive%2C%20Canton%2C%20Michigan%2C%2048188</t>
         </is>
       </c>
     </row>
@@ -2814,13 +2814,13 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Livonia (6) • Farmington (1)</t>
+          <t>Livonia (7) • Redford (1)</t>
         </is>
       </c>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076&amp;waypoints=37508%20W%20SEVEN%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%7C17800%20Newburgh%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025&amp;waypoints=19000%20St%20Joe%27s%20Pkwy%20suite%20200%2C%20Livonia%2C%20Michigan%2C%2048152%7C17800%20Newburgh%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C37508%20W%20SEVEN%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>5</v>
@@ -2943,17 +2943,17 @@
         <v>3</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Shelby Township (3) • Clinton Township (3)</t>
+          <t>Clinton Township (3) • Shelby Township (3)</t>
         </is>
       </c>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=36750%2026%20Mile%20Rd%2C%20ste%20140%2C%20New%20Baltimore%2C%20Michigan%2C%2048047&amp;waypoints=79720%20Kidder%20Rd%20Bruce%20Township%2C%20Michigan%2C%2048065%7C57850%20Van%20Dyke%20Ave%20ste%20600%2C%20Washington%2C%20Michigan%2C%2048094%7C50720%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C15125%2022%20Mile%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C45640%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20Michigan%2C%2048315%7C41060%20Hayes%20Road%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C43555%20Dalcoma%20Dr%20suite%204%20Clinton%20Twp%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C36267%2026%20Mile%20Road%2C%20Suite%203%2C%20Lenox%2C%20MI%2C%2048048</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=36750%2026%20Mile%20Rd%2C%20ste%20140%2C%20New%20Baltimore%2C%20Michigan%2C%2048047&amp;waypoints=57850%20Van%20Dyke%20Ave%20ste%20600%2C%20Washington%2C%20Michigan%2C%2048094%7C115%20E%20Long%20Lake%20Rd%2C%20Troy%2C%20MI%2048085%7C41060%20Hayes%20Road%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C43555%20Dalcoma%20Dr%20suite%204%20Clinton%20Twp%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C45640%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20Michigan%2C%2048315%7C50720%20Schoenherr%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C15125%2022%20Mile%20Rd%2C%20Shelby%20Township%2C%20MI%2048315%7C36267%2026%20Mile%20Road%2C%20Suite%203%2C%20Lenox%2C%20MI%2C%2048048</t>
         </is>
       </c>
     </row>
@@ -2990,13 +2990,13 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Southfield (3) • Farmington Hills (2)</t>
+          <t>Southfield (3) • West Bloomfield (2)</t>
         </is>
       </c>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2940%20Crooks%20Rd%2C%20Rochester%20Hills%2C%20Michigan%2C%2048309&amp;waypoints=5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2940%20Crooks%20Rd%2C%20Rochester%20Hills%2C%20Michigan%2C%2048309&amp;waypoints=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22318%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127&amp;waypoints=6543%20TELEGRAPH%20RD%2C%20BLOOMFIELD%20TOWNSHIP%2C%20Michigan%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C36600%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22318%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127&amp;waypoints=2630%20UNION%20LAKE%20RD%20STE%20100%2C%20COMMERCE%20TOWNSHIP%2C%20Michigan%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336%7C22821%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%2C%20MI%2C%2048336%7C14700%20Farmington%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C36600%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C30900%20FORD%20RD%20STE%20B%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C28000%20Joy%20Road%2C%20Livonia%2C%20MI%2048150%7C27031%20W%20Warren%20St%2C%20Dearborn%20Heights%2C%20MI%2048127</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3072,17 +3072,17 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Commerce Township (5) • Novi (1)</t>
+          <t>Commerce Township (4) • White Lake (1)</t>
         </is>
       </c>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2157%20ORCHARD%20LAKE%20RD%2C%20SYLVAN%20LAKE%2C%20Michigan&amp;waypoints=1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C26850%20PROVIDENCE%20PKWY%20STE%20455%2C%20NOVI%2C%20Michigan%7C100%20N%20POND%20DR%20STE%20C%2C%20WALLED%20LAKE%2C%20MI%2C%2048390%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2685%20Union%20Lake%20Rd%20Commerce%20Charter%20Twp%2C%20Commerce%20Charter%20Township%2C%20Michigan%2C%2048382%7C2630%20UNION%20LAKE%20RD%20STE%20100%2C%20COMMERCE%20TOWNSHIP%2C%20Michigan%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=29877%20Telegraph%20Rd%20Ste%20200%2C%20Southfield%2C%20MI%2048034&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C1965%20Union%20Lake%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C2600%20Union%20Lake%20Rd%20suite%20140%20Commerce%20Township%2C%20Michigan%2C%2048382%7C2685%20Union%20Lake%20Rd%20Commerce%20Charter%20Twp%2C%20Commerce%20Charter%20Township%2C%20Michigan%2C%2048382%7C8800%20Commerce%20Rd%2C%20Commerce%20Township%2C%20MI%2048382%7C1%20William%20Carls%20Drive%2C%20Michigan%2C%2048382%7C26850%20PROVIDENCE%20PKWY%20STE%20455%2C%20NOVI%2C%20Michigan%7C100%20N%20POND%20DR%20STE%20C%2C%20WALLED%20LAKE%2C%20MI%2C%2048390%7C2300%20Haggerty%20Rd%20Ste%202150%2C%20West%20Bloomfield%2C%20MI%2048323</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>0</v>
@@ -3115,17 +3115,17 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Warren (5) • Sterling Heights (2)</t>
+          <t>Warren (6) • Southfield (2)</t>
         </is>
       </c>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=22250%20PROVIDENCE%20DR%20STE%20500%2C%20SOUTHFIELD%2C%20Michigan&amp;waypoints=115%20E%20Long%20Lake%20Rd%2C%20Troy%2C%20MI%2048085%7C35200%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C34764%20Dequindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2048310%7C11885%20E%2012%20Mile%20Rd%20Ste%20200B%2C%20Warren%2C%20MI%2048093%7C28401%20Hoover%2C%20Warren%2C%20Michigan%2C%2048093%7C28111%20HOOVER%20RD%20STE%201A%2C%20WARREN%2C%20Michigan%7C28111%20Hoover%20Rd%2C%20Ste%205A%20Warren%2C%20Mi%2048093%2C%20Usa%2C%20Warren%2C%20MI%2048093%7C27427%20Schoenherr%20Rd%2C%20Warren%2C%20MI%2048088%7C20599%20Mack%20Ave%2C%20Grosse%20Pointe%20Woods%2C%20MI%2048236</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27472%20Schoenherr%20Rd%20%23100%2C%20Warren%2C%20MI%2C%2048088&amp;waypoints=29829%20Telegraph%20Road%2C%20Southfield%2C%20MI%2048034%7C22250%20PROVIDENCE%20DR%20STE%20500%2C%20SOUTHFIELD%2C%20Michigan%7C34764%20Dequindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2048310%7C35200%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C11885%20E%2012%20Mile%20Rd%20Ste%20200B%2C%20Warren%2C%20MI%2048093%7C28401%20Hoover%2C%20Warren%2C%20Michigan%2C%2048093%7C28111%20HOOVER%20RD%20STE%201A%2C%20WARREN%2C%20Michigan%7C28111%20Hoover%20Rd%2C%20Ste%205A%20Warren%2C%20Mi%2048093%2C%20Usa%2C%20Warren%2C%20MI%2048093%7C27427%20Schoenherr%20Rd%2C%20Warren%2C%20MI%2048088</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230&amp;waypoints=13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080%7C20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066%7C27472%20Schoenherr%20Rd%20%23100%2C%20Warren%2C%20MI%2C%2048088%7C21647%20Ryan%20Rd%2C%20Warren%2C%20MI%2C%2048091%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15050%20E%20Jefferson%20Ave%20suite%20101%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048230&amp;waypoints=13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C24725%20E%20Jefferson%2C%20Saint%20Clair%20Shores%2C%20MI%2C%2048080%7C20952%20Twelve%20Mile%20Rd%20ste%20101%2C%20St.%20Clair%20Shores%2C%20Michigan%2C%2048081%7C27850%20Gratiot%20Avenue%2C%20Roseville%2C%20Michigan%2C%2048066%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088%7C21647%20Ryan%20Rd%2C%20Warren%2C%20MI%2C%2048091%7C19251%20Mack%20Ave%20%23333%2C%20Grosse%20Pointe%2C%20Michigan%2C%2048236</t>
         </is>
       </c>
     </row>
@@ -3205,13 +3205,13 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Farmington Hills (4) • West Bloomfield (3)</t>
+          <t>Farmington Hills (5) • West Bloomfield (2)</t>
         </is>
       </c>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167&amp;waypoints=6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C29201%20Telegraph%20Rd%2C%20ste%20403%2C%20Southfield%2C%20MI%2C%2048034%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=308%20S%20Main%20St%2C%20Northville%2C%20Michigan%2C%2048167&amp;waypoints=6525%20W%20MAPLE%20RD%20STE%20101E%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6530%20FARMINGTON%20RD%20STE%20LL-02%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C32910%20West%2013%20Mile%20Road%2C%20A101%2C%20Farmington%20Hills%2C%20MI%2048334%7C27970%20ORCHARD%20LAKE%20RD%2C%20FARMINGTON%20HILLS%2C%20Michigan%2C%2048334%7C29930%20W%2012%20MILE%20RD%20STE%206%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C29201%20Telegraph%20Rd%2C%20ste%20403%2C%20Southfield%2C%20MI%2C%2048034%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C38215%20W%2010%20MILE%20RD%20STE%208%2C%20FARMINGTON%20HILLS%2C%20Michigan%7C422%20N%20Center%20St%2C%20Northville%2C%20Michigan%2C%2048167</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=26393%20Dequindre%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071&amp;waypoints=44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan%7C41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C28324%20Dequindre%20Road%2C%20Warren%2C%20Michigan%2C%2048092</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=39333%20Van%20Dyke%20Ave%2C%20Sterling%20Heights%2C%20Mi%2048313%2C%20United%20States%2C%20Sterling%20Heights%2C%20MI%2048313&amp;waypoints=29628%20Southfield%20Road%2C%20Southfield%2C%20Michigan%2C%2048076%7C26393%20Dequindre%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C350%20E%2012%20Mile%20Rd%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C36040%20Dequindre%20Road%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C2567%20Metro%20Parkway%2C%20Sterling%20Heights%2C%20Michigan%2C%2048310%7C37300%20Dequindre%20Rd%20Ste%20102%2C%20Sterling%20Heights%2C%20MI%2048310%7C37450%20DeQuindre%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048310%7C41400%20Dequindre%20Rd%2C%20ste%20121%2C%20Sterling%20Heights%2C%20Michigan%2C%2048314%7C44344%20Dequindre%20Rd%20Ste%20510%2C%20Sterling%20Heights%2C%20MI%20nan</t>
         </is>
       </c>
     </row>
@@ -3334,13 +3334,13 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Southfield (5) • Livonia (2)</t>
+          <t>Livonia (4) • Southfield (3)</t>
         </is>
       </c>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075&amp;waypoints=23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C30852%20W%2010%20MILE%20RD%2C%20FARMINGTON%20HILLS%2C%20MI%2C%2048336%7C28670%20Telegraph%20Road%2C%20Southfield%2C%20Michigan%2C%2048034%7C29829%20Telegraph%20Road%2C%20Southfield%2C%20MI%2048034%7C29877%20Telegraph%20Rd%20Ste%20200%2C%20Southfield%2C%20MI%2048034%7C17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=17330%20Northland%20Park%20Ct%20Ste%20100%2C%20Southfield%2C%20MI%2048075&amp;waypoints=23330%20%20Rd%20Farmington%2C%20Farmington%2C%20Michigan%2C%2048336%7C33523%20Eight%20Mile%20Rd%20m2%2C%20Livonia%2C%20Michigan%2C%2048152%7C17940%20Farmington%20Rd%20Ste%20130%2C%20Livonia%2C%20MI%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C23700%20Orchard%20Lake%20Rd%2C%20Farmington%20Hills%2C%20MI%2C%2048336-2559%7C28670%20Telegraph%20Road%2C%20Southfield%2C%20Michigan%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C17070%20W%2012%20MILE%20RD%20STE%20A%2C%20SOUTHFIELD%2C%20Michigan%2C%20MI%2048076</t>
         </is>
       </c>
     </row>
@@ -3377,13 +3377,13 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Livonia (3) • Farmington Hills (2)</t>
+          <t>Southfield (3) • Farmington Hills (2)</t>
         </is>
       </c>
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185&amp;waypoints=9178%20Highland%20Rd%2C%20White%20Lake%2C%20MI%20483864619%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C20216%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C33215%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6149%20Elmwood%20Street%2C%20Westland%2C%20Michigan%2C%2048185&amp;waypoints=8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C30055%20Northwestern%20Hwy%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C31390%20Northwestern%20Hwy.%2C%20Ste%20C%2C%20Farmington%20Hills%2C%20Michigan%2C%2048334%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20Northwestern%20Hwy%20%23210%2C%20Southfield%2C%20Michigan%2C%2048034%7C15540%20Beech%20Daly%2C%20Redford%20Charter%20Township%2C%20Michigan%2C%2048239%7C24224%20JOY%20RD%20STE%20100%2C%20REDFORD%2C%20Michigan%7C15604%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048154</t>
         </is>
       </c>
     </row>
@@ -3592,13 +3592,13 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Warren (4) • Clinton Township (4)</t>
+          <t>Clinton Township (4) • Sterling Heights (3)</t>
         </is>
       </c>
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038&amp;waypoints=38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C4600%2014%20Mile%20Rd%20ste%201%2C%20Warren%2C%20Michigan%2C%2048092%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093%7C29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093%7C30061%20Schoenherr%20Rd%2C%20Warren%2C%20Michigan%2C%2048088%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20599%20Mack%20Ave%2C%20Grosse%20Pointe%20Woods%2C%20MI%2048236&amp;waypoints=38300%20Van%20Dyke%20Ave%2C%20Ste%20105%2C%20Sterling%20Heights%2C%20MI%2048312%7C15500%2019%20Mile%20Rd%20Suite%20300%2C%20Clinton%20Township%2C%20MI%2048038%7C15520%2019%20Mile%20Road%2C%20Suite%20480%2C%20Clinton%20Township%2C%20MI%2C%2048038%7C43600%20Garfield%20Rd%2C%20Clinton%20Township%2C%20Michigan%2C%2048038%7C39200%20Garfield%20Rd%20Suite%20E%20Clinton%20Twp%2C%20Clinton%20Township%2C%20MI%2048038%7C13951%20Plumbrook%2C%20Sterling%20Heights%2C%20Michigan%2C%2048312%7C35429%20Schoenherr%20Rd%2C%20Sterling%20Heights%2C%20MI%2C%2048312%7C11270%20East%20Thirteen%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048093%7C29703%20HOOVER%20RD%20STE%20A%2C%20WARREN%2C%20Michigan%2C%2048093</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>0</v>
@@ -3674,17 +3674,17 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Southfield (2) • White Lake Charter Township (1)</t>
+          <t>West Bloomfield (2) • Troy (2)</t>
         </is>
       </c>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302&amp;waypoints=8355%20Highland%20Road%2C%20White%20Lake%20Charter%20Township%2C%20MI%2048386%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336%7C29355%20Northwestern%20Hwy%2C%20Southfield%2C%20Michigan%2C%2048034%7C29355%20NORTHWESTERN%20HWY%20STE%20120%2C%20SOUTHFIELD%2C%20MI%2C%2048034%7C31500%20TELEGRAPH%20RD%20STE%20115%2C%20BINGHAM%20FARMS%2C%20MI%2C%2048025%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=23133%20Orchard%20Lake%20Rd%2C%20Farmington%2C%20Michigan%2C%2048336&amp;waypoints=6089%20W%20MAPLE%20RD%20STE%20200%2C%20WEST%20BLOOMFIELD%2C%20Michigan%7C5799%20W%20MAPLE%20RD%20STE%20163%2C%20WEST%20BLOOMFIELD%2C%20MI%2C%2048322%7C6543%20TELEGRAPH%20RD%2C%20BLOOMFIELD%20TOWNSHIP%2C%20Michigan%7C43700%20WOODWARD%20AVE%20STE%20206%2C%20BLOOMFIELD%2C%20Michigan%2C%20MI%2048302%7C115%20E%20Long%20Lake%20Rd%2C%20Troy%2C%20MI%2048085%7C3456%20Rochester%20Rd%2C%20Troy%2C%20Michigan%2C%2048083%7C31005%20John%20R%20Rd%20suite%20a%2C%20Madison%20Heights%2C%20Michigan%2C%2048071%7C3270%20Greenfield%20Rd%2C%20Berkley%2C%20Michigan%2C%2048072%7C23800%20Orchard%20Lake%20Rd%20suite%20202%2C%20Farmington%20Hills%2C%20Michigan%2C%2048336</t>
         </is>
       </c>
     </row>
@@ -27485,7 +27485,7 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>📝 Center For Hollistic Medicine</t>
+          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
@@ -27500,17 +27500,17 @@
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
+          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J390" s="2" t="n">
@@ -27518,12 +27518,12 @@
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr">
         <is>
-          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
+          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
         </is>
       </c>
       <c r="M390" s="3" t="n"/>
@@ -28985,12 +28985,12 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>📝 Trinity IHA Primary Care - Schoolcraft Campus</t>
+          <t>📝 Ivy Rehab - Farmington</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
@@ -29000,12 +29000,12 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>4b1cacba-85fb-4f63-8660-c3314cf72677</t>
+          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr">
@@ -29014,16 +29014,16 @@
         </is>
       </c>
       <c r="J415" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K415" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L415" s="3" t="inlineStr">
         <is>
-          <t>19000 St Joe's Pkwy suite 200, Livonia, Michigan, 48152</t>
+          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M415" s="3" t="n"/>
@@ -29045,12 +29045,12 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>📝 Park Medical Centers</t>
+          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 27</t>
+          <t>Tier 1 producer · last check-in Sep 1</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>92913d4d-edc4-462b-aecf-ef3f54198f09</t>
+          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -29074,16 +29074,16 @@
         </is>
       </c>
       <c r="J416" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr">
         <is>
-          <t>38253 Ann Arbor Road, Livonia, Michigan, 48150</t>
+          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M416" s="3" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>📝 GARDEN CITY FAMILY PHYSICIANS</t>
+          <t>📝 Greg Monroe DO PC</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>be4c4280-49d5-443c-b413-3471ee753d27</t>
+          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -29134,16 +29134,16 @@
         </is>
       </c>
       <c r="J417" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
         <is>
-          <t>30900 FORD RD STE B, GARDEN CITY, MI, 48135</t>
+          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
         </is>
       </c>
       <c r="M417" s="3" t="n"/>
@@ -29165,12 +29165,12 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>📝 Greg Monroe DO PC</t>
+          <t>📝 Park Medical Centers</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 1</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>4de0cfd4-93f7-4efa-a4ed-25a3ceaf173b</t>
+          <t>92913d4d-edc4-462b-aecf-ef3f54198f09</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -29194,16 +29194,16 @@
         </is>
       </c>
       <c r="J418" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
-          <t>Westland</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr">
         <is>
-          <t>6149 Elmwood Street, Westland, Michigan, 48185</t>
+          <t>38253 Ann Arbor Road, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M418" s="3" t="n"/>
@@ -31445,12 +31445,12 @@
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Health Medical Center - Seven Mile Road</t>
+          <t>📝 Trinity IHA Primary Care - Schoolcraft Campus</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 11</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>44019f00-063b-4cdc-83d9-96ee51f8c6e3</t>
+          <t>4b1cacba-85fb-4f63-8660-c3314cf72677</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="L456" s="3" t="inlineStr">
         <is>
-          <t>37508 W SEVEN MILE RD, LIVONIA, Michigan</t>
+          <t>19000 St Joe's Pkwy suite 200, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M456" s="3" t="n"/>
@@ -31565,12 +31565,12 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>📝 Henry Ford Health Medical Center - Seven Mile Road</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -31580,7 +31580,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
+          <t>44019f00-063b-4cdc-83d9-96ee51f8c6e3</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="L458" s="3" t="inlineStr">
         <is>
-          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
+          <t>37508 W SEVEN MILE RD, LIVONIA, Michigan</t>
         </is>
       </c>
       <c r="M458" s="3" t="n"/>
@@ -31625,12 +31625,12 @@
       </c>
       <c r="D459" s="3" t="inlineStr">
         <is>
-          <t>📝 Ivy Rehab - Farmington</t>
+          <t>📝 Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
@@ -31640,12 +31640,12 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>d1393500-eb13-4514-9e0b-427f872ffa8b</t>
+          <t>22476694-35cd-4d2b-b17f-07cee1f1db4b</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
@@ -31654,16 +31654,16 @@
         </is>
       </c>
       <c r="J459" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
-          <t>Farmington</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L459" s="3" t="inlineStr">
         <is>
-          <t>23330  Rd Farmington, Farmington, Michigan, 48336</t>
+          <t>33523 Eight Mile Rd m2, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M459" s="3" t="n"/>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="D465" s="3" t="inlineStr">
         <is>
-          <t>📝 SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>📝 ROSE MEDICINE</t>
         </is>
       </c>
       <c r="E465" s="3" t="inlineStr">
@@ -32000,12 +32000,12 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>297a710c-01f5-41e0-9ffc-d1df69e9329d</t>
+          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I465" s="2" t="inlineStr">
@@ -32018,12 +32018,12 @@
       </c>
       <c r="K465" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Bingham Farms</t>
         </is>
       </c>
       <c r="L465" s="3" t="inlineStr">
         <is>
-          <t>17070 W 12 MILE RD STE A, SOUTHFIELD, Michigan, MI 48076</t>
+          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
         </is>
       </c>
       <c r="M465" s="3" t="n"/>
@@ -33005,27 +33005,27 @@
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>Total Urgent Care - Romeo</t>
+          <t>📝 Academic Internal Medicine (Ascension)</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>Prospect first-touch</t>
+          <t>Tier 3 · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>faf664cc-930b-4471-8786-7027f805cedd</t>
+          <t>97ae4125-fd10-47de-8cae-c053e42232d0</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I482" s="2" t="inlineStr">
@@ -33038,12 +33038,12 @@
       </c>
       <c r="K482" s="2" t="inlineStr">
         <is>
-          <t>Bruce Township</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr">
         <is>
-          <t>79720 Kidder Rd Bruce Township, Michigan, 48065</t>
+          <t>57850 Van Dyke Ave ste 600, Washington, Michigan, 48094</t>
         </is>
       </c>
       <c r="M482" s="3" t="n"/>
@@ -33065,45 +33065,45 @@
       </c>
       <c r="D483" s="3" t="inlineStr">
         <is>
-          <t>📝 Academic Internal Medicine (Ascension)</t>
+          <t>Oakland Medical Center</t>
         </is>
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Aug 24</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>97ae4125-fd10-47de-8cae-c053e42232d0</t>
+          <t>77bba5d4-d050-4705-b292-6e3a8a78dec8</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J483" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K483" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L483" s="3" t="inlineStr">
         <is>
-          <t>57850 Van Dyke Ave ste 600, Washington, Michigan, 48094</t>
+          <t>115 E Long Lake Rd, Troy, MI 48085</t>
         </is>
       </c>
       <c r="M483" s="3" t="n"/>
@@ -33125,32 +33125,32 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>Pediatric Consultants of Troy - Shelby Township</t>
+          <t>📝 Macomb Spine Care</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jun 22</t>
+          <t>Tier 3 · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>7f486a16-5999-4a69-b80d-9de7d1f85a2d</t>
+          <t>c3d66a4c-f046-43dd-ae93-ae4aabe95524</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J484" s="2" t="n">
@@ -33158,12 +33158,12 @@
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
-          <t>Shelby Township</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr">
         <is>
-          <t>50720 Schoenherr Rd, Shelby Township, MI 48315</t>
+          <t>41060 Hayes Road, Clinton Township, Michigan, 48038</t>
         </is>
       </c>
       <c r="M484" s="3" t="n"/>
@@ -33185,45 +33185,45 @@
       </c>
       <c r="D485" s="3" t="inlineStr">
         <is>
-          <t>Shelby Pediatric Associates &amp; Child Lung Center</t>
+          <t>📝 Macomb Internal Medicine</t>
         </is>
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 22</t>
+          <t>Tier 1 producer · last check-in Jul 10</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>cbb6770d-0a7e-4610-a0a9-34566000818b</t>
+          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J485" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
-          <t>Shelby Township</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L485" s="3" t="inlineStr">
         <is>
-          <t>15125 22 Mile Rd, Shelby Township, MI 48315</t>
+          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
         </is>
       </c>
       <c r="M485" s="3" t="n"/>
@@ -33245,7 +33245,7 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>📝 Cornerstone St. Clair Internists</t>
+          <t>📝 David S Weingarden MD &amp; Associates</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
@@ -33260,12 +33260,12 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>cc9cf66d-2e3c-4e56-9aeb-85ba4b7e600c</t>
+          <t>ec2dcadc-ce63-4324-aea0-52ae2b2bdd91</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I486" s="2" t="inlineStr">
@@ -33278,12 +33278,12 @@
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
-          <t>Shelby Township</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr">
         <is>
-          <t>45640 Schoenherr Rd, Shelby Township, Michigan, 48315</t>
+          <t>43555 Dalcoma Dr suite 4 Clinton Twp, Clinton Township, Michigan, 48038</t>
         </is>
       </c>
       <c r="M486" s="3" t="n"/>
@@ -33305,27 +33305,27 @@
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>📝 Macomb Spine Care</t>
+          <t>📝 Cornerstone St. Clair Internists</t>
         </is>
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Aug 24</t>
+          <t>Tier 2 ortho · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>c3d66a4c-f046-43dd-ae93-ae4aabe95524</t>
+          <t>cc9cf66d-2e3c-4e56-9aeb-85ba4b7e600c</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I487" s="2" t="inlineStr">
@@ -33338,12 +33338,12 @@
       </c>
       <c r="K487" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="L487" s="3" t="inlineStr">
         <is>
-          <t>41060 Hayes Road, Clinton Township, Michigan, 48038</t>
+          <t>45640 Schoenherr Rd, Shelby Township, Michigan, 48315</t>
         </is>
       </c>
       <c r="M487" s="3" t="n"/>
@@ -33365,45 +33365,45 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>📝 Macomb Internal Medicine</t>
+          <t>Pediatric Consultants of Troy - Shelby Township</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 10</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jun 22</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
+          <t>7f486a16-5999-4a69-b80d-9de7d1f85a2d</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J488" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr">
         <is>
-          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
+          <t>50720 Schoenherr Rd, Shelby Township, MI 48315</t>
         </is>
       </c>
       <c r="M488" s="3" t="n"/>
@@ -33425,12 +33425,12 @@
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>📝 David S Weingarden MD &amp; Associates</t>
+          <t>Shelby Pediatric Associates &amp; Child Lung Center</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Aug 24</t>
+          <t>Tier 2 ortho · last check-in Jun 22</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
@@ -33440,17 +33440,17 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>ec2dcadc-ce63-4324-aea0-52ae2b2bdd91</t>
+          <t>cbb6770d-0a7e-4610-a0a9-34566000818b</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J489" s="2" t="n">
@@ -33458,12 +33458,12 @@
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Shelby Township</t>
         </is>
       </c>
       <c r="L489" s="3" t="inlineStr">
         <is>
-          <t>43555 Dalcoma Dr suite 4 Clinton Twp, Clinton Township, Michigan, 48038</t>
+          <t>15125 22 Mile Rd, Shelby Township, MI 48315</t>
         </is>
       </c>
       <c r="M489" s="3" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>📝 MARY LEE, MD, PC</t>
+          <t>📝 Center For Hollistic Medicine</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
@@ -33620,17 +33620,17 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>d62a30ae-10fe-4408-a2cc-7b0aa9422bb8</t>
+          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J492" s="2" t="n">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="L492" s="3" t="inlineStr">
         <is>
-          <t>5799 W MAPLE RD STE 163, WEST BLOOMFIELD, MI, 48322</t>
+          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
         </is>
       </c>
       <c r="M492" s="3" t="n"/>
@@ -33665,12 +33665,12 @@
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Primary Care Center - 160</t>
+          <t>📝 MARY LEE, MD, PC</t>
         </is>
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
+          <t>d62a30ae-10fe-4408-a2cc-7b0aa9422bb8</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
@@ -33694,16 +33694,16 @@
         </is>
       </c>
       <c r="J493" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K493" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L493" s="3" t="inlineStr">
         <is>
-          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
+          <t>5799 W MAPLE RD STE 163, WEST BLOOMFIELD, MI, 48322</t>
         </is>
       </c>
       <c r="M493" s="3" t="n"/>
@@ -33725,7 +33725,7 @@
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>📝 Levine Clinic of Chiropractic</t>
+          <t>📝 Henry Ford Primary Care Center - 160</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
@@ -33740,12 +33740,12 @@
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
+          <t>b6033c7f-ac4e-4957-b3b0-519077da6c8d</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I494" s="2" t="inlineStr">
@@ -33754,7 +33754,7 @@
         </is>
       </c>
       <c r="J494" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K494" s="2" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="L494" s="3" t="inlineStr">
         <is>
-          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
+          <t>30055 Northwestern Hwy, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M494" s="3" t="n"/>
@@ -33785,12 +33785,12 @@
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Internal Medicine Southfield</t>
+          <t>📝 Levine Clinic of Chiropractic</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
@@ -33800,12 +33800,12 @@
       </c>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
+          <t>e19f7675-d86b-445b-ad8d-c06409bfde92</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I495" s="2" t="inlineStr">
@@ -33814,16 +33814,16 @@
         </is>
       </c>
       <c r="J495" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L495" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
+          <t>31390 Northwestern Hwy., Ste C, Farmington Hills, Michigan, 48334</t>
         </is>
       </c>
       <c r="M495" s="3" t="n"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>📝 Jian Zu MD</t>
+          <t>📝 Corewell Internal Medicine Southfield</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
+          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
@@ -33883,7 +33883,7 @@
       </c>
       <c r="L496" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
+          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M496" s="3" t="n"/>
@@ -33905,7 +33905,7 @@
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>📝 Carson Center Specialty</t>
+          <t>📝 Jian Zu MD</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
+          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
@@ -33934,7 +33934,7 @@
         </is>
       </c>
       <c r="J497" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="L497" s="3" t="inlineStr">
         <is>
-          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
+          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M497" s="3" t="n"/>
@@ -33965,12 +33965,12 @@
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>📝 ROSE MEDICINE</t>
+          <t>📝 Carson Center Specialty</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
+          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
@@ -33994,16 +33994,16 @@
         </is>
       </c>
       <c r="J498" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
-          <t>Bingham Farms</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr">
         <is>
-          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
+          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
         </is>
       </c>
       <c r="M498" s="3" t="n"/>
@@ -34205,45 +34205,45 @@
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell URGENT CARE BY WELLSTREET</t>
+          <t>📝 IHA UNION LAKE PEDIATRICS</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 29</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>5f3e3632-715d-4e1c-b4ca-4c6bc3dac21e</t>
+          <t>905d0bbb-d935-4258-8a1e-2e30d0a25987</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J502" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
-          <t>Bloomfield Township</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr">
         <is>
-          <t>6543 TELEGRAPH RD, BLOOMFIELD TOWNSHIP, Michigan</t>
+          <t>2630 UNION LAKE RD STE 100, COMMERCE TOWNSHIP, Michigan</t>
         </is>
       </c>
       <c r="M502" s="3" t="n"/>
@@ -34805,12 +34805,12 @@
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>📝 DMC Orthopedics - Commerce Township</t>
+          <t>White Lake Family Medicine</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 21</t>
+          <t>Tier 1 producer · last check-in Jul 21</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
@@ -34820,30 +34820,30 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>568c9052-985c-48fa-b5bc-44baafba3dea</t>
+          <t>6f873c6d-498d-4d61-b717-d6648675da4e</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J512" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>White Lake</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr">
         <is>
-          <t>1 William Carls Drive, Michigan, 48382</t>
+          <t>9178 Highland Rd, White Lake, MI 483864619</t>
         </is>
       </c>
       <c r="M512" s="3" t="n"/>
@@ -34865,12 +34865,12 @@
       </c>
       <c r="D513" s="3" t="inlineStr">
         <is>
-          <t>📝 Providence Park Pediatrics - Novi</t>
+          <t>ALAN L FELDMAN, DO, PC</t>
         </is>
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 25</t>
+          <t>Tier 1 producer · last check-in May 26</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
@@ -34880,17 +34880,17 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>9db7de95-514d-45c7-8a73-449a08d1d590</t>
+          <t>5d0e63d7-bdd3-445e-a627-ef0ea5dc48f7</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J513" s="2" t="n">
@@ -34898,12 +34898,12 @@
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L513" s="3" t="inlineStr">
         <is>
-          <t>26850 PROVIDENCE PKWY STE 455, NOVI, Michigan</t>
+          <t>1965 Union Lake Rd, Commerce Township, MI 48382</t>
         </is>
       </c>
       <c r="M513" s="3" t="n"/>
@@ -34925,12 +34925,12 @@
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>📝 PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC</t>
+          <t>📝 CoreMed - Commerce</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>f5f4f354-94f3-42a1-a3be-10f8a64cdaae</t>
+          <t>eab7d954-a523-466a-a75b-3eca7bf9c6d0</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -34958,12 +34958,12 @@
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>Walled Lake</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr">
         <is>
-          <t>100 N POND DR STE C, WALLED LAKE, MI, 48390</t>
+          <t>2600 Union Lake Rd suite 140 Commerce Township, Michigan, 48382</t>
         </is>
       </c>
       <c r="M514" s="3" t="n"/>
@@ -34985,12 +34985,12 @@
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>LAKES INTERNAL MEDICINE - 2150</t>
+          <t>📝 Rodnick Chiropractic</t>
         </is>
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
@@ -35000,17 +35000,17 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>8b9ada78-08d8-45f0-8d09-c043db61a6fd</t>
+          <t>97e1431f-4c5b-4ec4-b3a5-47267613937b</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J515" s="2" t="n">
@@ -35018,12 +35018,12 @@
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Commerce Charter Township</t>
         </is>
       </c>
       <c r="L515" s="3" t="inlineStr">
         <is>
-          <t>2300 Haggerty Rd Ste 2150, West Bloomfield, MI 48323</t>
+          <t>2685 Union Lake Rd Commerce Charter Twp, Commerce Charter Township, Michigan, 48382</t>
         </is>
       </c>
       <c r="M515" s="3" t="n"/>
@@ -35105,12 +35105,12 @@
       </c>
       <c r="D517" s="3" t="inlineStr">
         <is>
-          <t>📝 Rodnick Chiropractic</t>
+          <t>📝 DMC Orthopedics - Commerce Township</t>
         </is>
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -35120,12 +35120,12 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>97e1431f-4c5b-4ec4-b3a5-47267613937b</t>
+          <t>568c9052-985c-48fa-b5bc-44baafba3dea</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I517" s="2" t="inlineStr">
@@ -35134,16 +35134,16 @@
         </is>
       </c>
       <c r="J517" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K517" s="2" t="inlineStr">
         <is>
-          <t>Commerce Charter Township</t>
+          <t>Commerce Township</t>
         </is>
       </c>
       <c r="L517" s="3" t="inlineStr">
         <is>
-          <t>2685 Union Lake Rd Commerce Charter Twp, Commerce Charter Township, Michigan, 48382</t>
+          <t>1 William Carls Drive, Michigan, 48382</t>
         </is>
       </c>
       <c r="M517" s="3" t="n"/>
@@ -35165,12 +35165,12 @@
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>📝 IHA UNION LAKE PEDIATRICS</t>
+          <t>📝 Providence Park Pediatrics - Novi</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 15</t>
+          <t>Tier 1 producer · last check-in Sep 25</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>905d0bbb-d935-4258-8a1e-2e30d0a25987</t>
+          <t>9db7de95-514d-45c7-8a73-449a08d1d590</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J518" s="2" t="n">
@@ -35198,12 +35198,12 @@
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr">
         <is>
-          <t>2630 UNION LAKE RD STE 100, COMMERCE TOWNSHIP, Michigan</t>
+          <t>26850 PROVIDENCE PKWY STE 455, NOVI, Michigan</t>
         </is>
       </c>
       <c r="M518" s="3" t="n"/>
@@ -35225,12 +35225,12 @@
       </c>
       <c r="D519" s="3" t="inlineStr">
         <is>
-          <t>📝 CoreMed - Commerce</t>
+          <t>📝 PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC</t>
         </is>
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 21</t>
+          <t>Tier 1 producer · last check-in Sep 15</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>eab7d954-a523-466a-a75b-3eca7bf9c6d0</t>
+          <t>f5f4f354-94f3-42a1-a3be-10f8a64cdaae</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -35258,12 +35258,12 @@
       </c>
       <c r="K519" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>Walled Lake</t>
         </is>
       </c>
       <c r="L519" s="3" t="inlineStr">
         <is>
-          <t>2600 Union Lake Rd suite 140 Commerce Township, Michigan, 48382</t>
+          <t>100 N POND DR STE C, WALLED LAKE, MI, 48390</t>
         </is>
       </c>
       <c r="M519" s="3" t="n"/>
@@ -35285,12 +35285,12 @@
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>ALAN L FELDMAN, DO, PC</t>
+          <t>LAKES INTERNAL MEDICINE - 2150</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 26</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>5d0e63d7-bdd3-445e-a627-ef0ea5dc48f7</t>
+          <t>8b9ada78-08d8-45f0-8d09-c043db61a6fd</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -35318,12 +35318,12 @@
       </c>
       <c r="K520" s="2" t="inlineStr">
         <is>
-          <t>Commerce Township</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr">
         <is>
-          <t>1965 Union Lake Rd, Commerce Township, MI 48382</t>
+          <t>2300 Haggerty Rd Ste 2150, West Bloomfield, MI 48323</t>
         </is>
       </c>
       <c r="M520" s="3" t="n"/>
@@ -35345,45 +35345,45 @@
       </c>
       <c r="D521" s="3" t="inlineStr">
         <is>
-          <t>📝 HEALING HANDS URGENT CARE</t>
+          <t>MICHIGAN PREMIER INTERNISTS</t>
         </is>
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 30</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>ed1959ed-68b4-4788-bfa4-24c1e6d994d6</t>
+          <t>1a1e59ec-5621-4caa-a9e9-b4d86b5218e7</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J521" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K521" s="2" t="inlineStr">
         <is>
-          <t>Sylvan Lake</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L521" s="3" t="inlineStr">
         <is>
-          <t>2157 ORCHARD LAKE RD, SYLVAN LAKE, Michigan</t>
+          <t>29877 Telegraph Rd Ste 200, Southfield, MI 48034</t>
         </is>
       </c>
       <c r="M521" s="3" t="n"/>
@@ -35405,12 +35405,12 @@
       </c>
       <c r="D522" s="3" t="inlineStr">
         <is>
-          <t>Oakland Medical Center</t>
+          <t>Franklin Medical Consultants</t>
         </is>
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>77bba5d4-d050-4705-b292-6e3a8a78dec8</t>
+          <t>559bee40-1fa3-437d-9e4b-692838015293</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -35438,12 +35438,12 @@
       </c>
       <c r="K522" s="2" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr">
         <is>
-          <t>115 E Long Lake Rd, Troy, MI 48085</t>
+          <t>29829 Telegraph Road, Southfield, MI 48034</t>
         </is>
       </c>
       <c r="M522" s="3" t="n"/>
@@ -35465,12 +35465,12 @@
       </c>
       <c r="D523" s="3" t="inlineStr">
         <is>
-          <t>📝 Kashat Urgent care</t>
+          <t>📝 DEIGHTON FAMILY PRACTICE - use this one</t>
         </is>
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -35480,12 +35480,12 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>0b9485b1-39bd-4f21-8222-387834af8472</t>
+          <t>a6779fd4-289a-49f7-8602-76dc1bf5764c</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I523" s="2" t="inlineStr">
@@ -35498,12 +35498,12 @@
       </c>
       <c r="K523" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L523" s="3" t="inlineStr">
         <is>
-          <t>35200 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+          <t>22250 PROVIDENCE DR STE 500, SOUTHFIELD, Michigan</t>
         </is>
       </c>
       <c r="M523" s="3" t="n"/>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="D525" s="3" t="inlineStr">
         <is>
-          <t>ASCENSION MACOMB OAKLAND HOSPITAL MOTOR CITY INTERNISTS</t>
+          <t>📝 Kashat Urgent care</t>
         </is>
       </c>
       <c r="E525" s="3" t="inlineStr">
@@ -35600,17 +35600,17 @@
       </c>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>dc78e75f-e0d1-4c67-8de9-8ea4f13f15a1</t>
+          <t>0b9485b1-39bd-4f21-8222-387834af8472</t>
         </is>
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J525" s="2" t="n">
@@ -35618,12 +35618,12 @@
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L525" s="3" t="inlineStr">
         <is>
-          <t>11885 E 12 Mile Rd Ste 200B, Warren, MI 48093</t>
+          <t>35200 Dequindre Road, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M525" s="3" t="n"/>
@@ -35645,7 +35645,7 @@
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>📝 Michigan Compassionate Care</t>
+          <t>ASCENSION MACOMB OAKLAND HOSPITAL MOTOR CITY INTERNISTS</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr">
@@ -35660,21 +35660,21 @@
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>33d0c0aa-7d47-450d-9673-71acb651321c</t>
+          <t>dc78e75f-e0d1-4c67-8de9-8ea4f13f15a1</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J526" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
       </c>
       <c r="L526" s="3" t="inlineStr">
         <is>
-          <t>28401 Hoover, Warren, Michigan, 48093</t>
+          <t>11885 E 12 Mile Rd Ste 200B, Warren, MI 48093</t>
         </is>
       </c>
       <c r="M526" s="3" t="n"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="D527" s="3" t="inlineStr">
         <is>
-          <t>📝 FERRIS, MARY C, MEDICAL GROUP</t>
+          <t>📝 Michigan Compassionate Care</t>
         </is>
       </c>
       <c r="E527" s="3" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>a5a045ce-889d-4018-81f5-3fd8d3d7af6b</t>
+          <t>33d0c0aa-7d47-450d-9673-71acb651321c</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
@@ -35734,7 +35734,7 @@
         </is>
       </c>
       <c r="J527" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="L527" s="3" t="inlineStr">
         <is>
-          <t>28111 HOOVER RD STE 1A, WARREN, Michigan</t>
+          <t>28401 Hoover, Warren, Michigan, 48093</t>
         </is>
       </c>
       <c r="M527" s="3" t="n"/>
@@ -35765,7 +35765,7 @@
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>Hoover Primary Care Medical Group</t>
+          <t>📝 FERRIS, MARY C, MEDICAL GROUP</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr">
@@ -35780,17 +35780,17 @@
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>d2472b07-69ea-403b-b954-d5d8227b1364</t>
+          <t>a5a045ce-889d-4018-81f5-3fd8d3d7af6b</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J528" s="2" t="n">
@@ -35803,7 +35803,7 @@
       </c>
       <c r="L528" s="3" t="inlineStr">
         <is>
-          <t>28111 Hoover Rd, Ste 5A Warren, Mi 48093, Usa, Warren, MI 48093</t>
+          <t>28111 HOOVER RD STE 1A, WARREN, Michigan</t>
         </is>
       </c>
       <c r="M528" s="3" t="n"/>
@@ -35825,7 +35825,7 @@
       </c>
       <c r="D529" s="3" t="inlineStr">
         <is>
-          <t>Macomb Neurology Associates</t>
+          <t>Hoover Primary Care Medical Group</t>
         </is>
       </c>
       <c r="E529" s="3" t="inlineStr">
@@ -35840,12 +35840,12 @@
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>1023090552</t>
+          <t>d2472b07-69ea-403b-b954-d5d8227b1364</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I529" s="2" t="inlineStr">
@@ -35863,7 +35863,7 @@
       </c>
       <c r="L529" s="3" t="inlineStr">
         <is>
-          <t>27427 Schoenherr Rd, Warren, MI 48088</t>
+          <t>28111 Hoover Rd, Ste 5A Warren, Mi 48093, Usa, Warren, MI 48093</t>
         </is>
       </c>
       <c r="M529" s="3" t="n"/>
@@ -35885,27 +35885,27 @@
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>Emcura Immediate Care - Grosse Pointe</t>
+          <t>Macomb Neurology Associates</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 3</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>bf549ea4-0d9c-4877-927c-ed3f99bf0988</t>
+          <t>1023090552</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="I530" s="2" t="inlineStr">
@@ -35914,16 +35914,16 @@
         </is>
       </c>
       <c r="J530" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
-          <t>Grosse Pointe Woods</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr">
         <is>
-          <t>20599 Mack Ave, Grosse Pointe Woods, MI 48236</t>
+          <t>27427 Schoenherr Rd, Warren, MI 48088</t>
         </is>
       </c>
       <c r="M530" s="3" t="n"/>
@@ -35945,12 +35945,12 @@
       </c>
       <c r="D531" s="3" t="inlineStr">
         <is>
-          <t>📝 DEIGHTON FAMILY PRACTICE - use this one</t>
+          <t>📝 Pulmonary &amp; Medical Associates</t>
         </is>
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
@@ -35960,7 +35960,7 @@
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>a6779fd4-289a-49f7-8602-76dc1bf5764c</t>
+          <t>dda630a5-9d61-49cd-bec6-61084e47ddb9</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
@@ -35974,16 +35974,16 @@
         </is>
       </c>
       <c r="J531" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L531" s="3" t="inlineStr">
         <is>
-          <t>22250 PROVIDENCE DR STE 500, SOUTHFIELD, Michigan</t>
+          <t>27472 Schoenherr Rd #100, Warren, MI, 48088</t>
         </is>
       </c>
       <c r="M531" s="3" t="n"/>
@@ -36365,7 +36365,7 @@
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>📝 Pulmonary &amp; Medical Associates</t>
+          <t>📝 Northpointe Pediatrics</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr">
@@ -36380,12 +36380,12 @@
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>dda630a5-9d61-49cd-bec6-61084e47ddb9</t>
+          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I538" s="2" t="inlineStr">
@@ -36394,7 +36394,7 @@
         </is>
       </c>
       <c r="J538" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
       </c>
       <c r="L538" s="3" t="inlineStr">
         <is>
-          <t>27472 Schoenherr Rd #100, Warren, MI, 48088</t>
+          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
         </is>
       </c>
       <c r="M538" s="3" t="n"/>
@@ -36725,12 +36725,12 @@
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>📝 Center For Hollistic Medicine</t>
+          <t>Burhani Medical Center - use this one</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in May 13</t>
         </is>
       </c>
       <c r="F544" s="2" t="inlineStr">
@@ -36740,17 +36740,17 @@
       </c>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
+          <t>3ade325e-79e3-41bc-a8b9-565bcfc77f2c</t>
         </is>
       </c>
       <c r="H544" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J544" s="2" t="n">
@@ -36758,12 +36758,12 @@
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr">
         <is>
-          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
+          <t>32910 West 13 Mile Road, A101, Farmington Hills, MI 48334</t>
         </is>
       </c>
       <c r="M544" s="3" t="n"/>
@@ -36785,12 +36785,12 @@
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>Burhani Medical Center - use this one</t>
+          <t>📝 Henry Ford Primary Care - Orchard Lake Road North</t>
         </is>
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in May 13</t>
+          <t>Tier 1 producer · last check-in Aug 13</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
@@ -36800,21 +36800,21 @@
       </c>
       <c r="G545" s="2" t="inlineStr">
         <is>
-          <t>3ade325e-79e3-41bc-a8b9-565bcfc77f2c</t>
+          <t>960ab807-be26-45c0-bbf9-135ef0a45ae0</t>
         </is>
       </c>
       <c r="H545" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I545" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J545" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
       </c>
       <c r="L545" s="3" t="inlineStr">
         <is>
-          <t>32910 West 13 Mile Road, A101, Farmington Hills, MI 48334</t>
+          <t>27970 ORCHARD LAKE RD, FARMINGTON HILLS, Michigan, 48334</t>
         </is>
       </c>
       <c r="M545" s="3" t="n"/>
@@ -36845,12 +36845,12 @@
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Primary Care - Orchard Lake Road North</t>
+          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 13</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F546" s="2" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>960ab807-be26-45c0-bbf9-135ef0a45ae0</t>
+          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr">
@@ -36874,7 +36874,7 @@
         </is>
       </c>
       <c r="J546" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
       </c>
       <c r="L546" s="3" t="inlineStr">
         <is>
-          <t>27970 ORCHARD LAKE RD, FARMINGTON HILLS, Michigan, 48334</t>
+          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
         </is>
       </c>
       <c r="M546" s="3" t="n"/>
@@ -36905,12 +36905,12 @@
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>📝 FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC</t>
+          <t>📝 Legend Health - Now One Health</t>
         </is>
       </c>
       <c r="E547" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F547" s="2" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="G547" s="2" t="inlineStr">
         <is>
-          <t>cc6d8767-1fad-4a5b-b658-38a67ea47a1c</t>
+          <t>078d2fa6-e81c-41d1-95f2-04234d511192</t>
         </is>
       </c>
       <c r="H547" s="2" t="inlineStr">
@@ -36934,16 +36934,16 @@
         </is>
       </c>
       <c r="J547" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K547" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L547" s="3" t="inlineStr">
         <is>
-          <t>29930 W 12 MILE RD STE 6, FARMINGTON HILLS, Michigan</t>
+          <t>29201 Telegraph Rd, ste 403, Southfield, MI, 48034</t>
         </is>
       </c>
       <c r="M547" s="3" t="n"/>
@@ -36965,12 +36965,12 @@
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>📝 Legend Health - Now One Health</t>
+          <t>📝 ORCHARD PRIMARY CARE</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="G548" s="2" t="inlineStr">
         <is>
-          <t>078d2fa6-e81c-41d1-95f2-04234d511192</t>
+          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
         </is>
       </c>
       <c r="H548" s="2" t="inlineStr">
@@ -36998,12 +36998,12 @@
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr">
         <is>
-          <t>29201 Telegraph Rd, ste 403, Southfield, MI, 48034</t>
+          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
         </is>
       </c>
       <c r="M548" s="3" t="n"/>
@@ -37805,45 +37805,45 @@
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>MALI AND MALI PEDIATRICS - use this one</t>
+          <t>📝 1st Choice Urgent Care</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Prospect · last check-in Aug 25</t>
         </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>2e26f7de-9e76-464a-a322-fbef639b64d7</t>
+          <t>e7cc65bc-b486-4ee3-9c39-431666859cbd</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J562" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr">
         <is>
-          <t>44344 Dequindre Rd Ste 510, Sterling Heights, MI nan</t>
+          <t>29628 Southfield Road, Southfield, Michigan, 48076</t>
         </is>
       </c>
       <c r="M562" s="3" t="n"/>
@@ -37865,12 +37865,12 @@
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>📝 Michigan Primary Care - Sterling Heights</t>
+          <t>📝 Lifetime Family Care</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F563" s="2" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>ce3b56cf-1381-41d0-b067-752448464958</t>
+          <t>b70053c3-f0fd-41de-9386-95fcc448a738</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -37894,16 +37894,16 @@
         </is>
       </c>
       <c r="J563" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L563" s="3" t="inlineStr">
         <is>
-          <t>41400 Dequindre Rd, ste 121, Sterling Heights, Michigan, 48314</t>
+          <t>26393 Dequindre Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M563" s="3" t="n"/>
@@ -37925,12 +37925,12 @@
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>Concentra Urgent Care - Sterling Heights</t>
+          <t>📝 Get Well Urgent Care Madison Heights</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Aug 25</t>
         </is>
       </c>
       <c r="F564" s="2" t="inlineStr">
@@ -37940,30 +37940,30 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
+          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J564" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K564" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr">
         <is>
-          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
+          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M564" s="3" t="n"/>
@@ -37985,12 +37985,12 @@
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care - Sterling Heights</t>
+          <t>📝 Sterling Physicians</t>
         </is>
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 3</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F565" s="2" t="inlineStr">
@@ -38000,12 +38000,12 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
+          <t>1972593499</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I565" s="2" t="inlineStr">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="L565" s="3" t="inlineStr">
         <is>
-          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
+          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M565" s="3" t="n"/>
@@ -38045,7 +38045,7 @@
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>📝 Tri-County Medical Clinic</t>
+          <t>📝 Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr">
@@ -38060,12 +38060,12 @@
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>1386634749</t>
+          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
         </is>
       </c>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I566" s="2" t="inlineStr">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="L566" s="3" t="inlineStr">
         <is>
-          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
+          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
         </is>
       </c>
       <c r="M566" s="3" t="n"/>
@@ -38165,12 +38165,12 @@
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>📝 Sterling Physicians</t>
+          <t>📝 Tri-County Medical Clinic</t>
         </is>
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Sep 3</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
@@ -38180,7 +38180,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>1972593499</t>
+          <t>1386634749</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="L568" s="3" t="inlineStr">
         <is>
-          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
         </is>
       </c>
       <c r="M568" s="3" t="n"/>
@@ -38225,12 +38225,12 @@
       </c>
       <c r="D569" s="3" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care Madison Heights</t>
+          <t>📝 Michigan Primary Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 25</t>
+          <t>Tier 1 producer · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F569" s="2" t="inlineStr">
@@ -38240,12 +38240,12 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
+          <t>ce3b56cf-1381-41d0-b067-752448464958</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I569" s="2" t="inlineStr">
@@ -38254,16 +38254,16 @@
         </is>
       </c>
       <c r="J569" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L569" s="3" t="inlineStr">
         <is>
-          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
+          <t>41400 Dequindre Rd, ste 121, Sterling Heights, Michigan, 48314</t>
         </is>
       </c>
       <c r="M569" s="3" t="n"/>
@@ -38285,45 +38285,45 @@
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Health Urgent Care - Warren West</t>
+          <t>MALI AND MALI PEDIATRICS - use this one</t>
         </is>
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>9152636b-052e-44f2-ab21-a7abf86561ff</t>
+          <t>2e26f7de-9e76-464a-a322-fbef639b64d7</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J570" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K570" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr">
         <is>
-          <t>28324 Dequindre Road, Warren, Michigan, 48092</t>
+          <t>44344 Dequindre Rd Ste 510, Sterling Heights, MI nan</t>
         </is>
       </c>
       <c r="M570" s="3" t="n"/>
@@ -38345,12 +38345,12 @@
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>📝 Lifetime Family Care</t>
+          <t>Concentra Urgent Care - Sterling Heights</t>
         </is>
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F571" s="2" t="inlineStr">
@@ -38360,30 +38360,30 @@
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>b70053c3-f0fd-41de-9386-95fcc448a738</t>
+          <t>dc6067ed-60f7-4ae5-8b5b-7b8b03095484</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I571" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L571" s="3" t="inlineStr">
         <is>
-          <t>26393 Dequindre Rd, Madison Heights, Michigan, 48071</t>
+          <t>39333 Van Dyke Ave, Sterling Heights, Mi 48313, United States, Sterling Heights, MI 48313</t>
         </is>
       </c>
       <c r="M571" s="3" t="n"/>
@@ -38585,12 +38585,12 @@
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>📝 Powers Family Medicine</t>
+          <t>📝 Brentwood Pediatric Associates</t>
         </is>
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Sep 11</t>
         </is>
       </c>
       <c r="F575" s="2" t="inlineStr">
@@ -38600,12 +38600,12 @@
       </c>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>00-761-7874</t>
+          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I575" s="2" t="inlineStr">
@@ -38614,16 +38614,16 @@
         </is>
       </c>
       <c r="J575" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K575" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L575" s="3" t="inlineStr">
         <is>
-          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
+          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M575" s="3" t="n"/>
@@ -38645,12 +38645,12 @@
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>📝 ORCHARD PRIMARY CARE</t>
+          <t>📝 Triumph chiropractic</t>
         </is>
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F576" s="2" t="inlineStr">
@@ -38660,12 +38660,12 @@
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>ba00dba0-20f9-440b-8df0-799ade91a785</t>
+          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I576" s="2" t="inlineStr">
@@ -38674,16 +38674,16 @@
         </is>
       </c>
       <c r="J576" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr">
         <is>
-          <t>30852 W 10 MILE RD, FARMINGTON HILLS, MI, 48336</t>
+          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M576" s="3" t="n"/>
@@ -38705,27 +38705,27 @@
       </c>
       <c r="D577" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Go Health Urgent Care</t>
+          <t>📝 Powers Family Medicine</t>
         </is>
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in May 27</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F577" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G577" s="2" t="inlineStr">
         <is>
-          <t>14f29ff1-cd7e-4e90-b5c7-b1114551c5b9</t>
+          <t>00-761-7874</t>
         </is>
       </c>
       <c r="H577" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I577" s="2" t="inlineStr">
@@ -38734,16 +38734,16 @@
         </is>
       </c>
       <c r="J577" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K577" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L577" s="3" t="inlineStr">
         <is>
-          <t>28670 Telegraph Road, Southfield, Michigan, 48034</t>
+          <t>23700 Orchard Lake Rd, Farmington Hills, MI, 48336-2559</t>
         </is>
       </c>
       <c r="M577" s="3" t="n"/>
@@ -38765,36 +38765,36 @@
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>Franklin Medical Consultants</t>
+          <t>📝 Henry Ford Go Health Urgent Care</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Prospect · last check-in May 27</t>
         </is>
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>559bee40-1fa3-437d-9e4b-692838015293</t>
+          <t>14f29ff1-cd7e-4e90-b5c7-b1114551c5b9</t>
         </is>
       </c>
       <c r="H578" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J578" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K578" s="2" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
       </c>
       <c r="L578" s="3" t="inlineStr">
         <is>
-          <t>29829 Telegraph Road, Southfield, MI 48034</t>
+          <t>28670 Telegraph Road, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M578" s="3" t="n"/>
@@ -38825,12 +38825,12 @@
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>MICHIGAN PREMIER INTERNISTS</t>
+          <t>📝 ROSE MEDICINE</t>
         </is>
       </c>
       <c r="E579" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F579" s="2" t="inlineStr">
@@ -38840,30 +38840,30 @@
       </c>
       <c r="G579" s="2" t="inlineStr">
         <is>
-          <t>1a1e59ec-5621-4caa-a9e9-b4d86b5218e7</t>
+          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
         </is>
       </c>
       <c r="H579" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I579" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J579" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K579" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Bingham Farms</t>
         </is>
       </c>
       <c r="L579" s="3" t="inlineStr">
         <is>
-          <t>29877 Telegraph Rd Ste 200, Southfield, MI 48034</t>
+          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
         </is>
       </c>
       <c r="M579" s="3" t="n"/>
@@ -39005,7 +39005,7 @@
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>White Lake Family Medicine</t>
+          <t>Core Med  - White Lake</t>
         </is>
       </c>
       <c r="E582" s="3" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>6f873c6d-498d-4d61-b717-d6648675da4e</t>
+          <t>ecbe00dd-1c49-4028-a575-d8852e23deba</t>
         </is>
       </c>
       <c r="H582" s="2" t="inlineStr">
@@ -39034,16 +39034,16 @@
         </is>
       </c>
       <c r="J582" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K582" s="2" t="inlineStr">
         <is>
-          <t>White Lake</t>
+          <t>White Lake Charter Township</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr">
         <is>
-          <t>9178 Highland Rd, White Lake, MI 483864619</t>
+          <t>8355 Highland Road, White Lake Charter Township, MI 48386</t>
         </is>
       </c>
       <c r="M582" s="3" t="n"/>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>📝 Corewell Internal Medicine Southfield</t>
+          <t>📝 Carson Center Specialty</t>
         </is>
       </c>
       <c r="E585" s="3" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
+          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
         </is>
       </c>
       <c r="H585" s="2" t="inlineStr">
@@ -39214,7 +39214,7 @@
         </is>
       </c>
       <c r="J585" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
       </c>
       <c r="L585" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
+          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
         </is>
       </c>
       <c r="M585" s="3" t="n"/>
@@ -39245,12 +39245,12 @@
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>📝 Triumph chiropractic</t>
+          <t>📝 Jian Zu MD</t>
         </is>
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
@@ -39260,12 +39260,12 @@
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>d99edd32-fb45-4528-94d3-645792efefa1</t>
+          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
         </is>
       </c>
       <c r="H586" s="2" t="inlineStr">
         <is>
-          <t>Other / Verify</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I586" s="2" t="inlineStr">
@@ -39274,16 +39274,16 @@
         </is>
       </c>
       <c r="J586" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr">
         <is>
-          <t>20216 Farmington Road, Livonia, Michigan, 48152</t>
+          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M586" s="3" t="n"/>
@@ -39305,12 +39305,12 @@
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>📝 Brentwood Pediatric Associates</t>
+          <t>📝 Corewell Internal Medicine Southfield</t>
         </is>
       </c>
       <c r="E587" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 11</t>
+          <t>Tier 1 producer · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F587" s="2" t="inlineStr">
@@ -39320,12 +39320,12 @@
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>9dfbaa38-07b2-4017-9d71-ff4cd2ce42f7</t>
+          <t>5eb6a409-5e7b-430f-a462-af3a919cfc22</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I587" s="2" t="inlineStr">
@@ -39338,12 +39338,12 @@
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L587" s="3" t="inlineStr">
         <is>
-          <t>33215 W Seven Mile Rd, Livonia, Michigan, 48152</t>
+          <t>29355 Northwestern Hwy #210, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M587" s="3" t="n"/>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
+          <t>📝 Beaumont Medical Center - Redford</t>
         </is>
       </c>
       <c r="E588" s="3" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
+          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
         </is>
       </c>
       <c r="H588" s="2" t="inlineStr">
@@ -39394,16 +39394,16 @@
         </is>
       </c>
       <c r="J588" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Redford Charter Township</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr">
         <is>
-          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
+          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
         </is>
       </c>
       <c r="M588" s="3" t="n"/>
@@ -39425,7 +39425,7 @@
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>📝 Beaumont Medical Center - Redford</t>
+          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
         </is>
       </c>
       <c r="E589" s="3" t="inlineStr">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="G589" s="2" t="inlineStr">
         <is>
-          <t>03095e36-e586-4709-8cd8-440a98b9bcd7</t>
+          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
         </is>
       </c>
       <c r="H589" s="2" t="inlineStr">
@@ -39454,16 +39454,16 @@
         </is>
       </c>
       <c r="J589" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K589" s="2" t="inlineStr">
         <is>
-          <t>Redford Charter Township</t>
+          <t>Redford</t>
         </is>
       </c>
       <c r="L589" s="3" t="inlineStr">
         <is>
-          <t>15540 Beech Daly, Redford Charter Township, Michigan, 48239</t>
+          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
         </is>
       </c>
       <c r="M589" s="3" t="n"/>
@@ -39485,7 +39485,7 @@
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>📝 ARBOR LANE FAMILY PHYSICIANS</t>
+          <t>📝 AGHA INTERNAL MEDICINE AND ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>ff61f8fa-5169-42e7-aafe-f189027c5f3a</t>
+          <t>85fd21cb-8cbc-4ead-9b3d-0cdbecdf7638</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -39518,12 +39518,12 @@
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Redford</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr">
         <is>
-          <t>24224 JOY RD STE 100, REDFORD, Michigan</t>
+          <t>15604 FARMINGTON RD, LIVONIA, MI, 48154</t>
         </is>
       </c>
       <c r="M590" s="3" t="n"/>
@@ -42005,45 +42005,45 @@
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>📝 Universal Clinic &amp; Urgent Care</t>
+          <t>Clinton Preferred Pediatrics</t>
         </is>
       </c>
       <c r="E632" s="3" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Sep 2</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F632" s="2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G632" s="2" t="inlineStr">
         <is>
-          <t>d689dac9-8b56-4f6e-9ba4-8bf3eb8e3550</t>
+          <t>abd1a370-f826-48dd-a800-9a15983f52e8</t>
         </is>
       </c>
       <c r="H632" s="2" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I632" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J632" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K632" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr">
         <is>
-          <t>4600 14 Mile Rd ste 1, Warren, Michigan, 48092</t>
+          <t>15500 19 Mile Rd Suite 300, Clinton Township, MI 48038</t>
         </is>
       </c>
       <c r="M632" s="3" t="n"/>
@@ -42065,12 +42065,12 @@
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>📝 Henry Ford Warren Family Physicians</t>
+          <t>📝 Macomb Internal Medicine</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Jul 10</t>
         </is>
       </c>
       <c r="F633" s="2" t="inlineStr">
@@ -42080,7 +42080,7 @@
       </c>
       <c r="G633" s="2" t="inlineStr">
         <is>
-          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
+          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
         </is>
       </c>
       <c r="H633" s="2" t="inlineStr">
@@ -42094,16 +42094,16 @@
         </is>
       </c>
       <c r="J633" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K633" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L633" s="3" t="inlineStr">
         <is>
-          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
+          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
         </is>
       </c>
       <c r="M633" s="3" t="n"/>
@@ -42125,12 +42125,12 @@
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
+          <t>📝 Swetech Medical Center</t>
         </is>
       </c>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 27</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F634" s="2" t="inlineStr">
@@ -42140,7 +42140,7 @@
       </c>
       <c r="G634" s="2" t="inlineStr">
         <is>
-          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
+          <t>1255427209</t>
         </is>
       </c>
       <c r="H634" s="2" t="inlineStr">
@@ -42158,12 +42158,12 @@
       </c>
       <c r="K634" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr">
         <is>
-          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
+          <t>43600 Garfield Rd, Clinton Township, Michigan, 48038</t>
         </is>
       </c>
       <c r="M634" s="3" t="n"/>
@@ -42185,12 +42185,12 @@
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>📝 Northpointe Pediatrics</t>
+          <t>Macomb Pediatrics - Clinton Township</t>
         </is>
       </c>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 8</t>
+          <t>Tier 1 producer · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F635" s="2" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="G635" s="2" t="inlineStr">
         <is>
-          <t>31b0544c-cc2c-4479-9df9-b11748ecefc7</t>
+          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
         </is>
       </c>
       <c r="H635" s="2" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="I635" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J635" s="2" t="n">
@@ -42218,12 +42218,12 @@
       </c>
       <c r="K635" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Clinton Township</t>
         </is>
       </c>
       <c r="L635" s="3" t="inlineStr">
         <is>
-          <t>30061 Schoenherr Rd, Warren, Michigan, 48088</t>
+          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
         </is>
       </c>
       <c r="M635" s="3" t="n"/>
@@ -42305,12 +42305,12 @@
       </c>
       <c r="D637" s="3" t="inlineStr">
         <is>
-          <t>Macomb Pediatrics - Clinton Township</t>
+          <t>📝 Legacy Family Medicine</t>
         </is>
       </c>
       <c r="E637" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F637" s="2" t="inlineStr">
@@ -42320,17 +42320,17 @@
       </c>
       <c r="G637" s="2" t="inlineStr">
         <is>
-          <t>9e284312-a8af-43ff-9b39-5d4a8c1ed834</t>
+          <t>1558340356</t>
         </is>
       </c>
       <c r="H637" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I637" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J637" s="2" t="n">
@@ -42338,12 +42338,12 @@
       </c>
       <c r="K637" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L637" s="3" t="inlineStr">
         <is>
-          <t>39200 Garfield Rd Suite E Clinton Twp, Clinton Township, MI 48038</t>
+          <t>35429 Schoenherr Rd, Sterling Heights, MI, 48312</t>
         </is>
       </c>
       <c r="M637" s="3" t="n"/>
@@ -42365,12 +42365,12 @@
       </c>
       <c r="D638" s="3" t="inlineStr">
         <is>
-          <t>📝 Macomb Internal Medicine</t>
+          <t>📝 Henry Ford Warren Family Physicians</t>
         </is>
       </c>
       <c r="E638" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 10</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F638" s="2" t="inlineStr">
@@ -42380,7 +42380,7 @@
       </c>
       <c r="G638" s="2" t="inlineStr">
         <is>
-          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
+          <t>6771a475-3022-40fd-9db9-b8e0291f7082</t>
         </is>
       </c>
       <c r="H638" s="2" t="inlineStr">
@@ -42394,16 +42394,16 @@
         </is>
       </c>
       <c r="J638" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K638" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr">
         <is>
-          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
+          <t>11270 East Thirteen Mile Road, Warren, Michigan, 48093</t>
         </is>
       </c>
       <c r="M638" s="3" t="n"/>
@@ -42425,12 +42425,12 @@
       </c>
       <c r="D639" s="3" t="inlineStr">
         <is>
-          <t>Clinton Preferred Pediatrics</t>
+          <t>📝 DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
         </is>
       </c>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Aug 27</t>
         </is>
       </c>
       <c r="F639" s="2" t="inlineStr">
@@ -42440,17 +42440,17 @@
       </c>
       <c r="G639" s="2" t="inlineStr">
         <is>
-          <t>abd1a370-f826-48dd-a800-9a15983f52e8</t>
+          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
         </is>
       </c>
       <c r="H639" s="2" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I639" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J639" s="2" t="n">
@@ -42458,12 +42458,12 @@
       </c>
       <c r="K639" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L639" s="3" t="inlineStr">
         <is>
-          <t>15500 19 Mile Rd Suite 300, Clinton Township, MI 48038</t>
+          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
         </is>
       </c>
       <c r="M639" s="3" t="n"/>
@@ -42485,45 +42485,45 @@
       </c>
       <c r="D640" s="3" t="inlineStr">
         <is>
-          <t>📝 Swetech Medical Center</t>
+          <t>Emcura Immediate Care - Grosse Pointe</t>
         </is>
       </c>
       <c r="E640" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 7</t>
+          <t>Prospect · last check-in Jun 3</t>
         </is>
       </c>
       <c r="F640" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G640" s="2" t="inlineStr">
         <is>
-          <t>1255427209</t>
+          <t>bf549ea4-0d9c-4877-927c-ed3f99bf0988</t>
         </is>
       </c>
       <c r="H640" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I640" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J640" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K640" s="2" t="inlineStr">
         <is>
-          <t>Clinton Township</t>
+          <t>Grosse Pointe Woods</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr">
         <is>
-          <t>43600 Garfield Rd, Clinton Township, Michigan, 48038</t>
+          <t>20599 Mack Ave, Grosse Pointe Woods, MI 48236</t>
         </is>
       </c>
       <c r="M640" s="3" t="n"/>
@@ -43145,12 +43145,12 @@
       </c>
       <c r="D651" s="3" t="inlineStr">
         <is>
-          <t>Core Med  - White Lake</t>
+          <t>📝 Center For Hollistic Medicine</t>
         </is>
       </c>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 21</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F651" s="2" t="inlineStr">
@@ -43160,17 +43160,17 @@
       </c>
       <c r="G651" s="2" t="inlineStr">
         <is>
-          <t>ecbe00dd-1c49-4028-a575-d8852e23deba</t>
+          <t>42b038b0-949b-46be-8843-e02868bb894a</t>
         </is>
       </c>
       <c r="H651" s="2" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>Other / Verify</t>
         </is>
       </c>
       <c r="I651" s="2" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="J651" s="2" t="n">
@@ -43178,12 +43178,12 @@
       </c>
       <c r="K651" s="2" t="inlineStr">
         <is>
-          <t>White Lake Charter Township</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L651" s="3" t="inlineStr">
         <is>
-          <t>8355 Highland Road, White Lake Charter Township, MI 48386</t>
+          <t>6089 W MAPLE RD STE 200, WEST BLOOMFIELD, Michigan</t>
         </is>
       </c>
       <c r="M651" s="3" t="n"/>
@@ -43265,27 +43265,27 @@
       </c>
       <c r="D653" s="3" t="inlineStr">
         <is>
-          <t>📝 Legacy Family Care</t>
+          <t>📝 Corewell URGENT CARE BY WELLSTREET</t>
         </is>
       </c>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 19</t>
+          <t>Prospect · last check-in Jul 29</t>
         </is>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
+          <t>5f3e3632-715d-4e1c-b4ca-4c6bc3dac21e</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I653" s="2" t="inlineStr">
@@ -43294,16 +43294,16 @@
         </is>
       </c>
       <c r="J653" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K653" s="2" t="inlineStr">
         <is>
-          <t>Farmington Hills</t>
+          <t>Bloomfield Township</t>
         </is>
       </c>
       <c r="L653" s="3" t="inlineStr">
         <is>
-          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
+          <t>6543 TELEGRAPH RD, BLOOMFIELD TOWNSHIP, Michigan</t>
         </is>
       </c>
       <c r="M653" s="3" t="n"/>
@@ -43325,12 +43325,12 @@
       </c>
       <c r="D654" s="3" t="inlineStr">
         <is>
-          <t>📝 Jian Zu MD</t>
+          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
         </is>
       </c>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F654" s="2" t="inlineStr">
@@ -43340,7 +43340,7 @@
       </c>
       <c r="G654" s="2" t="inlineStr">
         <is>
-          <t>85043f4d-a0d7-448b-9a3d-e0943de69dd8</t>
+          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
         </is>
       </c>
       <c r="H654" s="2" t="inlineStr">
@@ -43358,12 +43358,12 @@
       </c>
       <c r="K654" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Bloomfield</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr">
         <is>
-          <t>29355 Northwestern Hwy, Southfield, Michigan, 48034</t>
+          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
         </is>
       </c>
       <c r="M654" s="3" t="n"/>
@@ -43385,12 +43385,12 @@
       </c>
       <c r="D655" s="3" t="inlineStr">
         <is>
-          <t>📝 Carson Center Specialty</t>
+          <t>Oakland Medical Center</t>
         </is>
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 29</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F655" s="2" t="inlineStr">
@@ -43400,30 +43400,30 @@
       </c>
       <c r="G655" s="2" t="inlineStr">
         <is>
-          <t>fe708f7e-ac39-4cb4-91fb-ef244909b360</t>
+          <t>77bba5d4-d050-4705-b292-6e3a8a78dec8</t>
         </is>
       </c>
       <c r="H655" s="2" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I655" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J655" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K655" s="2" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L655" s="3" t="inlineStr">
         <is>
-          <t>29355 NORTHWESTERN HWY STE 120, SOUTHFIELD, MI, 48034</t>
+          <t>115 E Long Lake Rd, Troy, MI 48085</t>
         </is>
       </c>
       <c r="M655" s="3" t="n"/>
@@ -43445,12 +43445,12 @@
       </c>
       <c r="D656" s="3" t="inlineStr">
         <is>
-          <t>📝 ROSE MEDICINE</t>
+          <t>📝 Brigid Healthcare</t>
         </is>
       </c>
       <c r="E656" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 14</t>
         </is>
       </c>
       <c r="F656" s="2" t="inlineStr">
@@ -43460,7 +43460,7 @@
       </c>
       <c r="G656" s="2" t="inlineStr">
         <is>
-          <t>9c2f2817-fae0-4fb0-b943-376aef6fc719</t>
+          <t>63bf16ad-3645-45fb-8f1d-e1eb3a131efc</t>
         </is>
       </c>
       <c r="H656" s="2" t="inlineStr">
@@ -43474,16 +43474,16 @@
         </is>
       </c>
       <c r="J656" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K656" s="2" t="inlineStr">
         <is>
-          <t>Bingham Farms</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr">
         <is>
-          <t>31500 TELEGRAPH RD STE 115, BINGHAM FARMS, MI, 48025</t>
+          <t>3456 Rochester Rd, Troy, Michigan, 48083</t>
         </is>
       </c>
       <c r="M656" s="3" t="n"/>
@@ -43505,12 +43505,12 @@
       </c>
       <c r="D657" s="3" t="inlineStr">
         <is>
-          <t>📝 Berkley Urgent Care</t>
+          <t>📝 MedPro Primary Care</t>
         </is>
       </c>
       <c r="E657" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F657" s="2" t="inlineStr">
@@ -43520,7 +43520,7 @@
       </c>
       <c r="G657" s="2" t="inlineStr">
         <is>
-          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
+          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
         </is>
       </c>
       <c r="H657" s="2" t="inlineStr">
@@ -43534,16 +43534,16 @@
         </is>
       </c>
       <c r="J657" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K657" s="2" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Madison Heights</t>
         </is>
       </c>
       <c r="L657" s="3" t="inlineStr">
         <is>
-          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
+          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
         </is>
       </c>
       <c r="M657" s="3" t="n"/>
@@ -43565,12 +43565,12 @@
       </c>
       <c r="D658" s="3" t="inlineStr">
         <is>
-          <t>📝 MedPro Primary Care</t>
+          <t>📝 Berkley Urgent Care</t>
         </is>
       </c>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Tier 1 producer · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F658" s="2" t="inlineStr">
@@ -43580,7 +43580,7 @@
       </c>
       <c r="G658" s="2" t="inlineStr">
         <is>
-          <t>eebb725b-b031-43b9-a3d7-bfa83d77bc18</t>
+          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
         </is>
       </c>
       <c r="H658" s="2" t="inlineStr">
@@ -43594,16 +43594,16 @@
         </is>
       </c>
       <c r="J658" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K658" s="2" t="inlineStr">
         <is>
-          <t>Madison Heights</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr">
         <is>
-          <t>31005 John R Rd suite a, Madison Heights, Michigan, 48071</t>
+          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
         </is>
       </c>
       <c r="M658" s="3" t="n"/>
@@ -43625,12 +43625,12 @@
       </c>
       <c r="D659" s="3" t="inlineStr">
         <is>
-          <t>📝 Brigid Healthcare</t>
+          <t>📝 Legacy Family Care</t>
         </is>
       </c>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 14</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F659" s="2" t="inlineStr">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="G659" s="2" t="inlineStr">
         <is>
-          <t>63bf16ad-3645-45fb-8f1d-e1eb3a131efc</t>
+          <t>6a6a4408-2a28-4e5b-aea6-b70d4b47d57c</t>
         </is>
       </c>
       <c r="H659" s="2" t="inlineStr">
@@ -43654,16 +43654,16 @@
         </is>
       </c>
       <c r="J659" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K659" s="2" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Farmington Hills</t>
         </is>
       </c>
       <c r="L659" s="3" t="inlineStr">
         <is>
-          <t>3456 Rochester Rd, Troy, Michigan, 48083</t>
+          <t>23800 Orchard Lake Rd suite 202, Farmington Hills, Michigan, 48336</t>
         </is>
       </c>
       <c r="M659" s="3" t="n"/>
@@ -43685,12 +43685,12 @@
       </c>
       <c r="D660" s="3" t="inlineStr">
         <is>
-          <t>📝 TWIN LAKES MEDICAL ASSOCIATES, PC</t>
+          <t>📝 Village Medical Farmington</t>
         </is>
       </c>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 16</t>
+          <t>Tier 1 producer · last check-in Aug 19</t>
         </is>
       </c>
       <c r="F660" s="2" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>e7b52c83-5403-4607-98fb-61ffa473ccc4</t>
+          <t>8a6ae159-0242-4272-b933-bd11fc117733</t>
         </is>
       </c>
       <c r="H660" s="2" t="inlineStr">
@@ -43714,16 +43714,16 @@
         </is>
       </c>
       <c r="J660" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K660" s="2" t="inlineStr">
         <is>
-          <t>Bloomfield</t>
+          <t>Farmington</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr">
         <is>
-          <t>43700 WOODWARD AVE STE 206, BLOOMFIELD, Michigan, MI 48302</t>
+          <t>23133 Orchard Lake Rd, Farmington, Michigan, 48336</t>
         </is>
       </c>
       <c r="M660" s="3" t="n"/>
@@ -66345,7 +66345,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>14</v>
@@ -66354,7 +66354,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -66370,7 +66370,7 @@
         <v>50</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>6</v>
@@ -66379,7 +66379,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -66420,7 +66420,7 @@
         <v>49</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>12</v>
@@ -66429,7 +66429,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
